--- a/sql/Prop book.xlsx
+++ b/sql/Prop book.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thao Dien\Broker-page - Copy\sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720B4B4B-A6DC-43EF-8FC1-0C386E7F40AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B877029-A2A8-47B3-86DB-E47FB8872915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="84">
   <si>
     <t>Broker</t>
   </si>
@@ -282,6 +282,12 @@
   </si>
   <si>
     <t>DCM</t>
+  </si>
+  <si>
+    <t>IDC</t>
+  </si>
+  <si>
+    <t>TLP</t>
   </si>
 </sst>
 </file>
@@ -644,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E274"/>
+  <dimension ref="A1:E286"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -4451,6 +4457,171 @@
         <v>156.172</v>
       </c>
     </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A275" t="s">
+        <v>18</v>
+      </c>
+      <c r="B275" t="s">
+        <v>79</v>
+      </c>
+      <c r="C275" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
+        <v>18</v>
+      </c>
+      <c r="B276" t="s">
+        <v>79</v>
+      </c>
+      <c r="C276" t="s">
+        <v>20</v>
+      </c>
+      <c r="D276">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A277" t="s">
+        <v>18</v>
+      </c>
+      <c r="B277" t="s">
+        <v>79</v>
+      </c>
+      <c r="C277" t="s">
+        <v>21</v>
+      </c>
+      <c r="D277">
+        <v>8.3079999999999998</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A278" t="s">
+        <v>18</v>
+      </c>
+      <c r="B278" t="s">
+        <v>79</v>
+      </c>
+      <c r="C278" t="s">
+        <v>24</v>
+      </c>
+      <c r="D278">
+        <v>111.676</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A279" t="s">
+        <v>18</v>
+      </c>
+      <c r="B279" t="s">
+        <v>79</v>
+      </c>
+      <c r="C279" t="s">
+        <v>22</v>
+      </c>
+      <c r="D279">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A280" t="s">
+        <v>18</v>
+      </c>
+      <c r="B280" t="s">
+        <v>79</v>
+      </c>
+      <c r="C280" t="s">
+        <v>23</v>
+      </c>
+      <c r="D280">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A281" t="s">
+        <v>18</v>
+      </c>
+      <c r="B281" t="s">
+        <v>79</v>
+      </c>
+      <c r="C281" t="s">
+        <v>36</v>
+      </c>
+      <c r="D281">
+        <v>66.446399999999997</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>18</v>
+      </c>
+      <c r="B282" t="s">
+        <v>79</v>
+      </c>
+      <c r="C282" t="s">
+        <v>82</v>
+      </c>
+      <c r="D282">
+        <v>60.198599999999999</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>18</v>
+      </c>
+      <c r="B283" t="s">
+        <v>79</v>
+      </c>
+      <c r="C283" t="s">
+        <v>25</v>
+      </c>
+      <c r="D283">
+        <v>16.675999999999998</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>18</v>
+      </c>
+      <c r="B284" t="s">
+        <v>79</v>
+      </c>
+      <c r="C284" t="s">
+        <v>83</v>
+      </c>
+      <c r="D284">
+        <v>16.715</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>18</v>
+      </c>
+      <c r="B285" t="s">
+        <v>79</v>
+      </c>
+      <c r="C285" t="s">
+        <v>68</v>
+      </c>
+      <c r="D285">
+        <v>38.396999999999998</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>18</v>
+      </c>
+      <c r="B286" t="s">
+        <v>79</v>
+      </c>
+      <c r="C286" t="s">
+        <v>76</v>
+      </c>
+      <c r="D286">
+        <v>4.25</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E250" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sql/Prop book.xlsx
+++ b/sql/Prop book.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thao Dien\Broker-page - Copy\sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B877029-A2A8-47B3-86DB-E47FB8872915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA8E0539-8004-4912-8A4C-8B975AC554BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="84">
   <si>
     <t>Broker</t>
   </si>
@@ -650,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E286"/>
+  <dimension ref="A1:E290"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -4622,6 +4622,62 @@
         <v>4.25</v>
       </c>
     </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>18</v>
+      </c>
+      <c r="B287" t="s">
+        <v>79</v>
+      </c>
+      <c r="C287" t="s">
+        <v>40</v>
+      </c>
+      <c r="D287">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>70</v>
+      </c>
+      <c r="B288" t="s">
+        <v>79</v>
+      </c>
+      <c r="C288" t="s">
+        <v>40</v>
+      </c>
+      <c r="D288">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>23</v>
+      </c>
+      <c r="B289" t="s">
+        <v>79</v>
+      </c>
+      <c r="C289" t="s">
+        <v>40</v>
+      </c>
+      <c r="D289">
+        <v>3048</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>26</v>
+      </c>
+      <c r="B290" t="s">
+        <v>79</v>
+      </c>
+      <c r="C290" t="s">
+        <v>40</v>
+      </c>
+      <c r="D290">
+        <v>590</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E250" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sql/Prop book.xlsx
+++ b/sql/Prop book.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thao Dien\Broker-page - Copy\sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA8E0539-8004-4912-8A4C-8B975AC554BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08ACD8CC-490C-46AF-95C2-CE61CCCFF513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="85">
   <si>
     <t>Broker</t>
   </si>
@@ -288,6 +288,9 @@
   </si>
   <si>
     <t>TLP</t>
+  </si>
+  <si>
+    <t>NTP</t>
   </si>
 </sst>
 </file>
@@ -650,7 +653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E290"/>
+  <dimension ref="A1:E294"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -4678,6 +4681,62 @@
         <v>590</v>
       </c>
     </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
+        <v>63</v>
+      </c>
+      <c r="B291" t="s">
+        <v>79</v>
+      </c>
+      <c r="C291" t="s">
+        <v>84</v>
+      </c>
+      <c r="D291">
+        <v>74.397000000000006</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>63</v>
+      </c>
+      <c r="B292" t="s">
+        <v>79</v>
+      </c>
+      <c r="C292" t="s">
+        <v>28</v>
+      </c>
+      <c r="D292">
+        <v>163.31</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A293" t="s">
+        <v>63</v>
+      </c>
+      <c r="B293" t="s">
+        <v>79</v>
+      </c>
+      <c r="C293" t="s">
+        <v>25</v>
+      </c>
+      <c r="D293">
+        <v>534.41600000000005</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A294" t="s">
+        <v>63</v>
+      </c>
+      <c r="B294" t="s">
+        <v>79</v>
+      </c>
+      <c r="C294" t="s">
+        <v>40</v>
+      </c>
+      <c r="D294">
+        <v>269</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E250" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sql/Prop book.xlsx
+++ b/sql/Prop book.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thao Dien\Broker-page - Copy\sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08ACD8CC-490C-46AF-95C2-CE61CCCFF513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFA3FBD-C7A4-496D-82BC-F545E27008B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/sql/Prop book.xlsx
+++ b/sql/Prop book.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thao Dien\Broker-page - Copy\sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFA3FBD-C7A4-496D-82BC-F545E27008B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4567CC0A-2E50-45C3-A8BA-4541552761D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$250</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$320</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="91">
   <si>
     <t>Broker</t>
   </si>
@@ -291,6 +291,24 @@
   </si>
   <si>
     <t>NTP</t>
+  </si>
+  <si>
+    <t>BID</t>
+  </si>
+  <si>
+    <t>VIC</t>
+  </si>
+  <si>
+    <t>LPB</t>
+  </si>
+  <si>
+    <t>DGC</t>
+  </si>
+  <si>
+    <t>GAS</t>
+  </si>
+  <si>
+    <t>SAB</t>
   </si>
 </sst>
 </file>
@@ -346,11 +364,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -653,8 +672,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E294"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:E326"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="6" width="10.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -1039,7 +1062,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -1053,7 +1076,7 @@
         <v>172.64</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -1067,7 +1090,7 @@
         <v>282.2</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -1081,7 +1104,7 @@
         <v>7.84</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -1095,7 +1118,7 @@
         <v>64.372</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -1109,7 +1132,7 @@
         <v>105.5</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -1123,7 +1146,7 @@
         <v>87.8</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -1137,7 +1160,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>26</v>
       </c>
@@ -1151,7 +1174,7 @@
         <v>287.54000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>26</v>
       </c>
@@ -1165,7 +1188,7 @@
         <v>177.85</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>26</v>
       </c>
@@ -1179,7 +1202,7 @@
         <v>252.98500000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>26</v>
       </c>
@@ -1193,7 +1216,7 @@
         <v>91.463300000000004</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>26</v>
       </c>
@@ -1204,7 +1227,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>26</v>
       </c>
@@ -1219,7 +1242,7 @@
         <v>3843.058</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>26</v>
       </c>
@@ -1233,7 +1256,7 @@
         <v>275.23899999999998</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>26</v>
       </c>
@@ -1247,7 +1270,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -1261,7 +1284,7 @@
         <v>189.8</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -1275,7 +1298,7 @@
         <v>106.4</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -1289,7 +1312,7 @@
         <v>204.8</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -1303,7 +1326,7 @@
         <v>79.099999999999994</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -1317,7 +1340,7 @@
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -1331,7 +1354,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -1345,7 +1368,7 @@
         <v>170.9</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -1359,7 +1382,7 @@
         <v>238.4</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -1373,7 +1396,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -1387,7 +1410,7 @@
         <v>91.6</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -1401,7 +1424,7 @@
         <v>71.3</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -1415,7 +1438,7 @@
         <v>47.6</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -1429,7 +1452,7 @@
         <v>178.9</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -1443,7 +1466,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>23</v>
       </c>
@@ -1457,7 +1480,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>23</v>
       </c>
@@ -1471,7 +1494,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>23</v>
       </c>
@@ -1485,7 +1508,7 @@
         <v>734.97</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>23</v>
       </c>
@@ -1499,7 +1522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>23</v>
       </c>
@@ -1513,7 +1536,7 @@
         <v>683.3</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>23</v>
       </c>
@@ -1527,7 +1550,7 @@
         <v>428.9</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>23</v>
       </c>
@@ -1541,7 +1564,7 @@
         <v>4362.4489999999996</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>23</v>
       </c>
@@ -1555,7 +1578,7 @@
         <v>684.67200000000003</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>23</v>
       </c>
@@ -1569,7 +1592,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>23</v>
       </c>
@@ -1583,7 +1606,7 @@
         <v>298.214</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>26</v>
       </c>
@@ -1597,7 +1620,7 @@
         <v>462.96722006800002</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>23</v>
       </c>
@@ -1611,7 +1634,7 @@
         <v>1602.507328938</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>26</v>
       </c>
@@ -1625,7 +1648,7 @@
         <v>281.90273591300001</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>26</v>
       </c>
@@ -1639,7 +1662,7 @@
         <v>325.68608381000001</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>23</v>
       </c>
@@ -1653,7 +1676,7 @@
         <v>133.6666776649999</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>23</v>
       </c>
@@ -1667,7 +1690,7 @@
         <v>465.20486131000013</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -1681,7 +1704,7 @@
         <v>73.276574532000055</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -1695,7 +1718,7 @@
         <v>132.5779621770001</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -1751,7 +1774,7 @@
         <v>211.49055106</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>26</v>
       </c>
@@ -1765,7 +1788,7 @@
         <v>313.72500000000002</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>26</v>
       </c>
@@ -1779,7 +1802,7 @@
         <v>252.69882000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>26</v>
       </c>
@@ -1793,7 +1816,7 @@
         <v>131.61000000000001</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>26</v>
       </c>
@@ -1807,7 +1830,7 @@
         <v>115.5</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>26</v>
       </c>
@@ -1821,7 +1844,7 @@
         <v>80.653409999999994</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>26</v>
       </c>
@@ -1835,7 +1858,7 @@
         <v>4593.8958050000001</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>26</v>
       </c>
@@ -1846,7 +1869,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>26</v>
       </c>
@@ -1857,7 +1880,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>26</v>
       </c>
@@ -1871,7 +1894,7 @@
         <v>385.00864000000001</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>26</v>
       </c>
@@ -1885,7 +1908,7 @@
         <v>204.87155000000001</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>26</v>
       </c>
@@ -1899,7 +1922,7 @@
         <v>449.16890000000001</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>26</v>
       </c>
@@ -1913,7 +1936,7 @@
         <v>298.416</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>26</v>
       </c>
@@ -1927,7 +1950,7 @@
         <v>2868.1795425969999</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>26</v>
       </c>
@@ -1938,7 +1961,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>26</v>
       </c>
@@ -1949,7 +1972,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>44</v>
       </c>
@@ -1963,7 +1986,7 @@
         <v>471.11800299999999</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>44</v>
       </c>
@@ -1977,7 +2000,7 @@
         <v>444.90018559999999</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>44</v>
       </c>
@@ -1991,7 +2014,7 @@
         <v>194.95070833</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>44</v>
       </c>
@@ -2005,7 +2028,7 @@
         <v>459.73992199999998</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>44</v>
       </c>
@@ -2019,7 +2042,7 @@
         <v>105.4291377</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>44</v>
       </c>
@@ -2033,7 +2056,7 @@
         <v>112.9934461</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>44</v>
       </c>
@@ -2047,7 +2070,7 @@
         <v>795.19149128900006</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>44</v>
       </c>
@@ -2061,7 +2084,7 @@
         <v>418.20360959999999</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>44</v>
       </c>
@@ -2075,7 +2098,7 @@
         <v>379.16809019999999</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>44</v>
       </c>
@@ -2089,7 +2112,7 @@
         <v>641.44849673199997</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>46</v>
       </c>
@@ -2103,7 +2126,7 @@
         <v>495.18126749999999</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>46</v>
       </c>
@@ -2117,7 +2140,7 @@
         <v>41.564160000000001</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>46</v>
       </c>
@@ -2131,7 +2154,7 @@
         <v>34.574301900000002</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>46</v>
       </c>
@@ -2145,7 +2168,7 @@
         <v>17.764817699999998</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>46</v>
       </c>
@@ -2159,7 +2182,7 @@
         <v>377.74047731399997</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>46</v>
       </c>
@@ -2173,7 +2196,7 @@
         <v>47.814399999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>46</v>
       </c>
@@ -2187,7 +2210,7 @@
         <v>105.3778854</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>46</v>
       </c>
@@ -2201,7 +2224,7 @@
         <v>45.304979000000003</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>46</v>
       </c>
@@ -2215,7 +2238,7 @@
         <v>883.491355</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>46</v>
       </c>
@@ -2229,7 +2252,7 @@
         <v>329.83531951999998</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>46</v>
       </c>
@@ -2243,7 +2266,7 @@
         <v>56.4498575</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>46</v>
       </c>
@@ -2257,7 +2280,7 @@
         <v>48.783651149999997</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>46</v>
       </c>
@@ -2271,7 +2294,7 @@
         <v>53.905700000000003</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>46</v>
       </c>
@@ -2285,7 +2308,7 @@
         <v>897.44555519999994</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>46</v>
       </c>
@@ -2299,7 +2322,7 @@
         <v>567.41111581400003</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>50</v>
       </c>
@@ -2313,7 +2336,7 @@
         <v>1219.89348</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>50</v>
       </c>
@@ -2327,7 +2350,7 @@
         <v>891.07434000000001</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>50</v>
       </c>
@@ -2341,7 +2364,7 @@
         <v>386.46965</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>50</v>
       </c>
@@ -2355,7 +2378,7 @@
         <v>376.3553</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>50</v>
       </c>
@@ -2369,7 +2392,7 @@
         <v>258.97612800000002</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>50</v>
       </c>
@@ -2383,7 +2406,7 @@
         <v>157.063692</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>50</v>
       </c>
@@ -2397,7 +2420,7 @@
         <v>80.896979999999999</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>50</v>
       </c>
@@ -2411,7 +2434,7 @@
         <v>66.592600000000004</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>50</v>
       </c>
@@ -2425,7 +2448,7 @@
         <v>35.567970000000003</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>50</v>
       </c>
@@ -2439,7 +2462,7 @@
         <v>32.722560000000001</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>50</v>
       </c>
@@ -2453,7 +2476,7 @@
         <v>76.413469636000002</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>50</v>
       </c>
@@ -2467,7 +2490,7 @@
         <v>51.984900000000003</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>50</v>
       </c>
@@ -2481,7 +2504,7 @@
         <v>54.700949999999999</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>50</v>
       </c>
@@ -2495,7 +2518,7 @@
         <v>43.162300000000002</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>50</v>
       </c>
@@ -2509,7 +2532,7 @@
         <v>37.572000000000003</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>50</v>
       </c>
@@ -2523,7 +2546,7 @@
         <v>26.318750000000001</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>50</v>
       </c>
@@ -2537,7 +2560,7 @@
         <v>24.028199999999998</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>50</v>
       </c>
@@ -2551,7 +2574,7 @@
         <v>21.36645</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>50</v>
       </c>
@@ -2565,7 +2588,7 @@
         <v>17.355250000000002</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>50</v>
       </c>
@@ -2579,7 +2602,7 @@
         <v>17.120100000000001</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>50</v>
       </c>
@@ -2593,7 +2616,7 @@
         <v>16.202475</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>50</v>
       </c>
@@ -2607,7 +2630,7 @@
         <v>13.5169</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>50</v>
       </c>
@@ -2621,7 +2644,7 @@
         <v>8.3619000000000003</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>50</v>
       </c>
@@ -2635,7 +2658,7 @@
         <v>2.3957999999999999</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>50</v>
       </c>
@@ -2649,7 +2672,7 @@
         <v>1791.136023734</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>50</v>
       </c>
@@ -2663,7 +2686,7 @@
         <v>691.42874749999999</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>50</v>
       </c>
@@ -2677,7 +2700,7 @@
         <v>437.546178</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>50</v>
       </c>
@@ -2691,7 +2714,7 @@
         <v>398.44944659999999</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>50</v>
       </c>
@@ -2705,7 +2728,7 @@
         <v>85.158848000000006</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>50</v>
       </c>
@@ -2719,7 +2742,7 @@
         <v>56.339108600000003</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>50</v>
       </c>
@@ -2733,7 +2756,7 @@
         <v>50.207640599999998</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>50</v>
       </c>
@@ -2747,7 +2770,7 @@
         <v>48.181075200000002</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>50</v>
       </c>
@@ -2761,7 +2784,7 @@
         <v>48.151496999999999</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>50</v>
       </c>
@@ -2775,7 +2798,7 @@
         <v>38.785400000000003</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>50</v>
       </c>
@@ -2789,7 +2812,7 @@
         <v>33.768990000000002</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>50</v>
       </c>
@@ -2803,7 +2826,7 @@
         <v>27.742000000000001</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>50</v>
       </c>
@@ -2817,7 +2840,7 @@
         <v>26.166374399999999</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>50</v>
       </c>
@@ -2831,7 +2854,7 @@
         <v>312.90250348900003</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>61</v>
       </c>
@@ -2845,7 +2868,7 @@
         <v>537.23077231399998</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>61</v>
       </c>
@@ -2859,7 +2882,7 @@
         <v>1.2738610640000001</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>61</v>
       </c>
@@ -2873,7 +2896,7 @@
         <v>571.68737199999998</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>61</v>
       </c>
@@ -2887,7 +2910,7 @@
         <v>1.2426057850000001</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>63</v>
       </c>
@@ -2901,7 +2924,7 @@
         <v>81.770314499999998</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>63</v>
       </c>
@@ -2915,7 +2938,7 @@
         <v>114.13664420000001</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>63</v>
       </c>
@@ -2929,7 +2952,7 @@
         <v>74.028000000000006</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>63</v>
       </c>
@@ -2943,7 +2966,7 @@
         <v>334.50573044999999</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>63</v>
       </c>
@@ -2957,7 +2980,7 @@
         <v>82.876750000000001</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>63</v>
       </c>
@@ -2971,7 +2994,7 @@
         <v>96.033543249999994</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>63</v>
       </c>
@@ -2985,7 +3008,7 @@
         <v>619.63735652000003</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>63</v>
       </c>
@@ -2999,7 +3022,7 @@
         <v>66.806430000000006</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>63</v>
       </c>
@@ -3013,7 +3036,7 @@
         <v>62.841739349999997</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>63</v>
       </c>
@@ -3027,7 +3050,7 @@
         <v>64.178100000000001</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>63</v>
       </c>
@@ -3041,7 +3064,7 @@
         <v>462.98242733000001</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>64</v>
       </c>
@@ -3052,7 +3075,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>64</v>
       </c>
@@ -3066,7 +3089,7 @@
         <v>1.0325E-4</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>64</v>
       </c>
@@ -3077,7 +3100,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>64</v>
       </c>
@@ -3091,7 +3114,7 @@
         <v>1.1900000000000001E-4</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>64</v>
       </c>
@@ -3102,7 +3125,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>67</v>
       </c>
@@ -3116,7 +3139,7 @@
         <v>64.729280000000003</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>67</v>
       </c>
@@ -3130,7 +3153,7 @@
         <v>4.1003119999999997</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>67</v>
       </c>
@@ -3144,7 +3167,7 @@
         <v>7.8800173759999996</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>67</v>
       </c>
@@ -3158,7 +3181,7 @@
         <v>57.4816</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>67</v>
       </c>
@@ -3172,7 +3195,7 @@
         <v>3.4080650000000001E-3</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>67</v>
       </c>
@@ -3186,7 +3209,7 @@
         <v>9.5435766019999999</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>67</v>
       </c>
@@ -3200,7 +3223,7 @@
         <v>3.4080650000000001E-3</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>63</v>
       </c>
@@ -3214,7 +3237,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>63</v>
       </c>
@@ -3228,7 +3251,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>63</v>
       </c>
@@ -3242,7 +3265,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>61</v>
       </c>
@@ -3256,7 +3279,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>61</v>
       </c>
@@ -3270,7 +3293,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>61</v>
       </c>
@@ -3284,7 +3307,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>50</v>
       </c>
@@ -3298,7 +3321,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>50</v>
       </c>
@@ -3312,7 +3335,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>50</v>
       </c>
@@ -3326,7 +3349,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>64</v>
       </c>
@@ -3340,7 +3363,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>64</v>
       </c>
@@ -3354,7 +3377,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>64</v>
       </c>
@@ -3368,7 +3391,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>67</v>
       </c>
@@ -3382,7 +3405,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>67</v>
       </c>
@@ -3396,7 +3419,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>67</v>
       </c>
@@ -3410,7 +3433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>26</v>
       </c>
@@ -3424,7 +3447,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>26</v>
       </c>
@@ -3438,7 +3461,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>26</v>
       </c>
@@ -3452,7 +3475,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>46</v>
       </c>
@@ -3466,7 +3489,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>46</v>
       </c>
@@ -3480,7 +3503,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>46</v>
       </c>
@@ -3494,7 +3517,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>44</v>
       </c>
@@ -3508,7 +3531,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>44</v>
       </c>
@@ -3522,7 +3545,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>44</v>
       </c>
@@ -3536,7 +3559,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>70</v>
       </c>
@@ -3550,7 +3573,7 @@
         <v>291.53755000000001</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>70</v>
       </c>
@@ -3564,7 +3587,7 @@
         <v>97.599699999999999</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>70</v>
       </c>
@@ -3578,7 +3601,7 @@
         <v>139.96039999999999</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>70</v>
       </c>
@@ -3592,7 +3615,7 @@
         <v>126.0891627</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>70</v>
       </c>
@@ -3606,7 +3629,7 @@
         <v>484.16045324999999</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>70</v>
       </c>
@@ -3620,7 +3643,7 @@
         <v>97.860349999999997</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>70</v>
       </c>
@@ -3634,7 +3657,7 @@
         <v>118.3644</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>70</v>
       </c>
@@ -3648,7 +3671,7 @@
         <v>40.125</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>70</v>
       </c>
@@ -3662,7 +3685,7 @@
         <v>-17.442687286000002</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>70</v>
       </c>
@@ -3676,7 +3699,7 @@
         <v>319.48334</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>70</v>
       </c>
@@ -3690,7 +3713,7 @@
         <v>1110.0100874</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>70</v>
       </c>
@@ -3704,7 +3727,7 @@
         <v>131.24760000000001</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>70</v>
       </c>
@@ -3718,7 +3741,7 @@
         <v>77.801199999999994</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>70</v>
       </c>
@@ -3732,7 +3755,7 @@
         <v>49.610999999999997</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>70</v>
       </c>
@@ -3746,7 +3769,7 @@
         <v>36.58</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>70</v>
       </c>
@@ -3760,7 +3783,7 @@
         <v>22.643851017999999</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>70</v>
       </c>
@@ -3774,7 +3797,7 @@
         <v>147.13238000000001</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>70</v>
       </c>
@@ -3788,7 +3811,7 @@
         <v>102.867975</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>70</v>
       </c>
@@ -3802,7 +3825,7 @@
         <v>125.2624716</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>70</v>
       </c>
@@ -3816,7 +3839,7 @@
         <v>129.71071259999999</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>70</v>
       </c>
@@ -3830,7 +3853,7 @@
         <v>127.5998</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>70</v>
       </c>
@@ -3844,7 +3867,7 @@
         <v>466.77496559999997</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>70</v>
       </c>
@@ -3858,7 +3881,7 @@
         <v>270.72160000000002</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>70</v>
       </c>
@@ -3872,7 +3895,7 @@
         <v>145.33860000000001</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>70</v>
       </c>
@@ -3886,7 +3909,7 @@
         <v>50.883000000000003</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>70</v>
       </c>
@@ -3900,7 +3923,7 @@
         <v>62.96705</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>70</v>
       </c>
@@ -3914,7 +3937,7 @@
         <v>-33.634174170000001</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>74</v>
       </c>
@@ -3928,7 +3951,7 @@
         <v>91.021986687999998</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>74</v>
       </c>
@@ -3942,7 +3965,7 @@
         <v>66.466997524000007</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>74</v>
       </c>
@@ -3956,7 +3979,7 @@
         <v>41.544733348999998</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>23</v>
       </c>
@@ -3970,7 +3993,7 @@
         <v>1935.6160052</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>23</v>
       </c>
@@ -3984,7 +4007,7 @@
         <v>1093.40625</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>23</v>
       </c>
@@ -3998,7 +4021,7 @@
         <v>936.03599999999994</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>23</v>
       </c>
@@ -4012,7 +4035,7 @@
         <v>870.293138</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>23</v>
       </c>
@@ -4026,7 +4049,7 @@
         <v>703.93795499999999</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>23</v>
       </c>
@@ -4040,7 +4063,7 @@
         <v>453.33</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>23</v>
       </c>
@@ -4054,7 +4077,7 @@
         <v>490.97399999999999</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>23</v>
       </c>
@@ -4068,7 +4091,7 @@
         <v>465.35771999999997</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>23</v>
       </c>
@@ -4082,7 +4105,7 @@
         <v>2569.0349262</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>23</v>
       </c>
@@ -4096,7 +4119,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>23</v>
       </c>
@@ -4110,7 +4133,7 @@
         <v>959.69100000000003</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>23</v>
       </c>
@@ -4124,7 +4147,7 @@
         <v>284.44299999999998</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>23</v>
       </c>
@@ -4138,7 +4161,7 @@
         <v>1763.249</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>23</v>
       </c>
@@ -4152,7 +4175,7 @@
         <v>1752.2063000000001</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>23</v>
       </c>
@@ -4166,7 +4189,7 @@
         <v>2495.8277849999999</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>23</v>
       </c>
@@ -4180,7 +4203,7 @@
         <v>2574.3249999999998</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>23</v>
       </c>
@@ -4194,7 +4217,7 @@
         <v>1101.24</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>23</v>
       </c>
@@ -4208,7 +4231,7 @@
         <v>191.304</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>26</v>
       </c>
@@ -4222,7 +4245,7 @@
         <v>388.8</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>26</v>
       </c>
@@ -4236,7 +4259,7 @@
         <v>106.95099999999999</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>26</v>
       </c>
@@ -4250,7 +4273,7 @@
         <v>374.26499999999999</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>26</v>
       </c>
@@ -4264,7 +4287,7 @@
         <v>122.08</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>26</v>
       </c>
@@ -4278,7 +4301,7 @@
         <v>116.294</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>26</v>
       </c>
@@ -4292,7 +4315,7 @@
         <v>3805.7429999999999</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>26</v>
       </c>
@@ -4306,7 +4329,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>26</v>
       </c>
@@ -4320,7 +4343,7 @@
         <v>275.238</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>70</v>
       </c>
@@ -4334,7 +4357,7 @@
         <v>321.96100000000001</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>70</v>
       </c>
@@ -4348,7 +4371,7 @@
         <v>229.74100000000001</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>70</v>
       </c>
@@ -4362,7 +4385,7 @@
         <v>157.09299999999999</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>70</v>
       </c>
@@ -4376,7 +4399,7 @@
         <v>169.16200000000001</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>70</v>
       </c>
@@ -4390,7 +4413,7 @@
         <v>364.79500000000002</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>70</v>
       </c>
@@ -4404,7 +4427,7 @@
         <v>28.222999999999999</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>70</v>
       </c>
@@ -4418,7 +4441,7 @@
         <v>111.91</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>70</v>
       </c>
@@ -4432,7 +4455,7 @@
         <v>92.884</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>70</v>
       </c>
@@ -4446,7 +4469,7 @@
         <v>47.414999999999999</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>70</v>
       </c>
@@ -4460,7 +4483,7 @@
         <v>156.172</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>18</v>
       </c>
@@ -4471,7 +4494,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>18</v>
       </c>
@@ -4485,7 +4508,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>18</v>
       </c>
@@ -4499,7 +4522,7 @@
         <v>8.3079999999999998</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>18</v>
       </c>
@@ -4513,7 +4536,7 @@
         <v>111.676</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>18</v>
       </c>
@@ -4527,7 +4550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>18</v>
       </c>
@@ -4541,7 +4564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>18</v>
       </c>
@@ -4555,7 +4578,7 @@
         <v>66.446399999999997</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>18</v>
       </c>
@@ -4569,7 +4592,7 @@
         <v>60.198599999999999</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>18</v>
       </c>
@@ -4583,7 +4606,7 @@
         <v>16.675999999999998</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>18</v>
       </c>
@@ -4597,7 +4620,7 @@
         <v>16.715</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>18</v>
       </c>
@@ -4611,7 +4634,7 @@
         <v>38.396999999999998</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>18</v>
       </c>
@@ -4625,7 +4648,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>18</v>
       </c>
@@ -4639,7 +4662,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>70</v>
       </c>
@@ -4653,7 +4676,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>23</v>
       </c>
@@ -4667,7 +4690,7 @@
         <v>3048</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>26</v>
       </c>
@@ -4681,7 +4704,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>63</v>
       </c>
@@ -4695,7 +4718,7 @@
         <v>74.397000000000006</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>63</v>
       </c>
@@ -4709,7 +4732,7 @@
         <v>163.31</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>63</v>
       </c>
@@ -4723,7 +4746,7 @@
         <v>534.41600000000005</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>63</v>
       </c>
@@ -4737,8 +4760,462 @@
         <v>269</v>
       </c>
     </row>
+    <row r="295" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A295" t="s">
+        <v>50</v>
+      </c>
+      <c r="B295" t="s">
+        <v>79</v>
+      </c>
+      <c r="C295" t="s">
+        <v>22</v>
+      </c>
+      <c r="D295" s="2">
+        <v>560.84807000000001</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A296" t="s">
+        <v>50</v>
+      </c>
+      <c r="B296" t="s">
+        <v>79</v>
+      </c>
+      <c r="C296" t="s">
+        <v>48</v>
+      </c>
+      <c r="D296" s="2">
+        <v>480.37799999999999</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A297" t="s">
+        <v>50</v>
+      </c>
+      <c r="B297" t="s">
+        <v>79</v>
+      </c>
+      <c r="C297" t="s">
+        <v>41</v>
+      </c>
+      <c r="D297" s="2">
+        <v>457.70800000000003</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A298" t="s">
+        <v>50</v>
+      </c>
+      <c r="B298" t="s">
+        <v>79</v>
+      </c>
+      <c r="C298" t="s">
+        <v>85</v>
+      </c>
+      <c r="D298" s="2">
+        <v>440.096</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A299" t="s">
+        <v>50</v>
+      </c>
+      <c r="B299" t="s">
+        <v>79</v>
+      </c>
+      <c r="C299" t="s">
+        <v>49</v>
+      </c>
+      <c r="D299" s="2">
+        <v>388.70979</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A300" t="s">
+        <v>50</v>
+      </c>
+      <c r="B300" t="s">
+        <v>79</v>
+      </c>
+      <c r="C300" t="s">
+        <v>86</v>
+      </c>
+      <c r="D300" s="2">
+        <v>386.8227</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A301" t="s">
+        <v>50</v>
+      </c>
+      <c r="B301" t="s">
+        <v>79</v>
+      </c>
+      <c r="C301" t="s">
+        <v>10</v>
+      </c>
+      <c r="D301" s="2">
+        <v>324.61559999999997</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A302" t="s">
+        <v>50</v>
+      </c>
+      <c r="B302" t="s">
+        <v>79</v>
+      </c>
+      <c r="C302" t="s">
+        <v>28</v>
+      </c>
+      <c r="D302" s="2">
+        <v>283.223343</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
+        <v>50</v>
+      </c>
+      <c r="B303" t="s">
+        <v>79</v>
+      </c>
+      <c r="C303" t="s">
+        <v>47</v>
+      </c>
+      <c r="D303" s="2">
+        <v>257.17744499999998</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>50</v>
+      </c>
+      <c r="B304" t="s">
+        <v>79</v>
+      </c>
+      <c r="C304" t="s">
+        <v>87</v>
+      </c>
+      <c r="D304" s="2">
+        <v>267.80786999999998</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A305" t="s">
+        <v>50</v>
+      </c>
+      <c r="B305" t="s">
+        <v>79</v>
+      </c>
+      <c r="C305" t="s">
+        <v>11</v>
+      </c>
+      <c r="D305" s="2">
+        <v>236.04599999999999</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A306" t="s">
+        <v>50</v>
+      </c>
+      <c r="B306" t="s">
+        <v>79</v>
+      </c>
+      <c r="C306" t="s">
+        <v>57</v>
+      </c>
+      <c r="D306" s="2">
+        <v>207.93639999999999</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A307" t="s">
+        <v>50</v>
+      </c>
+      <c r="B307" t="s">
+        <v>79</v>
+      </c>
+      <c r="C307" t="s">
+        <v>88</v>
+      </c>
+      <c r="D307" s="2">
+        <v>184.02464000000001</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A308" t="s">
+        <v>50</v>
+      </c>
+      <c r="B308" t="s">
+        <v>79</v>
+      </c>
+      <c r="C308" t="s">
+        <v>60</v>
+      </c>
+      <c r="D308" s="2">
+        <v>186.27279999999999</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
+        <v>50</v>
+      </c>
+      <c r="B309" t="s">
+        <v>79</v>
+      </c>
+      <c r="C309" t="s">
+        <v>89</v>
+      </c>
+      <c r="D309" s="2">
+        <v>181.30464520000001</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>50</v>
+      </c>
+      <c r="B310" t="s">
+        <v>79</v>
+      </c>
+      <c r="C310" t="s">
+        <v>90</v>
+      </c>
+      <c r="D310" s="2">
+        <v>180.90083999999999</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>50</v>
+      </c>
+      <c r="B311" t="s">
+        <v>79</v>
+      </c>
+      <c r="C311" t="s">
+        <v>27</v>
+      </c>
+      <c r="D311" s="2">
+        <v>152.46270000000001</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
+        <v>50</v>
+      </c>
+      <c r="B312" t="s">
+        <v>79</v>
+      </c>
+      <c r="C312" t="s">
+        <v>29</v>
+      </c>
+      <c r="D312" s="2">
+        <v>152.52197609999999</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A313" t="s">
+        <v>50</v>
+      </c>
+      <c r="B313" t="s">
+        <v>79</v>
+      </c>
+      <c r="C313" t="s">
+        <v>13</v>
+      </c>
+      <c r="D313" s="2">
+        <v>140.721555</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
+        <v>50</v>
+      </c>
+      <c r="B314" t="s">
+        <v>79</v>
+      </c>
+      <c r="C314" t="s">
+        <v>23</v>
+      </c>
+      <c r="D314" s="2">
+        <v>116.40547100000001</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
+        <v>50</v>
+      </c>
+      <c r="B315" t="s">
+        <v>79</v>
+      </c>
+      <c r="C315" t="s">
+        <v>46</v>
+      </c>
+      <c r="D315" s="2">
+        <v>115.174015</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A316" t="s">
+        <v>50</v>
+      </c>
+      <c r="B316" t="s">
+        <v>79</v>
+      </c>
+      <c r="C316" t="s">
+        <v>12</v>
+      </c>
+      <c r="D316" s="2">
+        <v>115.07312</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A317" t="s">
+        <v>50</v>
+      </c>
+      <c r="B317" t="s">
+        <v>79</v>
+      </c>
+      <c r="C317" t="s">
+        <v>40</v>
+      </c>
+      <c r="D317" s="2">
+        <v>549.97500000000002</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A318" t="s">
+        <v>61</v>
+      </c>
+      <c r="B318" t="s">
+        <v>79</v>
+      </c>
+      <c r="C318" t="s">
+        <v>62</v>
+      </c>
+      <c r="D318" s="2">
+        <v>455.26299999999998</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A319" t="s">
+        <v>61</v>
+      </c>
+      <c r="B319" t="s">
+        <v>79</v>
+      </c>
+      <c r="C319" t="s">
+        <v>40</v>
+      </c>
+      <c r="D319" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A320" t="s">
+        <v>5</v>
+      </c>
+      <c r="B320" t="s">
+        <v>79</v>
+      </c>
+      <c r="C320" t="s">
+        <v>7</v>
+      </c>
+      <c r="E320" s="2">
+        <v>847.84166740000001</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
+        <v>5</v>
+      </c>
+      <c r="B321" t="s">
+        <v>79</v>
+      </c>
+      <c r="C321" t="s">
+        <v>9</v>
+      </c>
+      <c r="E321" s="2">
+        <v>1503.1095700000001</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A322" t="s">
+        <v>5</v>
+      </c>
+      <c r="B322" t="s">
+        <v>79</v>
+      </c>
+      <c r="C322" t="s">
+        <v>11</v>
+      </c>
+      <c r="E322" s="2">
+        <v>211.977859</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A323" t="s">
+        <v>5</v>
+      </c>
+      <c r="B323" t="s">
+        <v>79</v>
+      </c>
+      <c r="C323" t="s">
+        <v>12</v>
+      </c>
+      <c r="E323" s="2">
+        <v>94.759552999999997</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
+        <v>5</v>
+      </c>
+      <c r="B324" t="s">
+        <v>79</v>
+      </c>
+      <c r="C324" t="s">
+        <v>13</v>
+      </c>
+      <c r="E324" s="2">
+        <v>487.711995</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A325" t="s">
+        <v>5</v>
+      </c>
+      <c r="B325" t="s">
+        <v>79</v>
+      </c>
+      <c r="C325" t="s">
+        <v>14</v>
+      </c>
+      <c r="E325" s="2">
+        <v>915.09</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A326" t="s">
+        <v>5</v>
+      </c>
+      <c r="B326" t="s">
+        <v>79</v>
+      </c>
+      <c r="C326" t="s">
+        <v>40</v>
+      </c>
+      <c r="D326">
+        <v>518.94299999999998</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E250" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:E320" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="VCI"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sql/Prop book.xlsx
+++ b/sql/Prop book.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thao Dien\Broker-page - Copy\sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4567CC0A-2E50-45C3-A8BA-4541552761D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4437B17-C19C-495F-B0EC-7544AE38DBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="795" yWindow="675" windowWidth="25200" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$320</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$326</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="92">
   <si>
     <t>Broker</t>
   </si>
@@ -309,6 +309,9 @@
   </si>
   <si>
     <t>SAB</t>
+  </si>
+  <si>
+    <t>REE</t>
   </si>
 </sst>
 </file>
@@ -672,14 +675,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:E326"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E332"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="6" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -696,7 +698,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -710,7 +712,7 @@
         <v>598.5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -724,7 +726,7 @@
         <v>81.7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -738,7 +740,7 @@
         <v>1945.2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -749,7 +751,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -763,7 +765,7 @@
         <v>180.69</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -777,7 +779,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -791,7 +793,7 @@
         <v>232.999</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -805,7 +807,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -819,7 +821,7 @@
         <v>2756</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -833,7 +835,7 @@
         <v>796.99</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -844,7 +846,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -858,7 +860,7 @@
         <v>1882.8</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -872,7 +874,7 @@
         <v>11.73</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -886,7 +888,7 @@
         <v>297.25</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -900,7 +902,7 @@
         <v>139.4</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -914,7 +916,7 @@
         <v>803.12</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -928,7 +930,7 @@
         <v>837.54</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -942,7 +944,7 @@
         <v>1673.2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -956,7 +958,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -967,7 +969,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -981,7 +983,7 @@
         <v>2117.6</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -992,7 +994,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -1006,7 +1008,7 @@
         <v>12.33</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -1020,7 +1022,7 @@
         <v>167.5</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -1034,7 +1036,7 @@
         <v>695.36</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -1048,7 +1050,7 @@
         <v>772.4</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -1062,7 +1064,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -1076,7 +1078,7 @@
         <v>172.64</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -1090,7 +1092,7 @@
         <v>282.2</v>
       </c>
     </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -1104,7 +1106,7 @@
         <v>7.84</v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -1118,7 +1120,7 @@
         <v>64.372</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -1132,7 +1134,7 @@
         <v>105.5</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -1146,7 +1148,7 @@
         <v>87.8</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -1160,7 +1162,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>26</v>
       </c>
@@ -1174,7 +1176,7 @@
         <v>287.54000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>26</v>
       </c>
@@ -1188,7 +1190,7 @@
         <v>177.85</v>
       </c>
     </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>26</v>
       </c>
@@ -1202,7 +1204,7 @@
         <v>252.98500000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>26</v>
       </c>
@@ -1216,7 +1218,7 @@
         <v>91.463300000000004</v>
       </c>
     </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>26</v>
       </c>
@@ -1227,7 +1229,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>26</v>
       </c>
@@ -1242,7 +1244,7 @@
         <v>3843.058</v>
       </c>
     </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>26</v>
       </c>
@@ -1256,7 +1258,7 @@
         <v>275.23899999999998</v>
       </c>
     </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>26</v>
       </c>
@@ -1270,7 +1272,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -1284,7 +1286,7 @@
         <v>189.8</v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -1298,7 +1300,7 @@
         <v>106.4</v>
       </c>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -1312,7 +1314,7 @@
         <v>204.8</v>
       </c>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -1326,7 +1328,7 @@
         <v>79.099999999999994</v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -1340,7 +1342,7 @@
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -1354,7 +1356,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -1368,7 +1370,7 @@
         <v>170.9</v>
       </c>
     </row>
-    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -1382,7 +1384,7 @@
         <v>238.4</v>
       </c>
     </row>
-    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -1396,7 +1398,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -1410,7 +1412,7 @@
         <v>91.6</v>
       </c>
     </row>
-    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -1424,7 +1426,7 @@
         <v>71.3</v>
       </c>
     </row>
-    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -1438,7 +1440,7 @@
         <v>47.6</v>
       </c>
     </row>
-    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -1452,7 +1454,7 @@
         <v>178.9</v>
       </c>
     </row>
-    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -1466,7 +1468,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>23</v>
       </c>
@@ -1480,7 +1482,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>23</v>
       </c>
@@ -1494,7 +1496,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>23</v>
       </c>
@@ -1508,7 +1510,7 @@
         <v>734.97</v>
       </c>
     </row>
-    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>23</v>
       </c>
@@ -1522,7 +1524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>23</v>
       </c>
@@ -1536,7 +1538,7 @@
         <v>683.3</v>
       </c>
     </row>
-    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>23</v>
       </c>
@@ -1550,7 +1552,7 @@
         <v>428.9</v>
       </c>
     </row>
-    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>23</v>
       </c>
@@ -1564,7 +1566,7 @@
         <v>4362.4489999999996</v>
       </c>
     </row>
-    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>23</v>
       </c>
@@ -1578,7 +1580,7 @@
         <v>684.67200000000003</v>
       </c>
     </row>
-    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>23</v>
       </c>
@@ -1592,7 +1594,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>23</v>
       </c>
@@ -1606,7 +1608,7 @@
         <v>298.214</v>
       </c>
     </row>
-    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>26</v>
       </c>
@@ -1620,7 +1622,7 @@
         <v>462.96722006800002</v>
       </c>
     </row>
-    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>23</v>
       </c>
@@ -1634,7 +1636,7 @@
         <v>1602.507328938</v>
       </c>
     </row>
-    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>26</v>
       </c>
@@ -1648,7 +1650,7 @@
         <v>281.90273591300001</v>
       </c>
     </row>
-    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>26</v>
       </c>
@@ -1662,7 +1664,7 @@
         <v>325.68608381000001</v>
       </c>
     </row>
-    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>23</v>
       </c>
@@ -1676,7 +1678,7 @@
         <v>133.6666776649999</v>
       </c>
     </row>
-    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>23</v>
       </c>
@@ -1690,7 +1692,7 @@
         <v>465.20486131000013</v>
       </c>
     </row>
-    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -1704,7 +1706,7 @@
         <v>73.276574532000055</v>
       </c>
     </row>
-    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -1718,7 +1720,7 @@
         <v>132.5779621770001</v>
       </c>
     </row>
-    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -1732,7 +1734,7 @@
         <v>217.38459526099999</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>5</v>
       </c>
@@ -1746,7 +1748,7 @@
         <v>253.33511597899991</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -1760,7 +1762,7 @@
         <v>355.10702067800003</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>5</v>
       </c>
@@ -1774,7 +1776,7 @@
         <v>211.49055106</v>
       </c>
     </row>
-    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>26</v>
       </c>
@@ -1788,7 +1790,7 @@
         <v>313.72500000000002</v>
       </c>
     </row>
-    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>26</v>
       </c>
@@ -1802,7 +1804,7 @@
         <v>252.69882000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>26</v>
       </c>
@@ -1816,7 +1818,7 @@
         <v>131.61000000000001</v>
       </c>
     </row>
-    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>26</v>
       </c>
@@ -1830,7 +1832,7 @@
         <v>115.5</v>
       </c>
     </row>
-    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>26</v>
       </c>
@@ -1844,7 +1846,7 @@
         <v>80.653409999999994</v>
       </c>
     </row>
-    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>26</v>
       </c>
@@ -1858,7 +1860,7 @@
         <v>4593.8958050000001</v>
       </c>
     </row>
-    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>26</v>
       </c>
@@ -1869,7 +1871,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>26</v>
       </c>
@@ -1880,7 +1882,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>26</v>
       </c>
@@ -1894,7 +1896,7 @@
         <v>385.00864000000001</v>
       </c>
     </row>
-    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>26</v>
       </c>
@@ -1908,7 +1910,7 @@
         <v>204.87155000000001</v>
       </c>
     </row>
-    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>26</v>
       </c>
@@ -1922,7 +1924,7 @@
         <v>449.16890000000001</v>
       </c>
     </row>
-    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>26</v>
       </c>
@@ -1936,7 +1938,7 @@
         <v>298.416</v>
       </c>
     </row>
-    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>26</v>
       </c>
@@ -1950,7 +1952,7 @@
         <v>2868.1795425969999</v>
       </c>
     </row>
-    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>26</v>
       </c>
@@ -1961,7 +1963,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>26</v>
       </c>
@@ -1972,7 +1974,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>44</v>
       </c>
@@ -1986,7 +1988,7 @@
         <v>471.11800299999999</v>
       </c>
     </row>
-    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>44</v>
       </c>
@@ -2000,7 +2002,7 @@
         <v>444.90018559999999</v>
       </c>
     </row>
-    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>44</v>
       </c>
@@ -2014,7 +2016,7 @@
         <v>194.95070833</v>
       </c>
     </row>
-    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>44</v>
       </c>
@@ -2028,7 +2030,7 @@
         <v>459.73992199999998</v>
       </c>
     </row>
-    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>44</v>
       </c>
@@ -2042,7 +2044,7 @@
         <v>105.4291377</v>
       </c>
     </row>
-    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>44</v>
       </c>
@@ -2056,7 +2058,7 @@
         <v>112.9934461</v>
       </c>
     </row>
-    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>44</v>
       </c>
@@ -2070,7 +2072,7 @@
         <v>795.19149128900006</v>
       </c>
     </row>
-    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>44</v>
       </c>
@@ -2084,7 +2086,7 @@
         <v>418.20360959999999</v>
       </c>
     </row>
-    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>44</v>
       </c>
@@ -2098,7 +2100,7 @@
         <v>379.16809019999999</v>
       </c>
     </row>
-    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>44</v>
       </c>
@@ -2112,7 +2114,7 @@
         <v>641.44849673199997</v>
       </c>
     </row>
-    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>46</v>
       </c>
@@ -2126,7 +2128,7 @@
         <v>495.18126749999999</v>
       </c>
     </row>
-    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>46</v>
       </c>
@@ -2140,7 +2142,7 @@
         <v>41.564160000000001</v>
       </c>
     </row>
-    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>46</v>
       </c>
@@ -2154,7 +2156,7 @@
         <v>34.574301900000002</v>
       </c>
     </row>
-    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>46</v>
       </c>
@@ -2168,7 +2170,7 @@
         <v>17.764817699999998</v>
       </c>
     </row>
-    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>46</v>
       </c>
@@ -2182,7 +2184,7 @@
         <v>377.74047731399997</v>
       </c>
     </row>
-    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>46</v>
       </c>
@@ -2196,7 +2198,7 @@
         <v>47.814399999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>46</v>
       </c>
@@ -2210,7 +2212,7 @@
         <v>105.3778854</v>
       </c>
     </row>
-    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>46</v>
       </c>
@@ -2224,7 +2226,7 @@
         <v>45.304979000000003</v>
       </c>
     </row>
-    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>46</v>
       </c>
@@ -2238,7 +2240,7 @@
         <v>883.491355</v>
       </c>
     </row>
-    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>46</v>
       </c>
@@ -2252,7 +2254,7 @@
         <v>329.83531951999998</v>
       </c>
     </row>
-    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>46</v>
       </c>
@@ -2266,7 +2268,7 @@
         <v>56.4498575</v>
       </c>
     </row>
-    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>46</v>
       </c>
@@ -2280,7 +2282,7 @@
         <v>48.783651149999997</v>
       </c>
     </row>
-    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>46</v>
       </c>
@@ -2294,7 +2296,7 @@
         <v>53.905700000000003</v>
       </c>
     </row>
-    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>46</v>
       </c>
@@ -2308,7 +2310,7 @@
         <v>897.44555519999994</v>
       </c>
     </row>
-    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>46</v>
       </c>
@@ -2322,7 +2324,7 @@
         <v>567.41111581400003</v>
       </c>
     </row>
-    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>50</v>
       </c>
@@ -2336,7 +2338,7 @@
         <v>1219.89348</v>
       </c>
     </row>
-    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>50</v>
       </c>
@@ -2350,7 +2352,7 @@
         <v>891.07434000000001</v>
       </c>
     </row>
-    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>50</v>
       </c>
@@ -2364,7 +2366,7 @@
         <v>386.46965</v>
       </c>
     </row>
-    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>50</v>
       </c>
@@ -2378,7 +2380,7 @@
         <v>376.3553</v>
       </c>
     </row>
-    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>50</v>
       </c>
@@ -2392,7 +2394,7 @@
         <v>258.97612800000002</v>
       </c>
     </row>
-    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>50</v>
       </c>
@@ -2406,7 +2408,7 @@
         <v>157.063692</v>
       </c>
     </row>
-    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>50</v>
       </c>
@@ -2420,7 +2422,7 @@
         <v>80.896979999999999</v>
       </c>
     </row>
-    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>50</v>
       </c>
@@ -2434,7 +2436,7 @@
         <v>66.592600000000004</v>
       </c>
     </row>
-    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>50</v>
       </c>
@@ -2448,7 +2450,7 @@
         <v>35.567970000000003</v>
       </c>
     </row>
-    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>50</v>
       </c>
@@ -2462,7 +2464,7 @@
         <v>32.722560000000001</v>
       </c>
     </row>
-    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>50</v>
       </c>
@@ -2476,7 +2478,7 @@
         <v>76.413469636000002</v>
       </c>
     </row>
-    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>50</v>
       </c>
@@ -2490,7 +2492,7 @@
         <v>51.984900000000003</v>
       </c>
     </row>
-    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>50</v>
       </c>
@@ -2504,7 +2506,7 @@
         <v>54.700949999999999</v>
       </c>
     </row>
-    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>50</v>
       </c>
@@ -2518,7 +2520,7 @@
         <v>43.162300000000002</v>
       </c>
     </row>
-    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>50</v>
       </c>
@@ -2532,7 +2534,7 @@
         <v>37.572000000000003</v>
       </c>
     </row>
-    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>50</v>
       </c>
@@ -2546,7 +2548,7 @@
         <v>26.318750000000001</v>
       </c>
     </row>
-    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>50</v>
       </c>
@@ -2560,7 +2562,7 @@
         <v>24.028199999999998</v>
       </c>
     </row>
-    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>50</v>
       </c>
@@ -2574,7 +2576,7 @@
         <v>21.36645</v>
       </c>
     </row>
-    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>50</v>
       </c>
@@ -2588,7 +2590,7 @@
         <v>17.355250000000002</v>
       </c>
     </row>
-    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>50</v>
       </c>
@@ -2602,7 +2604,7 @@
         <v>17.120100000000001</v>
       </c>
     </row>
-    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>50</v>
       </c>
@@ -2616,7 +2618,7 @@
         <v>16.202475</v>
       </c>
     </row>
-    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>50</v>
       </c>
@@ -2630,7 +2632,7 @@
         <v>13.5169</v>
       </c>
     </row>
-    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>50</v>
       </c>
@@ -2644,7 +2646,7 @@
         <v>8.3619000000000003</v>
       </c>
     </row>
-    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>50</v>
       </c>
@@ -2658,7 +2660,7 @@
         <v>2.3957999999999999</v>
       </c>
     </row>
-    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>50</v>
       </c>
@@ -2672,7 +2674,7 @@
         <v>1791.136023734</v>
       </c>
     </row>
-    <row r="145" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>50</v>
       </c>
@@ -2686,7 +2688,7 @@
         <v>691.42874749999999</v>
       </c>
     </row>
-    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>50</v>
       </c>
@@ -2700,7 +2702,7 @@
         <v>437.546178</v>
       </c>
     </row>
-    <row r="147" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>50</v>
       </c>
@@ -2714,7 +2716,7 @@
         <v>398.44944659999999</v>
       </c>
     </row>
-    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>50</v>
       </c>
@@ -2728,7 +2730,7 @@
         <v>85.158848000000006</v>
       </c>
     </row>
-    <row r="149" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>50</v>
       </c>
@@ -2742,7 +2744,7 @@
         <v>56.339108600000003</v>
       </c>
     </row>
-    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>50</v>
       </c>
@@ -2756,7 +2758,7 @@
         <v>50.207640599999998</v>
       </c>
     </row>
-    <row r="151" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>50</v>
       </c>
@@ -2770,7 +2772,7 @@
         <v>48.181075200000002</v>
       </c>
     </row>
-    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>50</v>
       </c>
@@ -2784,7 +2786,7 @@
         <v>48.151496999999999</v>
       </c>
     </row>
-    <row r="153" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>50</v>
       </c>
@@ -2798,7 +2800,7 @@
         <v>38.785400000000003</v>
       </c>
     </row>
-    <row r="154" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>50</v>
       </c>
@@ -2812,7 +2814,7 @@
         <v>33.768990000000002</v>
       </c>
     </row>
-    <row r="155" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>50</v>
       </c>
@@ -2826,7 +2828,7 @@
         <v>27.742000000000001</v>
       </c>
     </row>
-    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>50</v>
       </c>
@@ -2840,7 +2842,7 @@
         <v>26.166374399999999</v>
       </c>
     </row>
-    <row r="157" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>50</v>
       </c>
@@ -2854,7 +2856,7 @@
         <v>312.90250348900003</v>
       </c>
     </row>
-    <row r="158" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>61</v>
       </c>
@@ -2868,7 +2870,7 @@
         <v>537.23077231399998</v>
       </c>
     </row>
-    <row r="159" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>61</v>
       </c>
@@ -2882,7 +2884,7 @@
         <v>1.2738610640000001</v>
       </c>
     </row>
-    <row r="160" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>61</v>
       </c>
@@ -2896,7 +2898,7 @@
         <v>571.68737199999998</v>
       </c>
     </row>
-    <row r="161" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>61</v>
       </c>
@@ -2910,7 +2912,7 @@
         <v>1.2426057850000001</v>
       </c>
     </row>
-    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>63</v>
       </c>
@@ -2924,7 +2926,7 @@
         <v>81.770314499999998</v>
       </c>
     </row>
-    <row r="163" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>63</v>
       </c>
@@ -2938,7 +2940,7 @@
         <v>114.13664420000001</v>
       </c>
     </row>
-    <row r="164" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>63</v>
       </c>
@@ -2952,7 +2954,7 @@
         <v>74.028000000000006</v>
       </c>
     </row>
-    <row r="165" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>63</v>
       </c>
@@ -2966,7 +2968,7 @@
         <v>334.50573044999999</v>
       </c>
     </row>
-    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>63</v>
       </c>
@@ -2980,7 +2982,7 @@
         <v>82.876750000000001</v>
       </c>
     </row>
-    <row r="167" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>63</v>
       </c>
@@ -2994,7 +2996,7 @@
         <v>96.033543249999994</v>
       </c>
     </row>
-    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>63</v>
       </c>
@@ -3008,7 +3010,7 @@
         <v>619.63735652000003</v>
       </c>
     </row>
-    <row r="169" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>63</v>
       </c>
@@ -3022,7 +3024,7 @@
         <v>66.806430000000006</v>
       </c>
     </row>
-    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>63</v>
       </c>
@@ -3036,7 +3038,7 @@
         <v>62.841739349999997</v>
       </c>
     </row>
-    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>63</v>
       </c>
@@ -3050,7 +3052,7 @@
         <v>64.178100000000001</v>
       </c>
     </row>
-    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>63</v>
       </c>
@@ -3064,7 +3066,7 @@
         <v>462.98242733000001</v>
       </c>
     </row>
-    <row r="173" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>64</v>
       </c>
@@ -3075,7 +3077,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>64</v>
       </c>
@@ -3089,7 +3091,7 @@
         <v>1.0325E-4</v>
       </c>
     </row>
-    <row r="175" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>64</v>
       </c>
@@ -3100,7 +3102,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="176" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>64</v>
       </c>
@@ -3114,7 +3116,7 @@
         <v>1.1900000000000001E-4</v>
       </c>
     </row>
-    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>64</v>
       </c>
@@ -3125,7 +3127,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>67</v>
       </c>
@@ -3139,7 +3141,7 @@
         <v>64.729280000000003</v>
       </c>
     </row>
-    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>67</v>
       </c>
@@ -3153,7 +3155,7 @@
         <v>4.1003119999999997</v>
       </c>
     </row>
-    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>67</v>
       </c>
@@ -3167,7 +3169,7 @@
         <v>7.8800173759999996</v>
       </c>
     </row>
-    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>67</v>
       </c>
@@ -3181,7 +3183,7 @@
         <v>57.4816</v>
       </c>
     </row>
-    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>67</v>
       </c>
@@ -3195,7 +3197,7 @@
         <v>3.4080650000000001E-3</v>
       </c>
     </row>
-    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>67</v>
       </c>
@@ -3209,7 +3211,7 @@
         <v>9.5435766019999999</v>
       </c>
     </row>
-    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>67</v>
       </c>
@@ -3223,7 +3225,7 @@
         <v>3.4080650000000001E-3</v>
       </c>
     </row>
-    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>63</v>
       </c>
@@ -3237,7 +3239,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>63</v>
       </c>
@@ -3251,7 +3253,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>63</v>
       </c>
@@ -3265,7 +3267,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>61</v>
       </c>
@@ -3279,7 +3281,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>61</v>
       </c>
@@ -3293,7 +3295,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>61</v>
       </c>
@@ -3307,7 +3309,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>50</v>
       </c>
@@ -3321,7 +3323,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>50</v>
       </c>
@@ -3335,7 +3337,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="193" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>50</v>
       </c>
@@ -3349,7 +3351,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="194" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>64</v>
       </c>
@@ -3363,7 +3365,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="195" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>64</v>
       </c>
@@ -3377,7 +3379,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="196" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>64</v>
       </c>
@@ -3391,7 +3393,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="197" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>67</v>
       </c>
@@ -3405,7 +3407,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="198" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>67</v>
       </c>
@@ -3419,7 +3421,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="199" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>67</v>
       </c>
@@ -3433,7 +3435,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>26</v>
       </c>
@@ -3447,7 +3449,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="201" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>26</v>
       </c>
@@ -3461,7 +3463,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="202" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>26</v>
       </c>
@@ -3475,7 +3477,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="203" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>46</v>
       </c>
@@ -3489,7 +3491,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="204" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>46</v>
       </c>
@@ -3503,7 +3505,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="205" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>46</v>
       </c>
@@ -3517,7 +3519,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="206" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>44</v>
       </c>
@@ -3531,7 +3533,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="207" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>44</v>
       </c>
@@ -3545,7 +3547,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="208" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>44</v>
       </c>
@@ -3559,7 +3561,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>70</v>
       </c>
@@ -3573,7 +3575,7 @@
         <v>291.53755000000001</v>
       </c>
     </row>
-    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>70</v>
       </c>
@@ -3587,7 +3589,7 @@
         <v>97.599699999999999</v>
       </c>
     </row>
-    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>70</v>
       </c>
@@ -3601,7 +3603,7 @@
         <v>139.96039999999999</v>
       </c>
     </row>
-    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>70</v>
       </c>
@@ -3615,7 +3617,7 @@
         <v>126.0891627</v>
       </c>
     </row>
-    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>70</v>
       </c>
@@ -3629,7 +3631,7 @@
         <v>484.16045324999999</v>
       </c>
     </row>
-    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>70</v>
       </c>
@@ -3643,7 +3645,7 @@
         <v>97.860349999999997</v>
       </c>
     </row>
-    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>70</v>
       </c>
@@ -3657,7 +3659,7 @@
         <v>118.3644</v>
       </c>
     </row>
-    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>70</v>
       </c>
@@ -3671,7 +3673,7 @@
         <v>40.125</v>
       </c>
     </row>
-    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>70</v>
       </c>
@@ -3685,7 +3687,7 @@
         <v>-17.442687286000002</v>
       </c>
     </row>
-    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>70</v>
       </c>
@@ -3699,7 +3701,7 @@
         <v>319.48334</v>
       </c>
     </row>
-    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>70</v>
       </c>
@@ -3713,7 +3715,7 @@
         <v>1110.0100874</v>
       </c>
     </row>
-    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>70</v>
       </c>
@@ -3727,7 +3729,7 @@
         <v>131.24760000000001</v>
       </c>
     </row>
-    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>70</v>
       </c>
@@ -3741,7 +3743,7 @@
         <v>77.801199999999994</v>
       </c>
     </row>
-    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>70</v>
       </c>
@@ -3755,7 +3757,7 @@
         <v>49.610999999999997</v>
       </c>
     </row>
-    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>70</v>
       </c>
@@ -3769,7 +3771,7 @@
         <v>36.58</v>
       </c>
     </row>
-    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>70</v>
       </c>
@@ -3783,7 +3785,7 @@
         <v>22.643851017999999</v>
       </c>
     </row>
-    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>70</v>
       </c>
@@ -3797,7 +3799,7 @@
         <v>147.13238000000001</v>
       </c>
     </row>
-    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>70</v>
       </c>
@@ -3811,7 +3813,7 @@
         <v>102.867975</v>
       </c>
     </row>
-    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>70</v>
       </c>
@@ -3825,7 +3827,7 @@
         <v>125.2624716</v>
       </c>
     </row>
-    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>70</v>
       </c>
@@ -3839,7 +3841,7 @@
         <v>129.71071259999999</v>
       </c>
     </row>
-    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>70</v>
       </c>
@@ -3853,7 +3855,7 @@
         <v>127.5998</v>
       </c>
     </row>
-    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>70</v>
       </c>
@@ -3867,7 +3869,7 @@
         <v>466.77496559999997</v>
       </c>
     </row>
-    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>70</v>
       </c>
@@ -3881,7 +3883,7 @@
         <v>270.72160000000002</v>
       </c>
     </row>
-    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>70</v>
       </c>
@@ -3895,7 +3897,7 @@
         <v>145.33860000000001</v>
       </c>
     </row>
-    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>70</v>
       </c>
@@ -3909,7 +3911,7 @@
         <v>50.883000000000003</v>
       </c>
     </row>
-    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>70</v>
       </c>
@@ -3923,7 +3925,7 @@
         <v>62.96705</v>
       </c>
     </row>
-    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>70</v>
       </c>
@@ -3937,7 +3939,7 @@
         <v>-33.634174170000001</v>
       </c>
     </row>
-    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>74</v>
       </c>
@@ -3951,7 +3953,7 @@
         <v>91.021986687999998</v>
       </c>
     </row>
-    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>74</v>
       </c>
@@ -3965,7 +3967,7 @@
         <v>66.466997524000007</v>
       </c>
     </row>
-    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>74</v>
       </c>
@@ -3979,7 +3981,7 @@
         <v>41.544733348999998</v>
       </c>
     </row>
-    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>23</v>
       </c>
@@ -3993,7 +3995,7 @@
         <v>1935.6160052</v>
       </c>
     </row>
-    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>23</v>
       </c>
@@ -4007,7 +4009,7 @@
         <v>1093.40625</v>
       </c>
     </row>
-    <row r="241" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>23</v>
       </c>
@@ -4021,7 +4023,7 @@
         <v>936.03599999999994</v>
       </c>
     </row>
-    <row r="242" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>23</v>
       </c>
@@ -4035,7 +4037,7 @@
         <v>870.293138</v>
       </c>
     </row>
-    <row r="243" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>23</v>
       </c>
@@ -4049,7 +4051,7 @@
         <v>703.93795499999999</v>
       </c>
     </row>
-    <row r="244" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>23</v>
       </c>
@@ -4063,7 +4065,7 @@
         <v>453.33</v>
       </c>
     </row>
-    <row r="245" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>23</v>
       </c>
@@ -4077,7 +4079,7 @@
         <v>490.97399999999999</v>
       </c>
     </row>
-    <row r="246" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>23</v>
       </c>
@@ -4091,7 +4093,7 @@
         <v>465.35771999999997</v>
       </c>
     </row>
-    <row r="247" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>23</v>
       </c>
@@ -4105,7 +4107,7 @@
         <v>2569.0349262</v>
       </c>
     </row>
-    <row r="248" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>23</v>
       </c>
@@ -4119,7 +4121,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="249" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>23</v>
       </c>
@@ -4133,7 +4135,7 @@
         <v>959.69100000000003</v>
       </c>
     </row>
-    <row r="250" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>23</v>
       </c>
@@ -4147,7 +4149,7 @@
         <v>284.44299999999998</v>
       </c>
     </row>
-    <row r="251" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>23</v>
       </c>
@@ -4161,7 +4163,7 @@
         <v>1763.249</v>
       </c>
     </row>
-    <row r="252" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>23</v>
       </c>
@@ -4175,7 +4177,7 @@
         <v>1752.2063000000001</v>
       </c>
     </row>
-    <row r="253" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>23</v>
       </c>
@@ -4189,7 +4191,7 @@
         <v>2495.8277849999999</v>
       </c>
     </row>
-    <row r="254" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>23</v>
       </c>
@@ -4203,7 +4205,7 @@
         <v>2574.3249999999998</v>
       </c>
     </row>
-    <row r="255" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>23</v>
       </c>
@@ -4217,7 +4219,7 @@
         <v>1101.24</v>
       </c>
     </row>
-    <row r="256" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>23</v>
       </c>
@@ -4231,7 +4233,7 @@
         <v>191.304</v>
       </c>
     </row>
-    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>26</v>
       </c>
@@ -4245,7 +4247,7 @@
         <v>388.8</v>
       </c>
     </row>
-    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>26</v>
       </c>
@@ -4259,7 +4261,7 @@
         <v>106.95099999999999</v>
       </c>
     </row>
-    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>26</v>
       </c>
@@ -4273,7 +4275,7 @@
         <v>374.26499999999999</v>
       </c>
     </row>
-    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>26</v>
       </c>
@@ -4287,7 +4289,7 @@
         <v>122.08</v>
       </c>
     </row>
-    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>26</v>
       </c>
@@ -4301,7 +4303,7 @@
         <v>116.294</v>
       </c>
     </row>
-    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>26</v>
       </c>
@@ -4315,7 +4317,7 @@
         <v>3805.7429999999999</v>
       </c>
     </row>
-    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>26</v>
       </c>
@@ -4329,7 +4331,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>26</v>
       </c>
@@ -4343,7 +4345,7 @@
         <v>275.238</v>
       </c>
     </row>
-    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>70</v>
       </c>
@@ -4357,7 +4359,7 @@
         <v>321.96100000000001</v>
       </c>
     </row>
-    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>70</v>
       </c>
@@ -4371,7 +4373,7 @@
         <v>229.74100000000001</v>
       </c>
     </row>
-    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>70</v>
       </c>
@@ -4385,7 +4387,7 @@
         <v>157.09299999999999</v>
       </c>
     </row>
-    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>70</v>
       </c>
@@ -4399,7 +4401,7 @@
         <v>169.16200000000001</v>
       </c>
     </row>
-    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>70</v>
       </c>
@@ -4413,7 +4415,7 @@
         <v>364.79500000000002</v>
       </c>
     </row>
-    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>70</v>
       </c>
@@ -4427,7 +4429,7 @@
         <v>28.222999999999999</v>
       </c>
     </row>
-    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>70</v>
       </c>
@@ -4441,7 +4443,7 @@
         <v>111.91</v>
       </c>
     </row>
-    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>70</v>
       </c>
@@ -4455,7 +4457,7 @@
         <v>92.884</v>
       </c>
     </row>
-    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>70</v>
       </c>
@@ -4469,7 +4471,7 @@
         <v>47.414999999999999</v>
       </c>
     </row>
-    <row r="274" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>70</v>
       </c>
@@ -4483,7 +4485,7 @@
         <v>156.172</v>
       </c>
     </row>
-    <row r="275" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>18</v>
       </c>
@@ -4494,7 +4496,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="276" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>18</v>
       </c>
@@ -4508,7 +4510,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>18</v>
       </c>
@@ -4522,7 +4524,7 @@
         <v>8.3079999999999998</v>
       </c>
     </row>
-    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>18</v>
       </c>
@@ -4536,7 +4538,7 @@
         <v>111.676</v>
       </c>
     </row>
-    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>18</v>
       </c>
@@ -4550,7 +4552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>18</v>
       </c>
@@ -4564,7 +4566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>18</v>
       </c>
@@ -4578,7 +4580,7 @@
         <v>66.446399999999997</v>
       </c>
     </row>
-    <row r="282" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>18</v>
       </c>
@@ -4592,7 +4594,7 @@
         <v>60.198599999999999</v>
       </c>
     </row>
-    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>18</v>
       </c>
@@ -4606,7 +4608,7 @@
         <v>16.675999999999998</v>
       </c>
     </row>
-    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>18</v>
       </c>
@@ -4620,7 +4622,7 @@
         <v>16.715</v>
       </c>
     </row>
-    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>18</v>
       </c>
@@ -4634,7 +4636,7 @@
         <v>38.396999999999998</v>
       </c>
     </row>
-    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>18</v>
       </c>
@@ -4648,7 +4650,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>18</v>
       </c>
@@ -4662,7 +4664,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>70</v>
       </c>
@@ -4676,7 +4678,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="289" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>23</v>
       </c>
@@ -4690,7 +4692,7 @@
         <v>3048</v>
       </c>
     </row>
-    <row r="290" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>26</v>
       </c>
@@ -4704,7 +4706,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="291" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>63</v>
       </c>
@@ -4718,7 +4720,7 @@
         <v>74.397000000000006</v>
       </c>
     </row>
-    <row r="292" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>63</v>
       </c>
@@ -4732,7 +4734,7 @@
         <v>163.31</v>
       </c>
     </row>
-    <row r="293" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>63</v>
       </c>
@@ -4746,7 +4748,7 @@
         <v>534.41600000000005</v>
       </c>
     </row>
-    <row r="294" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>63</v>
       </c>
@@ -4760,7 +4762,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="295" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>50</v>
       </c>
@@ -4774,7 +4776,7 @@
         <v>560.84807000000001</v>
       </c>
     </row>
-    <row r="296" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>50</v>
       </c>
@@ -4788,7 +4790,7 @@
         <v>480.37799999999999</v>
       </c>
     </row>
-    <row r="297" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>50</v>
       </c>
@@ -4802,7 +4804,7 @@
         <v>457.70800000000003</v>
       </c>
     </row>
-    <row r="298" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>50</v>
       </c>
@@ -4816,7 +4818,7 @@
         <v>440.096</v>
       </c>
     </row>
-    <row r="299" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>50</v>
       </c>
@@ -4830,7 +4832,7 @@
         <v>388.70979</v>
       </c>
     </row>
-    <row r="300" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>50</v>
       </c>
@@ -4844,7 +4846,7 @@
         <v>386.8227</v>
       </c>
     </row>
-    <row r="301" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>50</v>
       </c>
@@ -4858,7 +4860,7 @@
         <v>324.61559999999997</v>
       </c>
     </row>
-    <row r="302" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>50</v>
       </c>
@@ -4872,7 +4874,7 @@
         <v>283.223343</v>
       </c>
     </row>
-    <row r="303" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>50</v>
       </c>
@@ -4886,7 +4888,7 @@
         <v>257.17744499999998</v>
       </c>
     </row>
-    <row r="304" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>50</v>
       </c>
@@ -4900,7 +4902,7 @@
         <v>267.80786999999998</v>
       </c>
     </row>
-    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>50</v>
       </c>
@@ -4914,7 +4916,7 @@
         <v>236.04599999999999</v>
       </c>
     </row>
-    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>50</v>
       </c>
@@ -4928,7 +4930,7 @@
         <v>207.93639999999999</v>
       </c>
     </row>
-    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>50</v>
       </c>
@@ -4942,7 +4944,7 @@
         <v>184.02464000000001</v>
       </c>
     </row>
-    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>50</v>
       </c>
@@ -4956,7 +4958,7 @@
         <v>186.27279999999999</v>
       </c>
     </row>
-    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>50</v>
       </c>
@@ -4970,7 +4972,7 @@
         <v>181.30464520000001</v>
       </c>
     </row>
-    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>50</v>
       </c>
@@ -4984,7 +4986,7 @@
         <v>180.90083999999999</v>
       </c>
     </row>
-    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>50</v>
       </c>
@@ -4998,7 +5000,7 @@
         <v>152.46270000000001</v>
       </c>
     </row>
-    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>50</v>
       </c>
@@ -5012,7 +5014,7 @@
         <v>152.52197609999999</v>
       </c>
     </row>
-    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>50</v>
       </c>
@@ -5026,7 +5028,7 @@
         <v>140.721555</v>
       </c>
     </row>
-    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>50</v>
       </c>
@@ -5040,7 +5042,7 @@
         <v>116.40547100000001</v>
       </c>
     </row>
-    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>50</v>
       </c>
@@ -5054,7 +5056,7 @@
         <v>115.174015</v>
       </c>
     </row>
-    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>50</v>
       </c>
@@ -5068,7 +5070,7 @@
         <v>115.07312</v>
       </c>
     </row>
-    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>50</v>
       </c>
@@ -5082,7 +5084,7 @@
         <v>549.97500000000002</v>
       </c>
     </row>
-    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>61</v>
       </c>
@@ -5096,7 +5098,7 @@
         <v>455.26299999999998</v>
       </c>
     </row>
-    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>61</v>
       </c>
@@ -5110,7 +5112,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>5</v>
       </c>
@@ -5124,7 +5126,7 @@
         <v>847.84166740000001</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>5</v>
       </c>
@@ -5138,7 +5140,7 @@
         <v>1503.1095700000001</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>5</v>
       </c>
@@ -5152,7 +5154,7 @@
         <v>211.977859</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>5</v>
       </c>
@@ -5166,7 +5168,7 @@
         <v>94.759552999999997</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>5</v>
       </c>
@@ -5180,7 +5182,7 @@
         <v>487.711995</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>5</v>
       </c>
@@ -5194,7 +5196,7 @@
         <v>915.09</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>5</v>
       </c>
@@ -5208,14 +5210,92 @@
         <v>518.94299999999998</v>
       </c>
     </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>44</v>
+      </c>
+      <c r="B327" t="s">
+        <v>79</v>
+      </c>
+      <c r="C327" t="s">
+        <v>45</v>
+      </c>
+      <c r="D327">
+        <v>575.76700000000005</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>44</v>
+      </c>
+      <c r="B328" t="s">
+        <v>79</v>
+      </c>
+      <c r="C328" t="s">
+        <v>10</v>
+      </c>
+      <c r="D328">
+        <v>145.67400000000001</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>44</v>
+      </c>
+      <c r="B329" t="s">
+        <v>79</v>
+      </c>
+      <c r="C329" t="s">
+        <v>49</v>
+      </c>
+      <c r="D329">
+        <v>118.684</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>44</v>
+      </c>
+      <c r="B330" t="s">
+        <v>79</v>
+      </c>
+      <c r="C330" t="s">
+        <v>91</v>
+      </c>
+      <c r="D330">
+        <v>104.973</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>44</v>
+      </c>
+      <c r="B331" t="s">
+        <v>79</v>
+      </c>
+      <c r="C331" t="s">
+        <v>25</v>
+      </c>
+      <c r="D331">
+        <v>476.053</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>44</v>
+      </c>
+      <c r="B332" t="s">
+        <v>79</v>
+      </c>
+      <c r="C332" t="s">
+        <v>40</v>
+      </c>
+      <c r="D332">
+        <v>1165.2354190000001</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E320" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="VCI"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:E326" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sql/Prop book.xlsx
+++ b/sql/Prop book.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thao Dien\Broker-page - Copy\sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4437B17-C19C-495F-B0EC-7544AE38DBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1083B0DD-A37A-4A35-9DD9-8F26B55A9FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="795" yWindow="675" windowWidth="25200" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="22635" windowHeight="13515" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$326</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$336</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="93">
   <si>
     <t>Broker</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>REE</t>
+  </si>
+  <si>
+    <t>VRE</t>
   </si>
 </sst>
 </file>
@@ -675,7 +678,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E332"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:E336"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -698,7 +702,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -712,7 +716,7 @@
         <v>598.5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -726,7 +730,7 @@
         <v>81.7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -740,7 +744,7 @@
         <v>1945.2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -751,7 +755,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -765,7 +769,7 @@
         <v>180.69</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -779,7 +783,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -793,7 +797,7 @@
         <v>232.999</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -807,7 +811,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -821,7 +825,7 @@
         <v>2756</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -835,7 +839,7 @@
         <v>796.99</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -846,7 +850,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -860,7 +864,7 @@
         <v>1882.8</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -874,7 +878,7 @@
         <v>11.73</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -888,7 +892,7 @@
         <v>297.25</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -902,7 +906,7 @@
         <v>139.4</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -916,7 +920,7 @@
         <v>803.12</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -930,7 +934,7 @@
         <v>837.54</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -944,7 +948,7 @@
         <v>1673.2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -958,7 +962,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -969,7 +973,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -983,7 +987,7 @@
         <v>2117.6</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -994,7 +998,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -1008,7 +1012,7 @@
         <v>12.33</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -1022,7 +1026,7 @@
         <v>167.5</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -1036,7 +1040,7 @@
         <v>695.36</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -1050,7 +1054,7 @@
         <v>772.4</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -1064,7 +1068,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -1078,7 +1082,7 @@
         <v>172.64</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -1092,7 +1096,7 @@
         <v>282.2</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -1106,7 +1110,7 @@
         <v>7.84</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -1120,7 +1124,7 @@
         <v>64.372</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -1134,7 +1138,7 @@
         <v>105.5</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -1148,7 +1152,7 @@
         <v>87.8</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -1272,7 +1276,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -1286,7 +1290,7 @@
         <v>189.8</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -1300,7 +1304,7 @@
         <v>106.4</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -1314,7 +1318,7 @@
         <v>204.8</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -1328,7 +1332,7 @@
         <v>79.099999999999994</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -1342,7 +1346,7 @@
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -1356,7 +1360,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -1370,7 +1374,7 @@
         <v>170.9</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -1384,7 +1388,7 @@
         <v>238.4</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -1398,7 +1402,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -1412,7 +1416,7 @@
         <v>91.6</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -1426,7 +1430,7 @@
         <v>71.3</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -1440,7 +1444,7 @@
         <v>47.6</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -1454,7 +1458,7 @@
         <v>178.9</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -1468,7 +1472,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>23</v>
       </c>
@@ -1482,7 +1486,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>23</v>
       </c>
@@ -1496,7 +1500,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>23</v>
       </c>
@@ -1510,7 +1514,7 @@
         <v>734.97</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>23</v>
       </c>
@@ -1524,7 +1528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>23</v>
       </c>
@@ -1538,7 +1542,7 @@
         <v>683.3</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>23</v>
       </c>
@@ -1552,7 +1556,7 @@
         <v>428.9</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>23</v>
       </c>
@@ -1566,7 +1570,7 @@
         <v>4362.4489999999996</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>23</v>
       </c>
@@ -1580,7 +1584,7 @@
         <v>684.67200000000003</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>23</v>
       </c>
@@ -1594,7 +1598,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>23</v>
       </c>
@@ -1608,9 +1612,9 @@
         <v>298.214</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B68" t="s">
         <v>6</v>
@@ -1619,82 +1623,82 @@
         <v>40</v>
       </c>
       <c r="D68">
-        <v>462.96722006800002</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1602.507328938</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>23</v>
       </c>
       <c r="B69" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C69" t="s">
         <v>40</v>
       </c>
       <c r="D69">
-        <v>1602.507328938</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+        <v>133.6666776649999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B70" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C70" t="s">
         <v>40</v>
       </c>
       <c r="D70">
-        <v>281.90273591300001</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+        <v>465.20486131000013</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B71" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C71" t="s">
         <v>40</v>
       </c>
       <c r="D71">
-        <v>325.68608381000001</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+        <v>73.276574532000055</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B72" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C72" t="s">
         <v>40</v>
       </c>
       <c r="D72">
-        <v>133.6666776649999</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+        <v>132.5779621770001</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B73" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C73" t="s">
         <v>40</v>
       </c>
       <c r="D73">
-        <v>465.20486131000013</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+        <v>217.38459526099999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B74" t="s">
         <v>17</v>
@@ -1703,12 +1707,12 @@
         <v>40</v>
       </c>
       <c r="D74">
-        <v>73.276574532000055</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+        <v>253.33511597899991</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B75" t="s">
         <v>16</v>
@@ -1717,12 +1721,12 @@
         <v>40</v>
       </c>
       <c r="D75">
-        <v>132.5779621770001</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+        <v>355.10702067800003</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B76" t="s">
         <v>6</v>
@@ -1731,49 +1735,49 @@
         <v>40</v>
       </c>
       <c r="D76">
-        <v>217.38459526099999</v>
+        <v>211.49055106</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B77" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C77" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D77">
-        <v>253.33511597899991</v>
+        <v>313.72500000000002</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B78" t="s">
         <v>16</v>
       </c>
       <c r="C78" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="D78">
-        <v>355.10702067800003</v>
+        <v>252.69882000000001</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B79" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C79" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D79">
-        <v>211.49055106</v>
+        <v>131.61000000000001</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -1784,10 +1788,10 @@
         <v>16</v>
       </c>
       <c r="C80" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D80">
-        <v>313.72500000000002</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -1798,10 +1802,10 @@
         <v>16</v>
       </c>
       <c r="C81" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="D81">
-        <v>252.69882000000001</v>
+        <v>80.653409999999994</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -1812,10 +1816,10 @@
         <v>16</v>
       </c>
       <c r="C82" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D82">
-        <v>131.61000000000001</v>
+        <v>4593.8958050000001</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -1826,10 +1830,7 @@
         <v>16</v>
       </c>
       <c r="C83" t="s">
-        <v>27</v>
-      </c>
-      <c r="D83">
-        <v>115.5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -1840,10 +1841,7 @@
         <v>16</v>
       </c>
       <c r="C84" t="s">
-        <v>41</v>
-      </c>
-      <c r="D84">
-        <v>80.653409999999994</v>
+        <v>30</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -1851,13 +1849,13 @@
         <v>26</v>
       </c>
       <c r="B85" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C85" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D85">
-        <v>4593.8958050000001</v>
+        <v>385.00864000000001</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -1865,10 +1863,13 @@
         <v>26</v>
       </c>
       <c r="B86" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C86" t="s">
-        <v>29</v>
+        <v>13</v>
+      </c>
+      <c r="D86">
+        <v>204.87155000000001</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -1876,10 +1877,13 @@
         <v>26</v>
       </c>
       <c r="B87" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C87" t="s">
-        <v>30</v>
+        <v>43</v>
+      </c>
+      <c r="D87">
+        <v>449.16890000000001</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -1890,10 +1894,10 @@
         <v>17</v>
       </c>
       <c r="C88" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D88">
-        <v>385.00864000000001</v>
+        <v>298.416</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -1904,10 +1908,10 @@
         <v>17</v>
       </c>
       <c r="C89" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D89">
-        <v>204.87155000000001</v>
+        <v>2868.1795425969999</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -1918,10 +1922,7 @@
         <v>17</v>
       </c>
       <c r="C90" t="s">
-        <v>43</v>
-      </c>
-      <c r="D90">
-        <v>449.16890000000001</v>
+        <v>29</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -1932,91 +1933,94 @@
         <v>17</v>
       </c>
       <c r="C91" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>44</v>
+      </c>
+      <c r="B92" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" t="s">
         <v>22</v>
       </c>
-      <c r="D91">
-        <v>298.416</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>26</v>
-      </c>
-      <c r="B92" t="s">
-        <v>17</v>
-      </c>
-      <c r="C92" t="s">
+      <c r="D92">
+        <v>471.11800299999999</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>44</v>
+      </c>
+      <c r="B93" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" t="s">
+        <v>45</v>
+      </c>
+      <c r="D93">
+        <v>444.90018559999999</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>44</v>
+      </c>
+      <c r="B94" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" t="s">
         <v>25</v>
       </c>
-      <c r="D92">
-        <v>2868.1795425969999</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>26</v>
-      </c>
-      <c r="B93" t="s">
-        <v>17</v>
-      </c>
-      <c r="C93" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>26</v>
-      </c>
-      <c r="B94" t="s">
-        <v>17</v>
-      </c>
-      <c r="C94" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D94">
+        <v>194.95070833</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>44</v>
       </c>
       <c r="B95" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C95" t="s">
         <v>22</v>
       </c>
       <c r="D95">
-        <v>471.11800299999999</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+        <v>459.73992199999998</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>44</v>
       </c>
       <c r="B96" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C96" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D96">
-        <v>444.90018559999999</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+        <v>105.4291377</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>44</v>
       </c>
       <c r="B97" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C97" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D97">
-        <v>194.95070833</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+        <v>112.9934461</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>44</v>
       </c>
@@ -2024,97 +2028,97 @@
         <v>16</v>
       </c>
       <c r="C98" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D98">
-        <v>459.73992199999998</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+        <v>795.19149128900006</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>44</v>
       </c>
       <c r="B99" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C99" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D99">
-        <v>105.4291377</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+        <v>418.20360959999999</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>44</v>
       </c>
       <c r="B100" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C100" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D100">
-        <v>112.9934461</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+        <v>379.16809019999999</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>44</v>
       </c>
       <c r="B101" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C101" t="s">
         <v>25</v>
       </c>
       <c r="D101">
-        <v>795.19149128900006</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+        <v>641.44849673199997</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B102" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C102" t="s">
         <v>22</v>
       </c>
       <c r="D102">
-        <v>418.20360959999999</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+        <v>495.18126749999999</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B103" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C103" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="D103">
-        <v>379.16809019999999</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41.564160000000001</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B104" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C104" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D104">
-        <v>641.44849673199997</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+        <v>34.574301900000002</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>46</v>
       </c>
@@ -2122,13 +2126,13 @@
         <v>6</v>
       </c>
       <c r="C105" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="D105">
-        <v>495.18126749999999</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17.764817699999998</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>46</v>
       </c>
@@ -2136,55 +2140,55 @@
         <v>6</v>
       </c>
       <c r="C106" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D106">
-        <v>41.564160000000001</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+        <v>377.74047731399997</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>46</v>
       </c>
       <c r="B107" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C107" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D107">
-        <v>34.574301900000002</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47.814399999999999</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>46</v>
       </c>
       <c r="B108" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C108" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D108">
-        <v>17.764817699999998</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+        <v>105.3778854</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>46</v>
       </c>
       <c r="B109" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C109" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="D109">
-        <v>377.74047731399997</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45.304979000000003</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>46</v>
       </c>
@@ -2192,13 +2196,13 @@
         <v>16</v>
       </c>
       <c r="C110" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D110">
-        <v>47.814399999999999</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+        <v>883.491355</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>46</v>
       </c>
@@ -2206,55 +2210,55 @@
         <v>16</v>
       </c>
       <c r="C111" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="D111">
-        <v>105.3778854</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+        <v>329.83531951999998</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>46</v>
       </c>
       <c r="B112" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C112" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="D112">
-        <v>45.304979000000003</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+        <v>56.4498575</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>46</v>
       </c>
       <c r="B113" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C113" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D113">
-        <v>883.491355</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48.783651149999997</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>46</v>
       </c>
       <c r="B114" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C114" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="D114">
-        <v>329.83531951999998</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+        <v>53.905700000000003</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>46</v>
       </c>
@@ -2262,13 +2266,13 @@
         <v>17</v>
       </c>
       <c r="C115" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D115">
-        <v>56.4498575</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+        <v>897.44555519999994</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>46</v>
       </c>
@@ -2276,643 +2280,643 @@
         <v>17</v>
       </c>
       <c r="C116" t="s">
+        <v>25</v>
+      </c>
+      <c r="D116">
+        <v>567.41111581400003</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>50</v>
+      </c>
+      <c r="B117" t="s">
+        <v>6</v>
+      </c>
+      <c r="C117" t="s">
+        <v>27</v>
+      </c>
+      <c r="D117">
+        <v>1219.89348</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>50</v>
+      </c>
+      <c r="B118" t="s">
+        <v>6</v>
+      </c>
+      <c r="C118" t="s">
+        <v>13</v>
+      </c>
+      <c r="D118">
+        <v>891.07434000000001</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>50</v>
+      </c>
+      <c r="B119" t="s">
+        <v>6</v>
+      </c>
+      <c r="C119" t="s">
+        <v>49</v>
+      </c>
+      <c r="D119">
+        <v>386.46965</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>50</v>
+      </c>
+      <c r="B120" t="s">
+        <v>6</v>
+      </c>
+      <c r="C120" t="s">
+        <v>12</v>
+      </c>
+      <c r="D120">
+        <v>376.3553</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>50</v>
+      </c>
+      <c r="B121" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" t="s">
         <v>28</v>
       </c>
-      <c r="D116">
-        <v>48.783651149999997</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
+      <c r="D121">
+        <v>258.97612800000002</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>50</v>
+      </c>
+      <c r="B122" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" t="s">
+        <v>11</v>
+      </c>
+      <c r="D122">
+        <v>157.063692</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>50</v>
+      </c>
+      <c r="B123" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" t="s">
+        <v>51</v>
+      </c>
+      <c r="D123">
+        <v>80.896979999999999</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>50</v>
+      </c>
+      <c r="B124" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" t="s">
+        <v>22</v>
+      </c>
+      <c r="D124">
+        <v>66.592600000000004</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>50</v>
+      </c>
+      <c r="B125" t="s">
+        <v>6</v>
+      </c>
+      <c r="C125" t="s">
+        <v>52</v>
+      </c>
+      <c r="D125">
+        <v>35.567970000000003</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>50</v>
+      </c>
+      <c r="B126" t="s">
+        <v>6</v>
+      </c>
+      <c r="C126" t="s">
         <v>46</v>
       </c>
-      <c r="B117" t="s">
-        <v>17</v>
-      </c>
-      <c r="C117" t="s">
+      <c r="D126">
+        <v>32.722560000000001</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>50</v>
+      </c>
+      <c r="B127" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" t="s">
+        <v>25</v>
+      </c>
+      <c r="D127">
+        <v>76.413469636000002</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>50</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="s">
+        <v>53</v>
+      </c>
+      <c r="D128">
+        <v>51.984900000000003</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>50</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="s">
+        <v>21</v>
+      </c>
+      <c r="D129">
+        <v>54.700949999999999</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>50</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="s">
+        <v>22</v>
+      </c>
+      <c r="D130">
+        <v>43.162300000000002</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>50</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="s">
+        <v>48</v>
+      </c>
+      <c r="D131">
+        <v>37.572000000000003</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>50</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="s">
+        <v>54</v>
+      </c>
+      <c r="D132">
+        <v>26.318750000000001</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>50</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="s">
+        <v>55</v>
+      </c>
+      <c r="D133">
+        <v>24.028199999999998</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>50</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="s">
+        <v>56</v>
+      </c>
+      <c r="D134">
+        <v>21.36645</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>50</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="s">
+        <v>27</v>
+      </c>
+      <c r="D135">
+        <v>17.355250000000002</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>50</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="s">
+        <v>12</v>
+      </c>
+      <c r="D136">
+        <v>17.120100000000001</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>50</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="s">
+        <v>28</v>
+      </c>
+      <c r="D137">
+        <v>16.202475</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>50</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="s">
         <v>49</v>
       </c>
-      <c r="D117">
-        <v>53.905700000000003</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>46</v>
-      </c>
-      <c r="B118" t="s">
-        <v>17</v>
-      </c>
-      <c r="C118" t="s">
+      <c r="D138">
+        <v>13.5169</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>50</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="s">
+        <v>57</v>
+      </c>
+      <c r="D139">
+        <v>8.3619000000000003</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>50</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="s">
+        <v>13</v>
+      </c>
+      <c r="D140">
+        <v>2.3957999999999999</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>50</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="s">
+        <v>25</v>
+      </c>
+      <c r="D141">
+        <v>1791.136023734</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>50</v>
+      </c>
+      <c r="B142" t="s">
+        <v>17</v>
+      </c>
+      <c r="C142" t="s">
+        <v>13</v>
+      </c>
+      <c r="D142">
+        <v>691.42874749999999</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>50</v>
+      </c>
+      <c r="B143" t="s">
+        <v>17</v>
+      </c>
+      <c r="C143" t="s">
+        <v>12</v>
+      </c>
+      <c r="D143">
+        <v>437.546178</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>50</v>
+      </c>
+      <c r="B144" t="s">
+        <v>17</v>
+      </c>
+      <c r="C144" t="s">
+        <v>47</v>
+      </c>
+      <c r="D144">
+        <v>398.44944659999999</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>50</v>
+      </c>
+      <c r="B145" t="s">
+        <v>17</v>
+      </c>
+      <c r="C145" t="s">
+        <v>27</v>
+      </c>
+      <c r="D145">
+        <v>85.158848000000006</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>50</v>
+      </c>
+      <c r="B146" t="s">
+        <v>17</v>
+      </c>
+      <c r="C146" t="s">
+        <v>11</v>
+      </c>
+      <c r="D146">
+        <v>56.339108600000003</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>50</v>
+      </c>
+      <c r="B147" t="s">
+        <v>17</v>
+      </c>
+      <c r="C147" t="s">
+        <v>28</v>
+      </c>
+      <c r="D147">
+        <v>50.207640599999998</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>50</v>
+      </c>
+      <c r="B148" t="s">
+        <v>17</v>
+      </c>
+      <c r="C148" t="s">
         <v>22</v>
       </c>
-      <c r="D118">
-        <v>897.44555519999994</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>46</v>
-      </c>
-      <c r="B119" t="s">
-        <v>17</v>
-      </c>
-      <c r="C119" t="s">
+      <c r="D148">
+        <v>48.181075200000002</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>50</v>
+      </c>
+      <c r="B149" t="s">
+        <v>17</v>
+      </c>
+      <c r="C149" t="s">
+        <v>58</v>
+      </c>
+      <c r="D149">
+        <v>48.151496999999999</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>50</v>
+      </c>
+      <c r="B150" t="s">
+        <v>17</v>
+      </c>
+      <c r="C150" t="s">
+        <v>57</v>
+      </c>
+      <c r="D150">
+        <v>38.785400000000003</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>50</v>
+      </c>
+      <c r="B151" t="s">
+        <v>17</v>
+      </c>
+      <c r="C151" t="s">
+        <v>49</v>
+      </c>
+      <c r="D151">
+        <v>33.768990000000002</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>50</v>
+      </c>
+      <c r="B152" t="s">
+        <v>17</v>
+      </c>
+      <c r="C152" t="s">
+        <v>59</v>
+      </c>
+      <c r="D152">
+        <v>27.742000000000001</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>50</v>
+      </c>
+      <c r="B153" t="s">
+        <v>17</v>
+      </c>
+      <c r="C153" t="s">
+        <v>60</v>
+      </c>
+      <c r="D153">
+        <v>26.166374399999999</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>50</v>
+      </c>
+      <c r="B154" t="s">
+        <v>17</v>
+      </c>
+      <c r="C154" t="s">
         <v>25</v>
       </c>
-      <c r="D119">
-        <v>567.41111581400003</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>50</v>
-      </c>
-      <c r="B120" t="s">
-        <v>6</v>
-      </c>
-      <c r="C120" t="s">
-        <v>27</v>
-      </c>
-      <c r="D120">
-        <v>1219.89348</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>50</v>
-      </c>
-      <c r="B121" t="s">
-        <v>6</v>
-      </c>
-      <c r="C121" t="s">
-        <v>13</v>
-      </c>
-      <c r="D121">
-        <v>891.07434000000001</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>50</v>
-      </c>
-      <c r="B122" t="s">
-        <v>6</v>
-      </c>
-      <c r="C122" t="s">
-        <v>49</v>
-      </c>
-      <c r="D122">
-        <v>386.46965</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>50</v>
-      </c>
-      <c r="B123" t="s">
-        <v>6</v>
-      </c>
-      <c r="C123" t="s">
-        <v>12</v>
-      </c>
-      <c r="D123">
-        <v>376.3553</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>50</v>
-      </c>
-      <c r="B124" t="s">
-        <v>6</v>
-      </c>
-      <c r="C124" t="s">
-        <v>28</v>
-      </c>
-      <c r="D124">
-        <v>258.97612800000002</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>50</v>
-      </c>
-      <c r="B125" t="s">
-        <v>6</v>
-      </c>
-      <c r="C125" t="s">
-        <v>11</v>
-      </c>
-      <c r="D125">
-        <v>157.063692</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>50</v>
-      </c>
-      <c r="B126" t="s">
-        <v>6</v>
-      </c>
-      <c r="C126" t="s">
-        <v>51</v>
-      </c>
-      <c r="D126">
-        <v>80.896979999999999</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>50</v>
-      </c>
-      <c r="B127" t="s">
-        <v>6</v>
-      </c>
-      <c r="C127" t="s">
-        <v>22</v>
-      </c>
-      <c r="D127">
-        <v>66.592600000000004</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>50</v>
-      </c>
-      <c r="B128" t="s">
-        <v>6</v>
-      </c>
-      <c r="C128" t="s">
-        <v>52</v>
-      </c>
-      <c r="D128">
-        <v>35.567970000000003</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>50</v>
-      </c>
-      <c r="B129" t="s">
-        <v>6</v>
-      </c>
-      <c r="C129" t="s">
-        <v>46</v>
-      </c>
-      <c r="D129">
-        <v>32.722560000000001</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>50</v>
-      </c>
-      <c r="B130" t="s">
-        <v>6</v>
-      </c>
-      <c r="C130" t="s">
+      <c r="D154">
+        <v>312.90250348900003</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>61</v>
+      </c>
+      <c r="B155" t="s">
+        <v>6</v>
+      </c>
+      <c r="C155" t="s">
+        <v>62</v>
+      </c>
+      <c r="D155">
+        <v>537.23077231399998</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>61</v>
+      </c>
+      <c r="B156" t="s">
+        <v>6</v>
+      </c>
+      <c r="C156" t="s">
         <v>25</v>
       </c>
-      <c r="D130">
-        <v>76.413469636000002</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>50</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="s">
-        <v>53</v>
-      </c>
-      <c r="D131">
-        <v>51.984900000000003</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>50</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="s">
-        <v>21</v>
-      </c>
-      <c r="D132">
-        <v>54.700949999999999</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>50</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="s">
-        <v>22</v>
-      </c>
-      <c r="D133">
-        <v>43.162300000000002</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>50</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="s">
-        <v>48</v>
-      </c>
-      <c r="D134">
-        <v>37.572000000000003</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>50</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="s">
-        <v>54</v>
-      </c>
-      <c r="D135">
-        <v>26.318750000000001</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>50</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="s">
-        <v>55</v>
-      </c>
-      <c r="D136">
-        <v>24.028199999999998</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>50</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="s">
-        <v>56</v>
-      </c>
-      <c r="D137">
-        <v>21.36645</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>50</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="s">
-        <v>27</v>
-      </c>
-      <c r="D138">
-        <v>17.355250000000002</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>50</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="s">
-        <v>12</v>
-      </c>
-      <c r="D139">
-        <v>17.120100000000001</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>50</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="s">
-        <v>28</v>
-      </c>
-      <c r="D140">
-        <v>16.202475</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>50</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="s">
-        <v>49</v>
-      </c>
-      <c r="D141">
-        <v>13.5169</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>50</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="s">
-        <v>57</v>
-      </c>
-      <c r="D142">
-        <v>8.3619000000000003</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>50</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="s">
-        <v>13</v>
-      </c>
-      <c r="D143">
-        <v>2.3957999999999999</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>50</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="s">
-        <v>25</v>
-      </c>
-      <c r="D144">
-        <v>1791.136023734</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>50</v>
-      </c>
-      <c r="B145" t="s">
-        <v>17</v>
-      </c>
-      <c r="C145" t="s">
-        <v>13</v>
-      </c>
-      <c r="D145">
-        <v>691.42874749999999</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>50</v>
-      </c>
-      <c r="B146" t="s">
-        <v>17</v>
-      </c>
-      <c r="C146" t="s">
-        <v>12</v>
-      </c>
-      <c r="D146">
-        <v>437.546178</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>50</v>
-      </c>
-      <c r="B147" t="s">
-        <v>17</v>
-      </c>
-      <c r="C147" t="s">
-        <v>47</v>
-      </c>
-      <c r="D147">
-        <v>398.44944659999999</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>50</v>
-      </c>
-      <c r="B148" t="s">
-        <v>17</v>
-      </c>
-      <c r="C148" t="s">
-        <v>27</v>
-      </c>
-      <c r="D148">
-        <v>85.158848000000006</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>50</v>
-      </c>
-      <c r="B149" t="s">
-        <v>17</v>
-      </c>
-      <c r="C149" t="s">
-        <v>11</v>
-      </c>
-      <c r="D149">
-        <v>56.339108600000003</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>50</v>
-      </c>
-      <c r="B150" t="s">
-        <v>17</v>
-      </c>
-      <c r="C150" t="s">
-        <v>28</v>
-      </c>
-      <c r="D150">
-        <v>50.207640599999998</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>50</v>
-      </c>
-      <c r="B151" t="s">
-        <v>17</v>
-      </c>
-      <c r="C151" t="s">
-        <v>22</v>
-      </c>
-      <c r="D151">
-        <v>48.181075200000002</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>50</v>
-      </c>
-      <c r="B152" t="s">
-        <v>17</v>
-      </c>
-      <c r="C152" t="s">
-        <v>58</v>
-      </c>
-      <c r="D152">
-        <v>48.151496999999999</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>50</v>
-      </c>
-      <c r="B153" t="s">
-        <v>17</v>
-      </c>
-      <c r="C153" t="s">
-        <v>57</v>
-      </c>
-      <c r="D153">
-        <v>38.785400000000003</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>50</v>
-      </c>
-      <c r="B154" t="s">
-        <v>17</v>
-      </c>
-      <c r="C154" t="s">
-        <v>49</v>
-      </c>
-      <c r="D154">
-        <v>33.768990000000002</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>50</v>
-      </c>
-      <c r="B155" t="s">
-        <v>17</v>
-      </c>
-      <c r="C155" t="s">
-        <v>59</v>
-      </c>
-      <c r="D155">
-        <v>27.742000000000001</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>50</v>
-      </c>
-      <c r="B156" t="s">
-        <v>17</v>
-      </c>
-      <c r="C156" t="s">
-        <v>60</v>
-      </c>
       <c r="D156">
-        <v>26.166374399999999</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1.2738610640000001</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="B157" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C157" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="D157">
-        <v>312.90250348900003</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+        <v>571.68737199999998</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>61</v>
       </c>
       <c r="B158" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C158" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="D158">
-        <v>537.23077231399998</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1.2426057850000001</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B159" t="s">
         <v>6</v>
       </c>
       <c r="C159" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D159">
-        <v>1.2738610640000001</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+        <v>81.770314499999998</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B160" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C160" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="D160">
-        <v>571.68737199999998</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+        <v>114.13664420000001</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B161" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C161" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="D161">
-        <v>1.2426057850000001</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+        <v>74.028000000000006</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>63</v>
       </c>
@@ -2920,97 +2924,97 @@
         <v>6</v>
       </c>
       <c r="C162" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D162">
-        <v>81.770314499999998</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+        <v>334.50573044999999</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>63</v>
       </c>
       <c r="B163" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C163" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D163">
-        <v>114.13664420000001</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+        <v>82.876750000000001</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>63</v>
       </c>
       <c r="B164" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C164" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="D164">
-        <v>74.028000000000006</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+        <v>96.033543249999994</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>63</v>
       </c>
       <c r="B165" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C165" t="s">
         <v>25</v>
       </c>
       <c r="D165">
-        <v>334.50573044999999</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+        <v>619.63735652000003</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>63</v>
       </c>
       <c r="B166" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C166" t="s">
         <v>27</v>
       </c>
       <c r="D166">
-        <v>82.876750000000001</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+        <v>66.806430000000006</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>63</v>
       </c>
       <c r="B167" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C167" t="s">
         <v>28</v>
       </c>
       <c r="D167">
-        <v>96.033543249999994</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+        <v>62.841739349999997</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>63</v>
       </c>
       <c r="B168" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C168" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="D168">
-        <v>619.63735652000003</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+        <v>64.178100000000001</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>63</v>
       </c>
@@ -3018,216 +3022,216 @@
         <v>17</v>
       </c>
       <c r="C169" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D169">
-        <v>66.806430000000006</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+        <v>462.98242733000001</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B170" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C170" t="s">
-        <v>28</v>
-      </c>
-      <c r="D170">
-        <v>62.841739349999997</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B171" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C171" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D171">
-        <v>64.178100000000001</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1.0325E-4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B172" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C172" t="s">
-        <v>25</v>
-      </c>
-      <c r="D172">
-        <v>462.98242733000001</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>64</v>
       </c>
       <c r="B173" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C173" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="D173">
+        <v>1.1900000000000001E-4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>64</v>
       </c>
       <c r="B174" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C174" t="s">
-        <v>66</v>
-      </c>
-      <c r="D174">
-        <v>1.0325E-4</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B175" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C175" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+      <c r="D175">
+        <v>64.729280000000003</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B176" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C176" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="D176">
-        <v>1.1900000000000001E-4</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4.1003119999999997</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B177" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C177" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="D177">
+        <v>7.8800173759999996</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>67</v>
       </c>
       <c r="B178" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C178" t="s">
         <v>68</v>
       </c>
       <c r="D178">
-        <v>64.729280000000003</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57.4816</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>67</v>
       </c>
       <c r="B179" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C179" t="s">
         <v>25</v>
       </c>
       <c r="D179">
-        <v>4.1003119999999997</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3.4080650000000001E-3</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>67</v>
       </c>
       <c r="B180" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C180" t="s">
         <v>69</v>
       </c>
       <c r="D180">
-        <v>7.8800173759999996</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9.5435766019999999</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>67</v>
       </c>
       <c r="B181" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C181" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="D181">
-        <v>57.4816</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3.4080650000000001E-3</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B182" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C182" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D182">
-        <v>3.4080650000000001E-3</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B183" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C183" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="D183">
-        <v>9.5435766019999999</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B184" t="s">
         <v>17</v>
       </c>
       <c r="C184" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D184">
-        <v>3.4080650000000001E-3</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B185" t="s">
         <v>6</v>
@@ -3236,12 +3240,12 @@
         <v>40</v>
       </c>
       <c r="D185">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B186" t="s">
         <v>16</v>
@@ -3250,12 +3254,12 @@
         <v>40</v>
       </c>
       <c r="D186">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B187" t="s">
         <v>17</v>
@@ -3264,12 +3268,12 @@
         <v>40</v>
       </c>
       <c r="D187">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B188" t="s">
         <v>6</v>
@@ -3278,12 +3282,12 @@
         <v>40</v>
       </c>
       <c r="D188">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B189" t="s">
         <v>16</v>
@@ -3292,12 +3296,12 @@
         <v>40</v>
       </c>
       <c r="D189">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B190" t="s">
         <v>17</v>
@@ -3306,12 +3310,12 @@
         <v>40</v>
       </c>
       <c r="D190">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="B191" t="s">
         <v>6</v>
@@ -3320,12 +3324,12 @@
         <v>40</v>
       </c>
       <c r="D191">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="B192" t="s">
         <v>16</v>
@@ -3334,12 +3338,12 @@
         <v>40</v>
       </c>
       <c r="D192">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="B193" t="s">
         <v>17</v>
@@ -3348,12 +3352,12 @@
         <v>40</v>
       </c>
       <c r="D193">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B194" t="s">
         <v>6</v>
@@ -3362,12 +3366,12 @@
         <v>40</v>
       </c>
       <c r="D194">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B195" t="s">
         <v>16</v>
@@ -3376,12 +3380,12 @@
         <v>40</v>
       </c>
       <c r="D195">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B196" t="s">
         <v>17</v>
@@ -3390,12 +3394,12 @@
         <v>40</v>
       </c>
       <c r="D196">
-        <v>51</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="B197" t="s">
         <v>6</v>
@@ -3404,12 +3408,12 @@
         <v>40</v>
       </c>
       <c r="D197">
-        <v>3</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="B198" t="s">
         <v>16</v>
@@ -3418,12 +3422,12 @@
         <v>40</v>
       </c>
       <c r="D198">
-        <v>6</v>
+        <v>326</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="B199" t="s">
         <v>17</v>
@@ -3432,12 +3436,12 @@
         <v>40</v>
       </c>
       <c r="D199">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B200" t="s">
         <v>6</v>
@@ -3446,12 +3450,12 @@
         <v>40</v>
       </c>
       <c r="D200">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B201" t="s">
         <v>16</v>
@@ -3460,12 +3464,12 @@
         <v>40</v>
       </c>
       <c r="D201">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B202" t="s">
         <v>17</v>
@@ -3474,12 +3478,12 @@
         <v>40</v>
       </c>
       <c r="D202">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B203" t="s">
         <v>6</v>
@@ -3488,12 +3492,12 @@
         <v>40</v>
       </c>
       <c r="D203">
-        <v>1198</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B204" t="s">
         <v>16</v>
@@ -3502,12 +3506,12 @@
         <v>40</v>
       </c>
       <c r="D204">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B205" t="s">
         <v>17</v>
@@ -3516,52 +3520,52 @@
         <v>40</v>
       </c>
       <c r="D205">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B206" t="s">
         <v>6</v>
       </c>
       <c r="C206" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="D206">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+        <v>291.53755000000001</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B207" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C207" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D207">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+        <v>97.599699999999999</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B208" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C208" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D208">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+        <v>139.96039999999999</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>70</v>
       </c>
@@ -3569,13 +3573,13 @@
         <v>6</v>
       </c>
       <c r="C209" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="D209">
-        <v>291.53755000000001</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+        <v>126.0891627</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>70</v>
       </c>
@@ -3583,13 +3587,13 @@
         <v>6</v>
       </c>
       <c r="C210" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D210">
-        <v>97.599699999999999</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+        <v>484.16045324999999</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>70</v>
       </c>
@@ -3597,13 +3601,13 @@
         <v>6</v>
       </c>
       <c r="C211" t="s">
-        <v>49</v>
-      </c>
-      <c r="D211">
-        <v>139.96039999999999</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="E211">
+        <v>97.860349999999997</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>70</v>
       </c>
@@ -3611,13 +3615,13 @@
         <v>6</v>
       </c>
       <c r="C212" t="s">
-        <v>47</v>
-      </c>
-      <c r="D212">
-        <v>126.0891627</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="E212">
+        <v>118.3644</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>70</v>
       </c>
@@ -3625,13 +3629,13 @@
         <v>6</v>
       </c>
       <c r="C213" t="s">
-        <v>25</v>
-      </c>
-      <c r="D213">
-        <v>484.16045324999999</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="E213">
+        <v>40.125</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>70</v>
       </c>
@@ -3639,55 +3643,55 @@
         <v>6</v>
       </c>
       <c r="C214" t="s">
-        <v>72</v>
-      </c>
-      <c r="E214">
-        <v>97.860349999999997</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="D214">
+        <v>-17.442687286000002</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>70</v>
       </c>
       <c r="B215" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C215" t="s">
-        <v>7</v>
-      </c>
-      <c r="E215">
-        <v>118.3644</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="D215">
+        <v>319.48334</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>70</v>
       </c>
       <c r="B216" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C216" t="s">
-        <v>71</v>
-      </c>
-      <c r="E216">
-        <v>40.125</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="D216">
+        <v>1110.0100874</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>70</v>
       </c>
       <c r="B217" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C217" t="s">
-        <v>40</v>
-      </c>
-      <c r="D217">
-        <v>-17.442687286000002</v>
-      </c>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="E217">
+        <v>131.24760000000001</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>70</v>
       </c>
@@ -3695,13 +3699,13 @@
         <v>16</v>
       </c>
       <c r="C218" t="s">
-        <v>71</v>
-      </c>
-      <c r="D218">
-        <v>319.48334</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="E218">
+        <v>77.801199999999994</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>70</v>
       </c>
@@ -3709,13 +3713,13 @@
         <v>16</v>
       </c>
       <c r="C219" t="s">
-        <v>25</v>
-      </c>
-      <c r="D219">
-        <v>1110.0100874</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="E219">
+        <v>49.610999999999997</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>70</v>
       </c>
@@ -3723,13 +3727,13 @@
         <v>16</v>
       </c>
       <c r="C220" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="E220">
-        <v>131.24760000000001</v>
-      </c>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+        <v>36.58</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>70</v>
       </c>
@@ -3737,55 +3741,55 @@
         <v>16</v>
       </c>
       <c r="C221" t="s">
-        <v>72</v>
-      </c>
-      <c r="E221">
-        <v>77.801199999999994</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="D221">
+        <v>22.643851017999999</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>70</v>
       </c>
       <c r="B222" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C222" t="s">
-        <v>73</v>
-      </c>
-      <c r="E222">
-        <v>49.610999999999997</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+      <c r="D222">
+        <v>147.13238000000001</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>70</v>
       </c>
       <c r="B223" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C223" t="s">
-        <v>49</v>
-      </c>
-      <c r="E223">
-        <v>36.58</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="D223">
+        <v>102.867975</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>70</v>
       </c>
       <c r="B224" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C224" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D224">
-        <v>22.643851017999999</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+        <v>125.2624716</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>70</v>
       </c>
@@ -3793,13 +3797,13 @@
         <v>17</v>
       </c>
       <c r="C225" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D225">
-        <v>147.13238000000001</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+        <v>129.71071259999999</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>70</v>
       </c>
@@ -3807,13 +3811,13 @@
         <v>17</v>
       </c>
       <c r="C226" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D226">
-        <v>102.867975</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+        <v>127.5998</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>70</v>
       </c>
@@ -3821,13 +3825,13 @@
         <v>17</v>
       </c>
       <c r="C227" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D227">
-        <v>125.2624716</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+        <v>466.77496559999997</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>70</v>
       </c>
@@ -3835,13 +3839,13 @@
         <v>17</v>
       </c>
       <c r="C228" t="s">
-        <v>47</v>
-      </c>
-      <c r="D228">
-        <v>129.71071259999999</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="E228">
+        <v>270.72160000000002</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>70</v>
       </c>
@@ -3849,13 +3853,13 @@
         <v>17</v>
       </c>
       <c r="C229" t="s">
-        <v>49</v>
-      </c>
-      <c r="D229">
-        <v>127.5998</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="E229">
+        <v>145.33860000000001</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>70</v>
       </c>
@@ -3863,13 +3867,13 @@
         <v>17</v>
       </c>
       <c r="C230" t="s">
-        <v>25</v>
-      </c>
-      <c r="D230">
-        <v>466.77496559999997</v>
-      </c>
-    </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="E230">
+        <v>50.883000000000003</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>70</v>
       </c>
@@ -3877,13 +3881,13 @@
         <v>17</v>
       </c>
       <c r="C231" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="E231">
-        <v>270.72160000000002</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+        <v>62.96705</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>70</v>
       </c>
@@ -3891,43 +3895,43 @@
         <v>17</v>
       </c>
       <c r="C232" t="s">
-        <v>7</v>
-      </c>
-      <c r="E232">
-        <v>145.33860000000001</v>
-      </c>
-    </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="D232">
+        <v>-33.634174170000001</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B233" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C233" t="s">
-        <v>73</v>
-      </c>
-      <c r="E233">
-        <v>50.883000000000003</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="D233">
+        <v>91.021986687999998</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B234" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C234" t="s">
-        <v>15</v>
-      </c>
-      <c r="E234">
-        <v>62.96705</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="D234">
+        <v>66.466997524000007</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B235" t="s">
         <v>17</v>
@@ -3936,52 +3940,52 @@
         <v>40</v>
       </c>
       <c r="D235">
-        <v>-33.634174170000001</v>
-      </c>
-    </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41.544733348999998</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="B236" t="s">
         <v>6</v>
       </c>
       <c r="C236" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D236">
-        <v>91.021986687999998</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1935.6160052</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="B237" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C237" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="D237">
-        <v>66.466997524000007</v>
-      </c>
-    </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1093.40625</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="B238" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C238" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D238">
-        <v>41.544733348999998</v>
-      </c>
-    </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+        <v>936.03599999999994</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>23</v>
       </c>
@@ -3989,13 +3993,13 @@
         <v>6</v>
       </c>
       <c r="C239" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D239">
-        <v>1935.6160052</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+        <v>870.293138</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>23</v>
       </c>
@@ -4003,13 +4007,13 @@
         <v>6</v>
       </c>
       <c r="C240" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="D240">
-        <v>1093.40625</v>
-      </c>
-    </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+        <v>703.93795499999999</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>23</v>
       </c>
@@ -4017,13 +4021,13 @@
         <v>6</v>
       </c>
       <c r="C241" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D241">
-        <v>936.03599999999994</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+        <v>453.33</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>23</v>
       </c>
@@ -4031,13 +4035,13 @@
         <v>6</v>
       </c>
       <c r="C242" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D242">
-        <v>870.293138</v>
-      </c>
-    </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+        <v>490.97399999999999</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>23</v>
       </c>
@@ -4045,13 +4049,13 @@
         <v>6</v>
       </c>
       <c r="C243" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D243">
-        <v>703.93795499999999</v>
-      </c>
-    </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+        <v>465.35771999999997</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>23</v>
       </c>
@@ -4059,13 +4063,13 @@
         <v>6</v>
       </c>
       <c r="C244" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="D244">
-        <v>453.33</v>
-      </c>
-    </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2569.0349262</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>23</v>
       </c>
@@ -4073,13 +4077,13 @@
         <v>6</v>
       </c>
       <c r="C245" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D245">
-        <v>490.97399999999999</v>
-      </c>
-    </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>23</v>
       </c>
@@ -4087,13 +4091,13 @@
         <v>6</v>
       </c>
       <c r="C246" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D246">
-        <v>465.35771999999997</v>
-      </c>
-    </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+        <v>959.69100000000003</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>23</v>
       </c>
@@ -4101,55 +4105,55 @@
         <v>6</v>
       </c>
       <c r="C247" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="D247">
-        <v>2569.0349262</v>
-      </c>
-    </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+        <v>284.44299999999998</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>23</v>
       </c>
       <c r="B248" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="C248" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D248">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1763.249</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>23</v>
       </c>
       <c r="B249" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="C249" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D249">
-        <v>959.69100000000003</v>
-      </c>
-    </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1752.2063000000001</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>23</v>
       </c>
       <c r="B250" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="C250" t="s">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="D250">
-        <v>284.44299999999998</v>
-      </c>
-    </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2495.8277849999999</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>23</v>
       </c>
@@ -4157,13 +4161,13 @@
         <v>79</v>
       </c>
       <c r="C251" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D251">
-        <v>1763.249</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2574.3249999999998</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>23</v>
       </c>
@@ -4171,13 +4175,13 @@
         <v>79</v>
       </c>
       <c r="C252" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D252">
-        <v>1752.2063000000001</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1101.24</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>23</v>
       </c>
@@ -4185,52 +4189,52 @@
         <v>79</v>
       </c>
       <c r="C253" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="D253">
-        <v>2495.8277849999999</v>
+        <v>191.304</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B254" t="s">
         <v>79</v>
       </c>
       <c r="C254" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="D254">
-        <v>2574.3249999999998</v>
+        <v>388.8</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B255" t="s">
         <v>79</v>
       </c>
       <c r="C255" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="D255">
-        <v>1101.24</v>
+        <v>106.95099999999999</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B256" t="s">
         <v>79</v>
       </c>
       <c r="C256" t="s">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="D256">
-        <v>191.304</v>
+        <v>374.26499999999999</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
@@ -4241,10 +4245,10 @@
         <v>79</v>
       </c>
       <c r="C257" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="D257">
-        <v>388.8</v>
+        <v>122.08</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
@@ -4255,10 +4259,10 @@
         <v>79</v>
       </c>
       <c r="C258" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="D258">
-        <v>106.95099999999999</v>
+        <v>116.294</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
@@ -4269,10 +4273,10 @@
         <v>79</v>
       </c>
       <c r="C259" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D259">
-        <v>374.26499999999999</v>
+        <v>3805.7429999999999</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
@@ -4283,10 +4287,10 @@
         <v>79</v>
       </c>
       <c r="C260" t="s">
-        <v>28</v>
-      </c>
-      <c r="D260">
-        <v>122.08</v>
+        <v>30</v>
+      </c>
+      <c r="E260">
+        <v>200</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
@@ -4297,55 +4301,55 @@
         <v>79</v>
       </c>
       <c r="C261" t="s">
-        <v>27</v>
-      </c>
-      <c r="D261">
-        <v>116.294</v>
-      </c>
-    </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="E261">
+        <v>275.238</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="B262" t="s">
         <v>79</v>
       </c>
       <c r="C262" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="D262">
-        <v>3805.7429999999999</v>
-      </c>
-    </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+        <v>321.96100000000001</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="B263" t="s">
         <v>79</v>
       </c>
       <c r="C263" t="s">
-        <v>30</v>
-      </c>
-      <c r="E263">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="D263">
+        <v>229.74100000000001</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="B264" t="s">
         <v>79</v>
       </c>
       <c r="C264" t="s">
-        <v>29</v>
-      </c>
-      <c r="E264">
-        <v>275.238</v>
-      </c>
-    </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="D264">
+        <v>157.09299999999999</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>70</v>
       </c>
@@ -4353,13 +4357,13 @@
         <v>79</v>
       </c>
       <c r="C265" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="D265">
-        <v>321.96100000000001</v>
-      </c>
-    </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+        <v>169.16200000000001</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>70</v>
       </c>
@@ -4367,13 +4371,13 @@
         <v>79</v>
       </c>
       <c r="C266" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D266">
-        <v>229.74100000000001</v>
-      </c>
-    </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+        <v>364.79500000000002</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>70</v>
       </c>
@@ -4381,13 +4385,13 @@
         <v>79</v>
       </c>
       <c r="C267" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="D267">
-        <v>157.09299999999999</v>
-      </c>
-    </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+        <v>28.222999999999999</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>70</v>
       </c>
@@ -4395,13 +4399,13 @@
         <v>79</v>
       </c>
       <c r="C268" t="s">
-        <v>47</v>
-      </c>
-      <c r="D268">
-        <v>169.16200000000001</v>
-      </c>
-    </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="E268">
+        <v>111.91</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>70</v>
       </c>
@@ -4409,13 +4413,13 @@
         <v>79</v>
       </c>
       <c r="C269" t="s">
-        <v>25</v>
-      </c>
-      <c r="D269">
-        <v>364.79500000000002</v>
-      </c>
-    </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="E269">
+        <v>92.884</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>70</v>
       </c>
@@ -4423,13 +4427,13 @@
         <v>79</v>
       </c>
       <c r="C270" t="s">
-        <v>76</v>
-      </c>
-      <c r="D270">
-        <v>28.222999999999999</v>
-      </c>
-    </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="E270">
+        <v>47.414999999999999</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>70</v>
       </c>
@@ -4437,55 +4441,52 @@
         <v>79</v>
       </c>
       <c r="C271" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="E271">
-        <v>111.91</v>
-      </c>
-    </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+        <v>156.172</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="B272" t="s">
         <v>79</v>
       </c>
       <c r="C272" t="s">
-        <v>72</v>
-      </c>
-      <c r="E272">
-        <v>92.884</v>
-      </c>
-    </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="B273" t="s">
         <v>79</v>
       </c>
       <c r="C273" t="s">
-        <v>73</v>
-      </c>
-      <c r="E273">
-        <v>47.414999999999999</v>
-      </c>
-    </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="D273">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="B274" t="s">
         <v>79</v>
       </c>
       <c r="C274" t="s">
-        <v>25</v>
-      </c>
-      <c r="E274">
-        <v>156.172</v>
-      </c>
-    </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="D274">
+        <v>8.3079999999999998</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>18</v>
       </c>
@@ -4493,10 +4494,13 @@
         <v>79</v>
       </c>
       <c r="C275" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="D275">
+        <v>111.676</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>18</v>
       </c>
@@ -4504,13 +4508,13 @@
         <v>79</v>
       </c>
       <c r="C276" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D276">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>18</v>
       </c>
@@ -4518,13 +4522,13 @@
         <v>79</v>
       </c>
       <c r="C277" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D277">
-        <v>8.3079999999999998</v>
-      </c>
-    </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>18</v>
       </c>
@@ -4532,13 +4536,13 @@
         <v>79</v>
       </c>
       <c r="C278" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D278">
-        <v>111.676</v>
-      </c>
-    </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+        <v>66.446399999999997</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>18</v>
       </c>
@@ -4546,13 +4550,13 @@
         <v>79</v>
       </c>
       <c r="C279" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="D279">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+        <v>60.198599999999999</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>18</v>
       </c>
@@ -4560,13 +4564,13 @@
         <v>79</v>
       </c>
       <c r="C280" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D280">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+        <v>16.675999999999998</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>18</v>
       </c>
@@ -4574,13 +4578,13 @@
         <v>79</v>
       </c>
       <c r="C281" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="D281">
-        <v>66.446399999999997</v>
-      </c>
-    </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+        <v>16.715</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>18</v>
       </c>
@@ -4588,13 +4592,13 @@
         <v>79</v>
       </c>
       <c r="C282" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D282">
-        <v>60.198599999999999</v>
-      </c>
-    </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+        <v>38.396999999999998</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>18</v>
       </c>
@@ -4602,13 +4606,13 @@
         <v>79</v>
       </c>
       <c r="C283" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="D283">
-        <v>16.675999999999998</v>
-      </c>
-    </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>18</v>
       </c>
@@ -4616,43 +4620,43 @@
         <v>79</v>
       </c>
       <c r="C284" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="D284">
-        <v>16.715</v>
-      </c>
-    </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="B285" t="s">
         <v>79</v>
       </c>
       <c r="C285" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="D285">
-        <v>38.396999999999998</v>
-      </c>
-    </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B286" t="s">
         <v>79</v>
       </c>
       <c r="C286" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="D286">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3048</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B287" t="s">
         <v>79</v>
@@ -4661,52 +4665,52 @@
         <v>40</v>
       </c>
       <c r="D287">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B288" t="s">
         <v>79</v>
       </c>
       <c r="C288" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="D288">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+        <v>74.397000000000006</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="B289" t="s">
         <v>79</v>
       </c>
       <c r="C289" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D289">
-        <v>3048</v>
-      </c>
-    </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+        <v>163.31</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="B290" t="s">
         <v>79</v>
       </c>
       <c r="C290" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D290">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+        <v>534.41600000000005</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>63</v>
       </c>
@@ -4714,405 +4718,405 @@
         <v>79</v>
       </c>
       <c r="C291" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="D291">
-        <v>74.397000000000006</v>
-      </c>
-    </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="B292" t="s">
         <v>79</v>
       </c>
       <c r="C292" t="s">
+        <v>22</v>
+      </c>
+      <c r="D292" s="2">
+        <v>560.84807000000001</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>50</v>
+      </c>
+      <c r="B293" t="s">
+        <v>79</v>
+      </c>
+      <c r="C293" t="s">
+        <v>48</v>
+      </c>
+      <c r="D293" s="2">
+        <v>480.37799999999999</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>50</v>
+      </c>
+      <c r="B294" t="s">
+        <v>79</v>
+      </c>
+      <c r="C294" t="s">
+        <v>41</v>
+      </c>
+      <c r="D294" s="2">
+        <v>457.70800000000003</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>50</v>
+      </c>
+      <c r="B295" t="s">
+        <v>79</v>
+      </c>
+      <c r="C295" t="s">
+        <v>85</v>
+      </c>
+      <c r="D295" s="2">
+        <v>440.096</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>50</v>
+      </c>
+      <c r="B296" t="s">
+        <v>79</v>
+      </c>
+      <c r="C296" t="s">
+        <v>49</v>
+      </c>
+      <c r="D296" s="2">
+        <v>388.70979</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>50</v>
+      </c>
+      <c r="B297" t="s">
+        <v>79</v>
+      </c>
+      <c r="C297" t="s">
+        <v>86</v>
+      </c>
+      <c r="D297" s="2">
+        <v>386.8227</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>50</v>
+      </c>
+      <c r="B298" t="s">
+        <v>79</v>
+      </c>
+      <c r="C298" t="s">
+        <v>10</v>
+      </c>
+      <c r="D298" s="2">
+        <v>324.61559999999997</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>50</v>
+      </c>
+      <c r="B299" t="s">
+        <v>79</v>
+      </c>
+      <c r="C299" t="s">
         <v>28</v>
       </c>
-      <c r="D292">
-        <v>163.31</v>
-      </c>
-    </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A293" t="s">
-        <v>63</v>
-      </c>
-      <c r="B293" t="s">
-        <v>79</v>
-      </c>
-      <c r="C293" t="s">
-        <v>25</v>
-      </c>
-      <c r="D293">
-        <v>534.41600000000005</v>
-      </c>
-    </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A294" t="s">
-        <v>63</v>
-      </c>
-      <c r="B294" t="s">
-        <v>79</v>
-      </c>
-      <c r="C294" t="s">
+      <c r="D299" s="2">
+        <v>283.223343</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>50</v>
+      </c>
+      <c r="B300" t="s">
+        <v>79</v>
+      </c>
+      <c r="C300" t="s">
+        <v>47</v>
+      </c>
+      <c r="D300" s="2">
+        <v>257.17744499999998</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>50</v>
+      </c>
+      <c r="B301" t="s">
+        <v>79</v>
+      </c>
+      <c r="C301" t="s">
+        <v>87</v>
+      </c>
+      <c r="D301" s="2">
+        <v>267.80786999999998</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>50</v>
+      </c>
+      <c r="B302" t="s">
+        <v>79</v>
+      </c>
+      <c r="C302" t="s">
+        <v>11</v>
+      </c>
+      <c r="D302" s="2">
+        <v>236.04599999999999</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>50</v>
+      </c>
+      <c r="B303" t="s">
+        <v>79</v>
+      </c>
+      <c r="C303" t="s">
+        <v>57</v>
+      </c>
+      <c r="D303" s="2">
+        <v>207.93639999999999</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>50</v>
+      </c>
+      <c r="B304" t="s">
+        <v>79</v>
+      </c>
+      <c r="C304" t="s">
+        <v>88</v>
+      </c>
+      <c r="D304" s="2">
+        <v>184.02464000000001</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>50</v>
+      </c>
+      <c r="B305" t="s">
+        <v>79</v>
+      </c>
+      <c r="C305" t="s">
+        <v>60</v>
+      </c>
+      <c r="D305" s="2">
+        <v>186.27279999999999</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>50</v>
+      </c>
+      <c r="B306" t="s">
+        <v>79</v>
+      </c>
+      <c r="C306" t="s">
+        <v>89</v>
+      </c>
+      <c r="D306" s="2">
+        <v>181.30464520000001</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>50</v>
+      </c>
+      <c r="B307" t="s">
+        <v>79</v>
+      </c>
+      <c r="C307" t="s">
+        <v>90</v>
+      </c>
+      <c r="D307" s="2">
+        <v>180.90083999999999</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>50</v>
+      </c>
+      <c r="B308" t="s">
+        <v>79</v>
+      </c>
+      <c r="C308" t="s">
+        <v>27</v>
+      </c>
+      <c r="D308" s="2">
+        <v>152.46270000000001</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>50</v>
+      </c>
+      <c r="B309" t="s">
+        <v>79</v>
+      </c>
+      <c r="C309" t="s">
+        <v>29</v>
+      </c>
+      <c r="D309" s="2">
+        <v>152.52197609999999</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>50</v>
+      </c>
+      <c r="B310" t="s">
+        <v>79</v>
+      </c>
+      <c r="C310" t="s">
+        <v>13</v>
+      </c>
+      <c r="D310" s="2">
+        <v>140.721555</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>50</v>
+      </c>
+      <c r="B311" t="s">
+        <v>79</v>
+      </c>
+      <c r="C311" t="s">
+        <v>23</v>
+      </c>
+      <c r="D311" s="2">
+        <v>116.40547100000001</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>50</v>
+      </c>
+      <c r="B312" t="s">
+        <v>79</v>
+      </c>
+      <c r="C312" t="s">
+        <v>46</v>
+      </c>
+      <c r="D312" s="2">
+        <v>115.174015</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>50</v>
+      </c>
+      <c r="B313" t="s">
+        <v>79</v>
+      </c>
+      <c r="C313" t="s">
+        <v>12</v>
+      </c>
+      <c r="D313" s="2">
+        <v>115.07312</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>50</v>
+      </c>
+      <c r="B314" t="s">
+        <v>79</v>
+      </c>
+      <c r="C314" t="s">
         <v>40</v>
       </c>
-      <c r="D294">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A295" t="s">
-        <v>50</v>
-      </c>
-      <c r="B295" t="s">
-        <v>79</v>
-      </c>
-      <c r="C295" t="s">
-        <v>22</v>
-      </c>
-      <c r="D295" s="2">
-        <v>560.84807000000001</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A296" t="s">
-        <v>50</v>
-      </c>
-      <c r="B296" t="s">
-        <v>79</v>
-      </c>
-      <c r="C296" t="s">
-        <v>48</v>
-      </c>
-      <c r="D296" s="2">
-        <v>480.37799999999999</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A297" t="s">
-        <v>50</v>
-      </c>
-      <c r="B297" t="s">
-        <v>79</v>
-      </c>
-      <c r="C297" t="s">
-        <v>41</v>
-      </c>
-      <c r="D297" s="2">
-        <v>457.70800000000003</v>
-      </c>
-    </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A298" t="s">
-        <v>50</v>
-      </c>
-      <c r="B298" t="s">
-        <v>79</v>
-      </c>
-      <c r="C298" t="s">
-        <v>85</v>
-      </c>
-      <c r="D298" s="2">
-        <v>440.096</v>
-      </c>
-    </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A299" t="s">
-        <v>50</v>
-      </c>
-      <c r="B299" t="s">
-        <v>79</v>
-      </c>
-      <c r="C299" t="s">
-        <v>49</v>
-      </c>
-      <c r="D299" s="2">
-        <v>388.70979</v>
-      </c>
-    </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A300" t="s">
-        <v>50</v>
-      </c>
-      <c r="B300" t="s">
-        <v>79</v>
-      </c>
-      <c r="C300" t="s">
-        <v>86</v>
-      </c>
-      <c r="D300" s="2">
-        <v>386.8227</v>
-      </c>
-    </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A301" t="s">
-        <v>50</v>
-      </c>
-      <c r="B301" t="s">
-        <v>79</v>
-      </c>
-      <c r="C301" t="s">
-        <v>10</v>
-      </c>
-      <c r="D301" s="2">
-        <v>324.61559999999997</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A302" t="s">
-        <v>50</v>
-      </c>
-      <c r="B302" t="s">
-        <v>79</v>
-      </c>
-      <c r="C302" t="s">
-        <v>28</v>
-      </c>
-      <c r="D302" s="2">
-        <v>283.223343</v>
-      </c>
-    </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A303" t="s">
-        <v>50</v>
-      </c>
-      <c r="B303" t="s">
-        <v>79</v>
-      </c>
-      <c r="C303" t="s">
-        <v>47</v>
-      </c>
-      <c r="D303" s="2">
-        <v>257.17744499999998</v>
-      </c>
-    </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A304" t="s">
-        <v>50</v>
-      </c>
-      <c r="B304" t="s">
-        <v>79</v>
-      </c>
-      <c r="C304" t="s">
-        <v>87</v>
-      </c>
-      <c r="D304" s="2">
-        <v>267.80786999999998</v>
-      </c>
-    </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A305" t="s">
-        <v>50</v>
-      </c>
-      <c r="B305" t="s">
-        <v>79</v>
-      </c>
-      <c r="C305" t="s">
+      <c r="D314" s="2">
+        <v>549.97500000000002</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>61</v>
+      </c>
+      <c r="B315" t="s">
+        <v>79</v>
+      </c>
+      <c r="C315" t="s">
+        <v>62</v>
+      </c>
+      <c r="D315" s="2">
+        <v>455.26299999999998</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>61</v>
+      </c>
+      <c r="B316" t="s">
+        <v>79</v>
+      </c>
+      <c r="C316" t="s">
+        <v>40</v>
+      </c>
+      <c r="D316" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>5</v>
+      </c>
+      <c r="B317" t="s">
+        <v>79</v>
+      </c>
+      <c r="C317" t="s">
+        <v>7</v>
+      </c>
+      <c r="E317" s="2">
+        <v>847.84166740000001</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>5</v>
+      </c>
+      <c r="B318" t="s">
+        <v>79</v>
+      </c>
+      <c r="C318" t="s">
+        <v>9</v>
+      </c>
+      <c r="E318" s="2">
+        <v>1503.1095700000001</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>5</v>
+      </c>
+      <c r="B319" t="s">
+        <v>79</v>
+      </c>
+      <c r="C319" t="s">
         <v>11</v>
       </c>
-      <c r="D305" s="2">
-        <v>236.04599999999999</v>
-      </c>
-    </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A306" t="s">
-        <v>50</v>
-      </c>
-      <c r="B306" t="s">
-        <v>79</v>
-      </c>
-      <c r="C306" t="s">
-        <v>57</v>
-      </c>
-      <c r="D306" s="2">
-        <v>207.93639999999999</v>
-      </c>
-    </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A307" t="s">
-        <v>50</v>
-      </c>
-      <c r="B307" t="s">
-        <v>79</v>
-      </c>
-      <c r="C307" t="s">
-        <v>88</v>
-      </c>
-      <c r="D307" s="2">
-        <v>184.02464000000001</v>
-      </c>
-    </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A308" t="s">
-        <v>50</v>
-      </c>
-      <c r="B308" t="s">
-        <v>79</v>
-      </c>
-      <c r="C308" t="s">
-        <v>60</v>
-      </c>
-      <c r="D308" s="2">
-        <v>186.27279999999999</v>
-      </c>
-    </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A309" t="s">
-        <v>50</v>
-      </c>
-      <c r="B309" t="s">
-        <v>79</v>
-      </c>
-      <c r="C309" t="s">
-        <v>89</v>
-      </c>
-      <c r="D309" s="2">
-        <v>181.30464520000001</v>
-      </c>
-    </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A310" t="s">
-        <v>50</v>
-      </c>
-      <c r="B310" t="s">
-        <v>79</v>
-      </c>
-      <c r="C310" t="s">
-        <v>90</v>
-      </c>
-      <c r="D310" s="2">
-        <v>180.90083999999999</v>
-      </c>
-    </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A311" t="s">
-        <v>50</v>
-      </c>
-      <c r="B311" t="s">
-        <v>79</v>
-      </c>
-      <c r="C311" t="s">
-        <v>27</v>
-      </c>
-      <c r="D311" s="2">
-        <v>152.46270000000001</v>
-      </c>
-    </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A312" t="s">
-        <v>50</v>
-      </c>
-      <c r="B312" t="s">
-        <v>79</v>
-      </c>
-      <c r="C312" t="s">
-        <v>29</v>
-      </c>
-      <c r="D312" s="2">
-        <v>152.52197609999999</v>
-      </c>
-    </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A313" t="s">
-        <v>50</v>
-      </c>
-      <c r="B313" t="s">
-        <v>79</v>
-      </c>
-      <c r="C313" t="s">
-        <v>13</v>
-      </c>
-      <c r="D313" s="2">
-        <v>140.721555</v>
-      </c>
-    </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A314" t="s">
-        <v>50</v>
-      </c>
-      <c r="B314" t="s">
-        <v>79</v>
-      </c>
-      <c r="C314" t="s">
-        <v>23</v>
-      </c>
-      <c r="D314" s="2">
-        <v>116.40547100000001</v>
-      </c>
-    </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A315" t="s">
-        <v>50</v>
-      </c>
-      <c r="B315" t="s">
-        <v>79</v>
-      </c>
-      <c r="C315" t="s">
-        <v>46</v>
-      </c>
-      <c r="D315" s="2">
-        <v>115.174015</v>
-      </c>
-    </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A316" t="s">
-        <v>50</v>
-      </c>
-      <c r="B316" t="s">
-        <v>79</v>
-      </c>
-      <c r="C316" t="s">
-        <v>12</v>
-      </c>
-      <c r="D316" s="2">
-        <v>115.07312</v>
-      </c>
-    </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A317" t="s">
-        <v>50</v>
-      </c>
-      <c r="B317" t="s">
-        <v>79</v>
-      </c>
-      <c r="C317" t="s">
-        <v>40</v>
-      </c>
-      <c r="D317" s="2">
-        <v>549.97500000000002</v>
-      </c>
-    </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A318" t="s">
-        <v>61</v>
-      </c>
-      <c r="B318" t="s">
-        <v>79</v>
-      </c>
-      <c r="C318" t="s">
-        <v>62</v>
-      </c>
-      <c r="D318" s="2">
-        <v>455.26299999999998</v>
-      </c>
-    </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A319" t="s">
-        <v>61</v>
-      </c>
-      <c r="B319" t="s">
-        <v>79</v>
-      </c>
-      <c r="C319" t="s">
-        <v>40</v>
-      </c>
-      <c r="D319" s="2">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E319" s="2">
+        <v>211.977859</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>5</v>
       </c>
@@ -5120,13 +5124,13 @@
         <v>79</v>
       </c>
       <c r="C320" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E320" s="2">
-        <v>847.84166740000001</v>
-      </c>
-    </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
+        <v>94.759552999999997</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>5</v>
       </c>
@@ -5134,13 +5138,13 @@
         <v>79</v>
       </c>
       <c r="C321" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E321" s="2">
-        <v>1503.1095700000001</v>
-      </c>
-    </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
+        <v>487.711995</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>5</v>
       </c>
@@ -5148,13 +5152,13 @@
         <v>79</v>
       </c>
       <c r="C322" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E322" s="2">
-        <v>211.977859</v>
-      </c>
-    </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
+        <v>915.09</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>5</v>
       </c>
@@ -5162,55 +5166,55 @@
         <v>79</v>
       </c>
       <c r="C323" t="s">
-        <v>12</v>
-      </c>
-      <c r="E323" s="2">
-        <v>94.759552999999997</v>
-      </c>
-    </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="D323">
+        <v>518.94299999999998</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="B324" t="s">
         <v>79</v>
       </c>
       <c r="C324" t="s">
-        <v>13</v>
-      </c>
-      <c r="E324" s="2">
-        <v>487.711995</v>
-      </c>
-    </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="D324">
+        <v>575.76700000000005</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="B325" t="s">
         <v>79</v>
       </c>
       <c r="C325" t="s">
-        <v>14</v>
-      </c>
-      <c r="E325" s="2">
-        <v>915.09</v>
-      </c>
-    </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="D325">
+        <v>145.67400000000001</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="B326" t="s">
         <v>79</v>
       </c>
       <c r="C326" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D326">
-        <v>518.94299999999998</v>
-      </c>
-    </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+        <v>118.684</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>44</v>
       </c>
@@ -5218,13 +5222,13 @@
         <v>79</v>
       </c>
       <c r="C327" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="D327">
-        <v>575.76700000000005</v>
-      </c>
-    </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
+        <v>104.973</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>44</v>
       </c>
@@ -5232,13 +5236,13 @@
         <v>79</v>
       </c>
       <c r="C328" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D328">
-        <v>145.67400000000001</v>
-      </c>
-    </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
+        <v>476.053</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>44</v>
       </c>
@@ -5246,56 +5250,118 @@
         <v>79</v>
       </c>
       <c r="C329" t="s">
+        <v>40</v>
+      </c>
+      <c r="D329">
+        <v>1165.2354190000001</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>46</v>
+      </c>
+      <c r="B330" t="s">
+        <v>79</v>
+      </c>
+      <c r="C330" t="s">
+        <v>28</v>
+      </c>
+      <c r="D330">
+        <v>65.673950000000005</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>46</v>
+      </c>
+      <c r="B331" t="s">
+        <v>79</v>
+      </c>
+      <c r="C331" t="s">
+        <v>11</v>
+      </c>
+      <c r="D331">
+        <v>43.520085999999999</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>46</v>
+      </c>
+      <c r="B332" t="s">
+        <v>79</v>
+      </c>
+      <c r="C332" t="s">
+        <v>92</v>
+      </c>
+      <c r="D332">
+        <v>36.914999999999999</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>46</v>
+      </c>
+      <c r="B333" t="s">
+        <v>79</v>
+      </c>
+      <c r="C333" t="s">
+        <v>47</v>
+      </c>
+      <c r="D333">
+        <v>21.004349999999999</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>46</v>
+      </c>
+      <c r="B334" t="s">
+        <v>79</v>
+      </c>
+      <c r="C334" t="s">
         <v>49</v>
       </c>
-      <c r="D329">
-        <v>118.684</v>
-      </c>
-    </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A330" t="s">
-        <v>44</v>
-      </c>
-      <c r="B330" t="s">
-        <v>79</v>
-      </c>
-      <c r="C330" t="s">
-        <v>91</v>
-      </c>
-      <c r="D330">
-        <v>104.973</v>
-      </c>
-    </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A331" t="s">
-        <v>44</v>
-      </c>
-      <c r="B331" t="s">
-        <v>79</v>
-      </c>
-      <c r="C331" t="s">
+      <c r="D334">
+        <v>21.382999999999999</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>46</v>
+      </c>
+      <c r="B335" t="s">
+        <v>79</v>
+      </c>
+      <c r="C335" t="s">
         <v>25</v>
       </c>
-      <c r="D331">
-        <v>476.053</v>
-      </c>
-    </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A332" t="s">
-        <v>44</v>
-      </c>
-      <c r="B332" t="s">
-        <v>79</v>
-      </c>
-      <c r="C332" t="s">
+      <c r="D335">
+        <v>503.077</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>46</v>
+      </c>
+      <c r="B336" t="s">
+        <v>79</v>
+      </c>
+      <c r="C336" t="s">
         <v>40</v>
       </c>
-      <c r="D332">
-        <v>1165.2354190000001</v>
+      <c r="D336">
+        <v>1834.9179999999999</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E326" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:E336" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="SHS"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/sql/Prop book.xlsx
+++ b/sql/Prop book.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thao Dien\Broker-page - Copy\sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1083B0DD-A37A-4A35-9DD9-8F26B55A9FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB7F0E6-1503-4633-A70B-4BF54763780E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="22635" windowHeight="13515" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="93">
   <si>
-    <t>Broker</t>
-  </si>
-  <si>
     <t>Quarter</t>
   </si>
   <si>
@@ -315,6 +312,9 @@
   </si>
   <si>
     <t>VRE</t>
+  </si>
+  <si>
+    <t>Holdings</t>
   </si>
 </sst>
 </file>
@@ -680,4675 +680,4675 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:E336"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="5" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
       <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
         <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
       </c>
       <c r="E2">
         <v>598.5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3">
         <v>81.7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>1945.2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
       </c>
       <c r="E6">
         <v>180.69</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7">
         <v>3.3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E8">
         <v>232.999</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E9">
         <v>853</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10">
         <v>2756</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E11">
         <v>796.99</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="s">
-        <v>9</v>
       </c>
       <c r="E13">
         <v>1882.8</v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E14">
         <v>11.73</v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15">
         <v>297.25</v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E16">
         <v>139.4</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17">
         <v>803.12</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E18">
         <v>837.54</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19">
         <v>1673.2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20">
         <v>1184</v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" t="s">
-        <v>9</v>
       </c>
       <c r="E22">
         <v>2117.6</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" t="s">
-        <v>11</v>
       </c>
       <c r="E24">
         <v>12.33</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E25">
         <v>167.5</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E26">
         <v>695.36</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E27">
         <v>772.4</v>
       </c>
     </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E28">
         <v>2070</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" t="s">
         <v>18</v>
-      </c>
-      <c r="B29" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" t="s">
-        <v>19</v>
       </c>
       <c r="D29">
         <v>172.64</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D30">
         <v>282.2</v>
       </c>
     </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D31">
         <v>7.84</v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D32">
         <v>64.372</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D33">
         <v>105.5</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D34">
         <v>87.8</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D35">
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D36">
         <v>287.54000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" t="s">
         <v>26</v>
-      </c>
-      <c r="B37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" t="s">
-        <v>27</v>
       </c>
       <c r="D37">
         <v>177.85</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D38">
         <v>252.98500000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C39" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D39">
         <v>91.463300000000004</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D41">
         <f>3528.12+314.938</f>
         <v>3843.058</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E42">
         <v>275.23899999999998</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E43">
         <v>200</v>
       </c>
     </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" t="s">
         <v>18</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="s">
-        <v>19</v>
       </c>
       <c r="D44">
         <v>189.8</v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D45">
         <v>106.4</v>
       </c>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D46">
         <v>204.8</v>
       </c>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C47" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D47">
         <v>79.099999999999994</v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D48">
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D49">
         <v>0.1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
+        <v>17</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="s">
         <v>18</v>
-      </c>
-      <c r="B50" t="s">
-        <v>17</v>
-      </c>
-      <c r="C50" t="s">
-        <v>19</v>
       </c>
       <c r="D50">
         <v>170.9</v>
       </c>
     </row>
-    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B51" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C51" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D51">
         <v>238.4</v>
       </c>
     </row>
-    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D52">
         <v>123</v>
       </c>
     </row>
-    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D53">
         <v>91.6</v>
       </c>
     </row>
-    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B54" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C54" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D54">
         <v>71.3</v>
       </c>
     </row>
-    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D55">
         <v>47.6</v>
       </c>
     </row>
-    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B56" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C56" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D56">
         <v>178.9</v>
       </c>
     </row>
-    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C57" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D57">
         <v>10.3</v>
       </c>
     </row>
-    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B58" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C58" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D58">
         <v>1635</v>
       </c>
     </row>
-    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B59" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C59" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D59">
         <v>787</v>
       </c>
     </row>
-    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D60">
         <v>734.97</v>
       </c>
     </row>
-    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B61" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C61" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B62" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C62" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D62">
         <v>683.3</v>
       </c>
     </row>
-    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B63" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C63" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D63">
         <v>428.9</v>
       </c>
     </row>
-    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B64" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D64">
         <v>4362.4489999999996</v>
       </c>
     </row>
-    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B65" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C65" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D65">
         <v>684.67200000000003</v>
       </c>
     </row>
-    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B66" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C66" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D66">
         <v>873</v>
       </c>
     </row>
-    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B67" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C67" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D67">
         <v>298.214</v>
       </c>
     </row>
-    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B68" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C68" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D68">
         <v>1602.507328938</v>
       </c>
     </row>
-    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B69" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C69" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D69">
         <v>133.6666776649999</v>
       </c>
     </row>
-    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B70" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C70" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D70">
         <v>465.20486131000013</v>
       </c>
     </row>
-    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B71" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C71" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D71">
         <v>73.276574532000055</v>
       </c>
     </row>
-    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B72" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C72" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D72">
         <v>132.5779621770001</v>
       </c>
     </row>
-    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B73" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C73" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D73">
         <v>217.38459526099999</v>
       </c>
     </row>
-    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B74" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C74" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D74">
         <v>253.33511597899991</v>
       </c>
     </row>
-    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B75" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C75" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D75">
         <v>355.10702067800003</v>
       </c>
     </row>
-    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B76" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C76" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D76">
         <v>211.49055106</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B77" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C77" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D77">
         <v>313.72500000000002</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B78" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C78" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D78">
         <v>252.69882000000001</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B79" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C79" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D79">
         <v>131.61000000000001</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
+        <v>25</v>
+      </c>
+      <c r="B80" t="s">
+        <v>15</v>
+      </c>
+      <c r="C80" t="s">
         <v>26</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="s">
-        <v>27</v>
       </c>
       <c r="D80">
         <v>115.5</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B81" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C81" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D81">
         <v>80.653409999999994</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B82" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C82" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D82">
         <v>4593.8958050000001</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B83" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C83" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>25</v>
+      </c>
+      <c r="B84" t="s">
+        <v>15</v>
+      </c>
+      <c r="C84" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>26</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B85" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C85" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D85">
         <v>385.00864000000001</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B86" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C86" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D86">
         <v>204.87155000000001</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B87" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C87" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D87">
         <v>449.16890000000001</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B88" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C88" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D88">
         <v>298.416</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B89" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C89" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D89">
         <v>2868.1795425969999</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B90" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C90" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>25</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>26</v>
-      </c>
-      <c r="B91" t="s">
-        <v>17</v>
-      </c>
-      <c r="C91" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B92" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C92" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D92">
         <v>471.11800299999999</v>
       </c>
     </row>
-    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
+        <v>43</v>
+      </c>
+      <c r="B93" t="s">
+        <v>5</v>
+      </c>
+      <c r="C93" t="s">
         <v>44</v>
-      </c>
-      <c r="B93" t="s">
-        <v>6</v>
-      </c>
-      <c r="C93" t="s">
-        <v>45</v>
       </c>
       <c r="D93">
         <v>444.90018559999999</v>
       </c>
     </row>
-    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B94" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C94" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D94">
         <v>194.95070833</v>
       </c>
     </row>
-    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B95" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C95" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D95">
         <v>459.73992199999998</v>
       </c>
     </row>
-    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B96" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C96" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D96">
         <v>105.4291377</v>
       </c>
     </row>
-    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B97" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C97" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D97">
         <v>112.9934461</v>
       </c>
     </row>
-    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B98" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C98" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D98">
         <v>795.19149128900006</v>
       </c>
     </row>
-    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B99" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C99" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D99">
         <v>418.20360959999999</v>
       </c>
     </row>
-    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
+        <v>43</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="s">
         <v>44</v>
-      </c>
-      <c r="B100" t="s">
-        <v>17</v>
-      </c>
-      <c r="C100" t="s">
-        <v>45</v>
       </c>
       <c r="D100">
         <v>379.16809019999999</v>
       </c>
     </row>
-    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B101" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C101" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D101">
         <v>641.44849673199997</v>
       </c>
     </row>
-    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B102" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C102" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D102">
         <v>495.18126749999999</v>
       </c>
     </row>
-    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B103" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C103" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D103">
         <v>41.564160000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B104" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C104" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D104">
         <v>34.574301900000002</v>
       </c>
     </row>
-    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
+        <v>45</v>
+      </c>
+      <c r="B105" t="s">
+        <v>5</v>
+      </c>
+      <c r="C105" t="s">
         <v>46</v>
-      </c>
-      <c r="B105" t="s">
-        <v>6</v>
-      </c>
-      <c r="C105" t="s">
-        <v>47</v>
       </c>
       <c r="D105">
         <v>17.764817699999998</v>
       </c>
     </row>
-    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B106" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C106" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D106">
         <v>377.74047731399997</v>
       </c>
     </row>
-    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B107" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C107" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D107">
         <v>47.814399999999999</v>
       </c>
     </row>
-    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B108" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C108" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D108">
         <v>105.3778854</v>
       </c>
     </row>
-    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B109" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C109" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D109">
         <v>45.304979000000003</v>
       </c>
     </row>
-    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B110" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C110" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D110">
         <v>883.491355</v>
       </c>
     </row>
-    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B111" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C111" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D111">
         <v>329.83531951999998</v>
       </c>
     </row>
-    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B112" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C112" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D112">
         <v>56.4498575</v>
       </c>
     </row>
-    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B113" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C113" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D113">
         <v>48.783651149999997</v>
       </c>
     </row>
-    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B114" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C114" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D114">
         <v>53.905700000000003</v>
       </c>
     </row>
-    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B115" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C115" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D115">
         <v>897.44555519999994</v>
       </c>
     </row>
-    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B116" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C116" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D116">
         <v>567.41111581400003</v>
       </c>
     </row>
-    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B117" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C117" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D117">
         <v>1219.89348</v>
       </c>
     </row>
-    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B118" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C118" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D118">
         <v>891.07434000000001</v>
       </c>
     </row>
-    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B119" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C119" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D119">
         <v>386.46965</v>
       </c>
     </row>
-    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B120" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C120" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D120">
         <v>376.3553</v>
       </c>
     </row>
-    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B121" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C121" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D121">
         <v>258.97612800000002</v>
       </c>
     </row>
-    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B122" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C122" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D122">
         <v>157.063692</v>
       </c>
     </row>
-    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
+        <v>49</v>
+      </c>
+      <c r="B123" t="s">
+        <v>5</v>
+      </c>
+      <c r="C123" t="s">
         <v>50</v>
-      </c>
-      <c r="B123" t="s">
-        <v>6</v>
-      </c>
-      <c r="C123" t="s">
-        <v>51</v>
       </c>
       <c r="D123">
         <v>80.896979999999999</v>
       </c>
     </row>
-    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B124" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C124" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D124">
         <v>66.592600000000004</v>
       </c>
     </row>
-    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B125" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C125" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D125">
         <v>35.567970000000003</v>
       </c>
     </row>
-    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B126" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C126" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D126">
         <v>32.722560000000001</v>
       </c>
     </row>
-    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B127" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C127" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D127">
         <v>76.413469636000002</v>
       </c>
     </row>
-    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B128" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C128" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D128">
         <v>51.984900000000003</v>
       </c>
     </row>
-    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B129" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C129" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D129">
         <v>54.700949999999999</v>
       </c>
     </row>
-    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B130" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C130" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D130">
         <v>43.162300000000002</v>
       </c>
     </row>
-    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B131" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C131" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D131">
         <v>37.572000000000003</v>
       </c>
     </row>
-    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B132" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C132" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D132">
         <v>26.318750000000001</v>
       </c>
     </row>
-    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B133" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C133" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D133">
         <v>24.028199999999998</v>
       </c>
     </row>
-    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B134" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C134" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D134">
         <v>21.36645</v>
       </c>
     </row>
-    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B135" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C135" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D135">
         <v>17.355250000000002</v>
       </c>
     </row>
-    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B136" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C136" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D136">
         <v>17.120100000000001</v>
       </c>
     </row>
-    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B137" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C137" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D137">
         <v>16.202475</v>
       </c>
     </row>
-    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B138" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C138" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D138">
         <v>13.5169</v>
       </c>
     </row>
-    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B139" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C139" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D139">
         <v>8.3619000000000003</v>
       </c>
     </row>
-    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B140" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C140" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D140">
         <v>2.3957999999999999</v>
       </c>
     </row>
-    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B141" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C141" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D141">
         <v>1791.136023734</v>
       </c>
     </row>
-    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B142" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C142" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D142">
         <v>691.42874749999999</v>
       </c>
     </row>
-    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B143" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C143" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D143">
         <v>437.546178</v>
       </c>
     </row>
-    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B144" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C144" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D144">
         <v>398.44944659999999</v>
       </c>
     </row>
-    <row r="145" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B145" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C145" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D145">
         <v>85.158848000000006</v>
       </c>
     </row>
-    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B146" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C146" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D146">
         <v>56.339108600000003</v>
       </c>
     </row>
-    <row r="147" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B147" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C147" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D147">
         <v>50.207640599999998</v>
       </c>
     </row>
-    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B148" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C148" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D148">
         <v>48.181075200000002</v>
       </c>
     </row>
-    <row r="149" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B149" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C149" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D149">
         <v>48.151496999999999</v>
       </c>
     </row>
-    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B150" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C150" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D150">
         <v>38.785400000000003</v>
       </c>
     </row>
-    <row r="151" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B151" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C151" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D151">
         <v>33.768990000000002</v>
       </c>
     </row>
-    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B152" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C152" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D152">
         <v>27.742000000000001</v>
       </c>
     </row>
-    <row r="153" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B153" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C153" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D153">
         <v>26.166374399999999</v>
       </c>
     </row>
-    <row r="154" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B154" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C154" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D154">
         <v>312.90250348900003</v>
       </c>
     </row>
-    <row r="155" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
+        <v>60</v>
+      </c>
+      <c r="B155" t="s">
+        <v>5</v>
+      </c>
+      <c r="C155" t="s">
         <v>61</v>
-      </c>
-      <c r="B155" t="s">
-        <v>6</v>
-      </c>
-      <c r="C155" t="s">
-        <v>62</v>
       </c>
       <c r="D155">
         <v>537.23077231399998</v>
       </c>
     </row>
-    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B156" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C156" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D156">
         <v>1.2738610640000001</v>
       </c>
     </row>
-    <row r="157" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
+        <v>60</v>
+      </c>
+      <c r="B157" t="s">
+        <v>15</v>
+      </c>
+      <c r="C157" t="s">
         <v>61</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="s">
-        <v>62</v>
       </c>
       <c r="D157">
         <v>571.68737199999998</v>
       </c>
     </row>
-    <row r="158" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B158" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C158" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D158">
         <v>1.2426057850000001</v>
       </c>
     </row>
-    <row r="159" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B159" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C159" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D159">
         <v>81.770314499999998</v>
       </c>
     </row>
-    <row r="160" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B160" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C160" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D160">
         <v>114.13664420000001</v>
       </c>
     </row>
-    <row r="161" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B161" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C161" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D161">
         <v>74.028000000000006</v>
       </c>
     </row>
-    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B162" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C162" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D162">
         <v>334.50573044999999</v>
       </c>
     </row>
-    <row r="163" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B163" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C163" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D163">
         <v>82.876750000000001</v>
       </c>
     </row>
-    <row r="164" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B164" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C164" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D164">
         <v>96.033543249999994</v>
       </c>
     </row>
-    <row r="165" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B165" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C165" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D165">
         <v>619.63735652000003</v>
       </c>
     </row>
-    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B166" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C166" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D166">
         <v>66.806430000000006</v>
       </c>
     </row>
-    <row r="167" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B167" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C167" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D167">
         <v>62.841739349999997</v>
       </c>
     </row>
-    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B168" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C168" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D168">
         <v>64.178100000000001</v>
       </c>
     </row>
-    <row r="169" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B169" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C169" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D169">
         <v>462.98242733000001</v>
       </c>
     </row>
-    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
+        <v>63</v>
+      </c>
+      <c r="B170" t="s">
+        <v>5</v>
+      </c>
+      <c r="C170" t="s">
         <v>64</v>
       </c>
-      <c r="B170" t="s">
-        <v>6</v>
-      </c>
-      <c r="C170" t="s">
+    </row>
+    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>63</v>
+      </c>
+      <c r="B171" t="s">
+        <v>15</v>
+      </c>
+      <c r="C171" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>64</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="s">
-        <v>66</v>
       </c>
       <c r="D171">
         <v>1.0325E-4</v>
       </c>
     </row>
-    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
+        <v>63</v>
+      </c>
+      <c r="B172" t="s">
+        <v>15</v>
+      </c>
+      <c r="C172" t="s">
         <v>64</v>
       </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="s">
+    </row>
+    <row r="173" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>63</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>64</v>
-      </c>
-      <c r="B173" t="s">
-        <v>17</v>
-      </c>
-      <c r="C173" t="s">
-        <v>66</v>
       </c>
       <c r="D173">
         <v>1.1900000000000001E-4</v>
       </c>
     </row>
-    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
+        <v>63</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="s">
         <v>64</v>
       </c>
-      <c r="B174" t="s">
-        <v>17</v>
-      </c>
-      <c r="C174" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="175" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
+        <v>66</v>
+      </c>
+      <c r="B175" t="s">
+        <v>5</v>
+      </c>
+      <c r="C175" t="s">
         <v>67</v>
-      </c>
-      <c r="B175" t="s">
-        <v>6</v>
-      </c>
-      <c r="C175" t="s">
-        <v>68</v>
       </c>
       <c r="D175">
         <v>64.729280000000003</v>
       </c>
     </row>
-    <row r="176" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B176" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C176" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D176">
         <v>4.1003119999999997</v>
       </c>
     </row>
-    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B177" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C177" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D177">
         <v>7.8800173759999996</v>
       </c>
     </row>
-    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
+        <v>66</v>
+      </c>
+      <c r="B178" t="s">
+        <v>15</v>
+      </c>
+      <c r="C178" t="s">
         <v>67</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="s">
-        <v>68</v>
       </c>
       <c r="D178">
         <v>57.4816</v>
       </c>
     </row>
-    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B179" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C179" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D179">
         <v>3.4080650000000001E-3</v>
       </c>
     </row>
-    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B180" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C180" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D180">
         <v>9.5435766019999999</v>
       </c>
     </row>
-    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B181" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C181" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D181">
         <v>3.4080650000000001E-3</v>
       </c>
     </row>
-    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B182" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C182" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D182">
         <v>127</v>
       </c>
     </row>
-    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B183" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C183" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D183">
         <v>100</v>
       </c>
     </row>
-    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B184" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C184" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D184">
         <v>113</v>
       </c>
     </row>
-    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B185" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C185" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D185">
         <v>85</v>
       </c>
     </row>
-    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B186" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C186" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D186">
         <v>173</v>
       </c>
     </row>
-    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B187" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C187" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D187">
         <v>179</v>
       </c>
     </row>
-    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B188" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C188" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D188">
         <v>240</v>
       </c>
     </row>
-    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B189" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C189" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D189">
         <v>283</v>
       </c>
     </row>
-    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B190" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C190" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D190">
         <v>285</v>
       </c>
     </row>
-    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B191" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C191" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D191">
         <v>262</v>
       </c>
     </row>
-    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B192" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C192" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D192">
         <v>47</v>
       </c>
     </row>
-    <row r="193" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B193" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C193" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D193">
         <v>51</v>
       </c>
     </row>
-    <row r="194" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B194" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C194" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D194">
         <v>3</v>
       </c>
     </row>
-    <row r="195" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B195" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C195" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D195">
         <v>6</v>
       </c>
     </row>
-    <row r="196" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B196" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C196" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D196">
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B197" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C197" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D197">
         <v>463</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B198" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C198" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D198">
         <v>326</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B199" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C199" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D199">
         <v>287</v>
       </c>
     </row>
-    <row r="200" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B200" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C200" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D200">
         <v>1198</v>
       </c>
     </row>
-    <row r="201" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B201" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C201" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D201">
         <v>1047</v>
       </c>
     </row>
-    <row r="202" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B202" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C202" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D202">
         <v>555</v>
       </c>
     </row>
-    <row r="203" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B203" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C203" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D203">
         <v>488</v>
       </c>
     </row>
-    <row r="204" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B204" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C204" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D204">
         <v>478</v>
       </c>
     </row>
-    <row r="205" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B205" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C205" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D205">
         <v>275</v>
       </c>
     </row>
-    <row r="206" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
+        <v>69</v>
+      </c>
+      <c r="B206" t="s">
+        <v>5</v>
+      </c>
+      <c r="C206" t="s">
         <v>70</v>
-      </c>
-      <c r="B206" t="s">
-        <v>6</v>
-      </c>
-      <c r="C206" t="s">
-        <v>71</v>
       </c>
       <c r="D206">
         <v>291.53755000000001</v>
       </c>
     </row>
-    <row r="207" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B207" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C207" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D207">
         <v>97.599699999999999</v>
       </c>
     </row>
-    <row r="208" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B208" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C208" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D208">
         <v>139.96039999999999</v>
       </c>
     </row>
-    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B209" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C209" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D209">
         <v>126.0891627</v>
       </c>
     </row>
-    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B210" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C210" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D210">
         <v>484.16045324999999</v>
       </c>
     </row>
-    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B211" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C211" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E211">
         <v>97.860349999999997</v>
       </c>
     </row>
-    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B212" t="s">
+        <v>5</v>
+      </c>
+      <c r="C212" t="s">
         <v>6</v>
-      </c>
-      <c r="C212" t="s">
-        <v>7</v>
       </c>
       <c r="E212">
         <v>118.3644</v>
       </c>
     </row>
-    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
+        <v>69</v>
+      </c>
+      <c r="B213" t="s">
+        <v>5</v>
+      </c>
+      <c r="C213" t="s">
         <v>70</v>
-      </c>
-      <c r="B213" t="s">
-        <v>6</v>
-      </c>
-      <c r="C213" t="s">
-        <v>71</v>
       </c>
       <c r="E213">
         <v>40.125</v>
       </c>
     </row>
-    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B214" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C214" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D214">
         <v>-17.442687286000002</v>
       </c>
     </row>
-    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
+        <v>69</v>
+      </c>
+      <c r="B215" t="s">
+        <v>15</v>
+      </c>
+      <c r="C215" t="s">
         <v>70</v>
-      </c>
-      <c r="B215" t="s">
-        <v>16</v>
-      </c>
-      <c r="C215" t="s">
-        <v>71</v>
       </c>
       <c r="D215">
         <v>319.48334</v>
       </c>
     </row>
-    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B216" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C216" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D216">
         <v>1110.0100874</v>
       </c>
     </row>
-    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B217" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C217" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E217">
         <v>131.24760000000001</v>
       </c>
     </row>
-    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B218" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C218" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E218">
         <v>77.801199999999994</v>
       </c>
     </row>
-    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B219" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C219" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E219">
         <v>49.610999999999997</v>
       </c>
     </row>
-    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B220" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C220" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E220">
         <v>36.58</v>
       </c>
     </row>
-    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B221" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C221" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D221">
         <v>22.643851017999999</v>
       </c>
     </row>
-    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B222" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C222" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D222">
         <v>147.13238000000001</v>
       </c>
     </row>
-    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B223" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C223" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D223">
         <v>102.867975</v>
       </c>
     </row>
-    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B224" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C224" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D224">
         <v>125.2624716</v>
       </c>
     </row>
-    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B225" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C225" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D225">
         <v>129.71071259999999</v>
       </c>
     </row>
-    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B226" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C226" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D226">
         <v>127.5998</v>
       </c>
     </row>
-    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B227" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C227" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D227">
         <v>466.77496559999997</v>
       </c>
     </row>
-    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
+        <v>69</v>
+      </c>
+      <c r="B228" t="s">
+        <v>16</v>
+      </c>
+      <c r="C228" t="s">
         <v>70</v>
-      </c>
-      <c r="B228" t="s">
-        <v>17</v>
-      </c>
-      <c r="C228" t="s">
-        <v>71</v>
       </c>
       <c r="E228">
         <v>270.72160000000002</v>
       </c>
     </row>
-    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B229" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C229" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E229">
         <v>145.33860000000001</v>
       </c>
     </row>
-    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B230" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C230" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E230">
         <v>50.883000000000003</v>
       </c>
     </row>
-    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B231" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C231" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E231">
         <v>62.96705</v>
       </c>
     </row>
-    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B232" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C232" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D232">
         <v>-33.634174170000001</v>
       </c>
     </row>
-    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B233" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C233" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D233">
         <v>91.021986687999998</v>
       </c>
     </row>
-    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B234" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C234" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D234">
         <v>66.466997524000007</v>
       </c>
     </row>
-    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B235" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C235" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D235">
         <v>41.544733348999998</v>
       </c>
     </row>
-    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B236" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C236" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D236">
         <v>1935.6160052</v>
       </c>
     </row>
-    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B237" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C237" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D237">
         <v>1093.40625</v>
       </c>
     </row>
-    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B238" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C238" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D238">
         <v>936.03599999999994</v>
       </c>
     </row>
-    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B239" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C239" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D239">
         <v>870.293138</v>
       </c>
     </row>
-    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B240" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C240" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D240">
         <v>703.93795499999999</v>
       </c>
     </row>
-    <row r="241" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B241" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C241" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D241">
         <v>453.33</v>
       </c>
     </row>
-    <row r="242" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B242" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C242" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D242">
         <v>490.97399999999999</v>
       </c>
     </row>
-    <row r="243" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B243" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C243" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D243">
         <v>465.35771999999997</v>
       </c>
     </row>
-    <row r="244" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B244" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C244" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D244">
         <v>2569.0349262</v>
       </c>
     </row>
-    <row r="245" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B245" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C245" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D245">
         <v>720</v>
       </c>
     </row>
-    <row r="246" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B246" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C246" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D246">
         <v>959.69100000000003</v>
       </c>
     </row>
-    <row r="247" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B247" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C247" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D247">
         <v>284.44299999999998</v>
       </c>
     </row>
-    <row r="248" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B248" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C248" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D248">
         <v>1763.249</v>
       </c>
     </row>
-    <row r="249" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B249" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C249" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D249">
         <v>1752.2063000000001</v>
       </c>
     </row>
-    <row r="250" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B250" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C250" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D250">
         <v>2495.8277849999999</v>
       </c>
     </row>
-    <row r="251" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B251" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C251" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D251">
         <v>2574.3249999999998</v>
       </c>
     </row>
-    <row r="252" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B252" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C252" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D252">
         <v>1101.24</v>
       </c>
     </row>
-    <row r="253" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B253" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C253" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D253">
         <v>191.304</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B254" t="s">
+        <v>78</v>
+      </c>
+      <c r="C254" t="s">
         <v>79</v>
-      </c>
-      <c r="C254" t="s">
-        <v>80</v>
       </c>
       <c r="D254">
         <v>388.8</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B255" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C255" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D255">
         <v>106.95099999999999</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B256" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C256" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D256">
         <v>374.26499999999999</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B257" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C257" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D257">
         <v>122.08</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
+        <v>25</v>
+      </c>
+      <c r="B258" t="s">
+        <v>78</v>
+      </c>
+      <c r="C258" t="s">
         <v>26</v>
-      </c>
-      <c r="B258" t="s">
-        <v>79</v>
-      </c>
-      <c r="C258" t="s">
-        <v>27</v>
       </c>
       <c r="D258">
         <v>116.294</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B259" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C259" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D259">
         <v>3805.7429999999999</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B260" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C260" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E260">
         <v>200</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B261" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C261" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E261">
         <v>275.238</v>
       </c>
     </row>
-    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
+        <v>69</v>
+      </c>
+      <c r="B262" t="s">
+        <v>78</v>
+      </c>
+      <c r="C262" t="s">
         <v>70</v>
-      </c>
-      <c r="B262" t="s">
-        <v>79</v>
-      </c>
-      <c r="C262" t="s">
-        <v>71</v>
       </c>
       <c r="D262">
         <v>321.96100000000001</v>
       </c>
     </row>
-    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B263" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C263" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D263">
         <v>229.74100000000001</v>
       </c>
     </row>
-    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B264" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C264" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D264">
         <v>157.09299999999999</v>
       </c>
     </row>
-    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B265" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C265" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D265">
         <v>169.16200000000001</v>
       </c>
     </row>
-    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B266" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C266" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D266">
         <v>364.79500000000002</v>
       </c>
     </row>
-    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B267" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C267" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D267">
         <v>28.222999999999999</v>
       </c>
     </row>
-    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
+        <v>69</v>
+      </c>
+      <c r="B268" t="s">
+        <v>78</v>
+      </c>
+      <c r="C268" t="s">
         <v>70</v>
-      </c>
-      <c r="B268" t="s">
-        <v>79</v>
-      </c>
-      <c r="C268" t="s">
-        <v>71</v>
       </c>
       <c r="E268">
         <v>111.91</v>
       </c>
     </row>
-    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B269" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C269" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E269">
         <v>92.884</v>
       </c>
     </row>
-    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B270" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C270" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E270">
         <v>47.414999999999999</v>
       </c>
     </row>
-    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B271" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C271" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E271">
         <v>156.172</v>
       </c>
     </row>
-    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
+        <v>17</v>
+      </c>
+      <c r="B272" t="s">
+        <v>78</v>
+      </c>
+      <c r="C272" t="s">
         <v>18</v>
       </c>
-      <c r="B272" t="s">
-        <v>79</v>
-      </c>
-      <c r="C272" t="s">
+    </row>
+    <row r="273" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A273" t="s">
+        <v>17</v>
+      </c>
+      <c r="B273" t="s">
+        <v>78</v>
+      </c>
+      <c r="C273" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A273" t="s">
-        <v>18</v>
-      </c>
-      <c r="B273" t="s">
-        <v>79</v>
-      </c>
-      <c r="C273" t="s">
-        <v>20</v>
       </c>
       <c r="D273">
         <v>312</v>
       </c>
     </row>
-    <row r="274" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B274" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C274" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D274">
         <v>8.3079999999999998</v>
       </c>
     </row>
-    <row r="275" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B275" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C275" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D275">
         <v>111.676</v>
       </c>
     </row>
-    <row r="276" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B276" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C276" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D276">
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B277" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C277" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D277">
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B278" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C278" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D278">
         <v>66.446399999999997</v>
       </c>
     </row>
-    <row r="279" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B279" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C279" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D279">
         <v>60.198599999999999</v>
       </c>
     </row>
-    <row r="280" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B280" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C280" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D280">
         <v>16.675999999999998</v>
       </c>
     </row>
-    <row r="281" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B281" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C281" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D281">
         <v>16.715</v>
       </c>
     </row>
-    <row r="282" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B282" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C282" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D282">
         <v>38.396999999999998</v>
       </c>
     </row>
-    <row r="283" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B283" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C283" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D283">
         <v>4.25</v>
       </c>
     </row>
-    <row r="284" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B284" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C284" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D284">
         <v>338</v>
       </c>
     </row>
-    <row r="285" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B285" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C285" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D285">
         <v>310</v>
       </c>
     </row>
-    <row r="286" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B286" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C286" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D286">
         <v>3048</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B287" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C287" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D287">
         <v>590</v>
       </c>
     </row>
-    <row r="288" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B288" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C288" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D288">
         <v>74.397000000000006</v>
       </c>
     </row>
-    <row r="289" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B289" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C289" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D289">
         <v>163.31</v>
       </c>
     </row>
-    <row r="290" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B290" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C290" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D290">
         <v>534.41600000000005</v>
       </c>
     </row>
-    <row r="291" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B291" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C291" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D291">
         <v>269</v>
       </c>
     </row>
-    <row r="292" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B292" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C292" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D292" s="2">
         <v>560.84807000000001</v>
       </c>
     </row>
-    <row r="293" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B293" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C293" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D293" s="2">
         <v>480.37799999999999</v>
       </c>
     </row>
-    <row r="294" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B294" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C294" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D294" s="2">
         <v>457.70800000000003</v>
       </c>
     </row>
-    <row r="295" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B295" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C295" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D295" s="2">
         <v>440.096</v>
       </c>
     </row>
-    <row r="296" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B296" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C296" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D296" s="2">
         <v>388.70979</v>
       </c>
     </row>
-    <row r="297" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B297" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C297" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D297" s="2">
         <v>386.8227</v>
       </c>
     </row>
-    <row r="298" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B298" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C298" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D298" s="2">
         <v>324.61559999999997</v>
       </c>
     </row>
-    <row r="299" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B299" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C299" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D299" s="2">
         <v>283.223343</v>
       </c>
     </row>
-    <row r="300" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B300" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C300" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D300" s="2">
         <v>257.17744499999998</v>
       </c>
     </row>
-    <row r="301" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B301" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C301" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D301" s="2">
         <v>267.80786999999998</v>
       </c>
     </row>
-    <row r="302" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B302" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C302" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D302" s="2">
         <v>236.04599999999999</v>
       </c>
     </row>
-    <row r="303" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B303" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C303" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D303" s="2">
         <v>207.93639999999999</v>
       </c>
     </row>
-    <row r="304" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B304" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C304" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D304" s="2">
         <v>184.02464000000001</v>
       </c>
     </row>
-    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B305" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C305" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D305" s="2">
         <v>186.27279999999999</v>
       </c>
     </row>
-    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B306" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C306" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D306" s="2">
         <v>181.30464520000001</v>
       </c>
     </row>
-    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B307" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C307" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D307" s="2">
         <v>180.90083999999999</v>
       </c>
     </row>
-    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B308" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C308" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D308" s="2">
         <v>152.46270000000001</v>
       </c>
     </row>
-    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B309" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C309" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D309" s="2">
         <v>152.52197609999999</v>
       </c>
     </row>
-    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B310" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C310" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D310" s="2">
         <v>140.721555</v>
       </c>
     </row>
-    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B311" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C311" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D311" s="2">
         <v>116.40547100000001</v>
       </c>
     </row>
-    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B312" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C312" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D312" s="2">
         <v>115.174015</v>
       </c>
     </row>
-    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B313" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C313" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D313" s="2">
         <v>115.07312</v>
       </c>
     </row>
-    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B314" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C314" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D314" s="2">
         <v>549.97500000000002</v>
       </c>
     </row>
-    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
+        <v>60</v>
+      </c>
+      <c r="B315" t="s">
+        <v>78</v>
+      </c>
+      <c r="C315" t="s">
         <v>61</v>
-      </c>
-      <c r="B315" t="s">
-        <v>79</v>
-      </c>
-      <c r="C315" t="s">
-        <v>62</v>
       </c>
       <c r="D315" s="2">
         <v>455.26299999999998</v>
       </c>
     </row>
-    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B316" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C316" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D316" s="2">
         <v>89</v>
       </c>
     </row>
-    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B317" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C317" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E317" s="2">
         <v>847.84166740000001</v>
       </c>
     </row>
-    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B318" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C318" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E318" s="2">
         <v>1503.1095700000001</v>
       </c>
     </row>
-    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B319" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C319" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E319" s="2">
         <v>211.977859</v>
       </c>
     </row>
-    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B320" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C320" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E320" s="2">
         <v>94.759552999999997</v>
       </c>
     </row>
-    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B321" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C321" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E321" s="2">
         <v>487.711995</v>
       </c>
     </row>
-    <row r="322" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B322" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C322" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E322" s="2">
         <v>915.09</v>
       </c>
     </row>
-    <row r="323" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B323" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C323" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D323">
         <v>518.94299999999998</v>
       </c>
     </row>
-    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
+        <v>43</v>
+      </c>
+      <c r="B324" t="s">
+        <v>78</v>
+      </c>
+      <c r="C324" t="s">
         <v>44</v>
-      </c>
-      <c r="B324" t="s">
-        <v>79</v>
-      </c>
-      <c r="C324" t="s">
-        <v>45</v>
       </c>
       <c r="D324">
         <v>575.76700000000005</v>
       </c>
     </row>
-    <row r="325" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B325" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C325" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D325">
         <v>145.67400000000001</v>
       </c>
     </row>
-    <row r="326" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B326" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C326" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D326">
         <v>118.684</v>
       </c>
     </row>
-    <row r="327" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B327" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C327" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D327">
         <v>104.973</v>
       </c>
     </row>
-    <row r="328" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B328" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C328" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D328">
         <v>476.053</v>
       </c>
     </row>
-    <row r="329" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B329" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C329" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D329">
         <v>1165.2354190000001</v>
       </c>
     </row>
-    <row r="330" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B330" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C330" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D330">
         <v>65.673950000000005</v>
       </c>
     </row>
-    <row r="331" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B331" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C331" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D331">
         <v>43.520085999999999</v>
       </c>
     </row>
-    <row r="332" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B332" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C332" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D332">
         <v>36.914999999999999</v>
       </c>
     </row>
-    <row r="333" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
+        <v>45</v>
+      </c>
+      <c r="B333" t="s">
+        <v>78</v>
+      </c>
+      <c r="C333" t="s">
         <v>46</v>
-      </c>
-      <c r="B333" t="s">
-        <v>79</v>
-      </c>
-      <c r="C333" t="s">
-        <v>47</v>
       </c>
       <c r="D333">
         <v>21.004349999999999</v>
       </c>
     </row>
-    <row r="334" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B334" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C334" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D334">
         <v>21.382999999999999</v>
       </c>
     </row>
-    <row r="335" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B335" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C335" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D335">
         <v>503.077</v>
       </c>
     </row>
-    <row r="336" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B336" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C336" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D336">
         <v>1834.9179999999999</v>

--- a/sql/Prop book.xlsx
+++ b/sql/Prop book.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29711"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thao Dien\Broker-page - Copy\sql\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dragoncapitalvn-my.sharepoint.com/personal/thaodien_dragoncapital_com/Documents/Thao Dien/Streamlit-broker/sql/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB7F0E6-1503-4633-A70B-4BF54763780E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{CCB7F0E6-1503-4633-A70B-4BF54763780E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8CD6C5C-1AAE-48E0-AF97-01F4261C1948}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,11 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$336</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,12 +39,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1199" uniqueCount="97">
+  <si>
+    <t>Ticker</t>
+  </si>
   <si>
     <t>Quarter</t>
   </si>
   <si>
-    <t>Ticker</t>
+    <t>Holdings</t>
   </si>
   <si>
     <t>FVTPL value</t>
@@ -119,45 +125,51 @@
     <t>TCB</t>
   </si>
   <si>
+    <t>VGI</t>
+  </si>
+  <si>
+    <t>GDA</t>
+  </si>
+  <si>
+    <t>SHB</t>
+  </si>
+  <si>
+    <t>TCD</t>
+  </si>
+  <si>
+    <t>FCN</t>
+  </si>
+  <si>
+    <t>TTC</t>
+  </si>
+  <si>
+    <t>PLC</t>
+  </si>
+  <si>
+    <t>NVL</t>
+  </si>
+  <si>
+    <t>HAH</t>
+  </si>
+  <si>
+    <t>GEE</t>
+  </si>
+  <si>
+    <t>BSR</t>
+  </si>
+  <si>
+    <t>SEA</t>
+  </si>
+  <si>
+    <t>GEI</t>
+  </si>
+  <si>
+    <t>PBT</t>
+  </si>
+  <si>
     <t>HPG</t>
   </si>
   <si>
-    <t>SHB</t>
-  </si>
-  <si>
-    <t>TCD</t>
-  </si>
-  <si>
-    <t>FCN</t>
-  </si>
-  <si>
-    <t>TTC</t>
-  </si>
-  <si>
-    <t>PLC</t>
-  </si>
-  <si>
-    <t>NVL</t>
-  </si>
-  <si>
-    <t>HAH</t>
-  </si>
-  <si>
-    <t>GEE</t>
-  </si>
-  <si>
-    <t>BSR</t>
-  </si>
-  <si>
-    <t>SEA</t>
-  </si>
-  <si>
-    <t>GEI</t>
-  </si>
-  <si>
-    <t>PBT</t>
-  </si>
-  <si>
     <t>CTG</t>
   </si>
   <si>
@@ -266,12 +278,6 @@
     <t>Other unlisted</t>
   </si>
   <si>
-    <t>VGI</t>
-  </si>
-  <si>
-    <t>GDA</t>
-  </si>
-  <si>
     <t>3Q25</t>
   </si>
   <si>
@@ -314,14 +320,23 @@
     <t>VRE</t>
   </si>
   <si>
-    <t>Holdings</t>
+    <t>4Q25</t>
+  </si>
+  <si>
+    <t>HT1</t>
+  </si>
+  <si>
+    <t>GVR</t>
+  </si>
+  <si>
+    <t>HHV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,6 +348,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -370,12 +391,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -678,4690 +700,5628 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:E336"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E399"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="5" max="6" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>92</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>598.5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <v>81.7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>1945.2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6">
         <v>180.69</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7">
         <v>3.3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8">
         <v>232.999</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9">
         <v>853</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10">
         <v>2756</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11">
         <v>796.99</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13">
         <v>1882.8</v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14">
         <v>11.73</v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15">
         <v>297.25</v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16">
         <v>139.4</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17">
         <v>803.12</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E18">
         <v>837.54</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
         <v>15</v>
-      </c>
-      <c r="C19" t="s">
-        <v>14</v>
       </c>
       <c r="E19">
         <v>1673.2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20">
         <v>1184</v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E22">
         <v>2117.6</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E24">
         <v>12.33</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E25">
         <v>167.5</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E26">
         <v>695.36</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E27">
         <v>772.4</v>
       </c>
     </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E28">
         <v>2070</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D29">
         <v>172.64</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B30" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D30">
         <v>282.2</v>
       </c>
     </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B31" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D31">
         <v>7.84</v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B32" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D32">
         <v>64.372</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B33" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D33">
         <v>105.5</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B34" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D34">
         <v>87.8</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B35" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D35">
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B36" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D36">
         <v>287.54000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B37" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D37">
         <v>177.85</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B38" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D38">
         <v>252.98500000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B39" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="D39">
         <v>91.463300000000004</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
+        <v>26</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>26</v>
+      </c>
+      <c r="B41" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" t="s">
         <v>25</v>
-      </c>
-      <c r="B40" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>25</v>
-      </c>
-      <c r="B41" t="s">
-        <v>5</v>
-      </c>
-      <c r="C41" t="s">
-        <v>24</v>
       </c>
       <c r="D41">
         <f>3528.12+314.938</f>
         <v>3843.058</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B42" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E42">
         <v>275.23899999999998</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B43" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E43">
         <v>200</v>
       </c>
     </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D44">
         <v>189.8</v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D45">
         <v>106.4</v>
       </c>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D46">
         <v>204.8</v>
       </c>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B47" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D47">
         <v>79.099999999999994</v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C48" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D48">
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B49" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C49" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D49">
         <v>0.1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B50" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D50">
         <v>170.9</v>
       </c>
     </row>
-    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B51" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D51">
         <v>238.4</v>
       </c>
     </row>
-    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B52" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D52">
         <v>123</v>
       </c>
     </row>
-    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B53" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D53">
         <v>91.6</v>
       </c>
     </row>
-    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B54" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C54" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D54">
         <v>71.3</v>
       </c>
     </row>
-    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B55" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C55" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D55">
         <v>47.6</v>
       </c>
     </row>
-    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B56" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C56" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D56">
         <v>178.9</v>
       </c>
     </row>
-    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B57" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C57" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D57">
         <v>10.3</v>
       </c>
     </row>
-    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B58" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C58" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D58">
         <v>1635</v>
       </c>
     </row>
-    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B59" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D59">
         <v>787</v>
       </c>
     </row>
-    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B60" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C60" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D60">
         <v>734.97</v>
       </c>
     </row>
-    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B61" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C61" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B62" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C62" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D62">
         <v>683.3</v>
       </c>
     </row>
-    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B63" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C63" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D63">
         <v>428.9</v>
       </c>
     </row>
-    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B64" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C64" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D64">
         <v>4362.4489999999996</v>
       </c>
     </row>
-    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B65" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C65" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D65">
         <v>684.67200000000003</v>
       </c>
     </row>
-    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B66" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C66" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D66">
         <v>873</v>
       </c>
     </row>
-    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B67" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C67" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D67">
         <v>298.214</v>
       </c>
     </row>
-    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B68" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C68" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D68">
         <v>1602.507328938</v>
       </c>
     </row>
-    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B69" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C69" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D69">
         <v>133.6666776649999</v>
       </c>
     </row>
-    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B70" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C70" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D70">
         <v>465.20486131000013</v>
       </c>
     </row>
-    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B71" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C71" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D71">
         <v>73.276574532000055</v>
       </c>
     </row>
-    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B72" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C72" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D72">
         <v>132.5779621770001</v>
       </c>
     </row>
-    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B73" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C73" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D73">
         <v>217.38459526099999</v>
       </c>
     </row>
-    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B74" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C74" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D74">
         <v>253.33511597899991</v>
       </c>
     </row>
-    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B75" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C75" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D75">
         <v>355.10702067800003</v>
       </c>
     </row>
-    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B76" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C76" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D76">
         <v>211.49055106</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B77" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C77" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D77">
         <v>313.72500000000002</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B78" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C78" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D78">
         <v>252.69882000000001</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B79" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C79" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D79">
         <v>131.61000000000001</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B80" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C80" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D80">
         <v>115.5</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B81" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C81" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D81">
         <v>80.653409999999994</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4">
       <c r="A82" t="s">
+        <v>26</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="s">
         <v>25</v>
-      </c>
-      <c r="B82" t="s">
-        <v>15</v>
-      </c>
-      <c r="C82" t="s">
-        <v>24</v>
       </c>
       <c r="D82">
         <v>4593.8958050000001</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B83" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C83" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B84" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C84" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B85" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C85" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D85">
         <v>385.00864000000001</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B86" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C86" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D86">
         <v>204.87155000000001</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B87" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C87" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D87">
         <v>449.16890000000001</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B88" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C88" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D88">
         <v>298.416</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4">
       <c r="A89" t="s">
+        <v>26</v>
+      </c>
+      <c r="B89" t="s">
+        <v>17</v>
+      </c>
+      <c r="C89" t="s">
         <v>25</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="s">
-        <v>24</v>
       </c>
       <c r="D89">
         <v>2868.1795425969999</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B90" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C90" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B91" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C91" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B92" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C92" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D92">
         <v>471.11800299999999</v>
       </c>
     </row>
-    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B93" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C93" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D93">
         <v>444.90018559999999</v>
       </c>
     </row>
-    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B94" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C94" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D94">
         <v>194.95070833</v>
       </c>
     </row>
-    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B95" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C95" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D95">
         <v>459.73992199999998</v>
       </c>
     </row>
-    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B96" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C96" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D96">
         <v>105.4291377</v>
       </c>
     </row>
-    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4">
       <c r="A97" t="s">
+        <v>46</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="s">
         <v>43</v>
-      </c>
-      <c r="B97" t="s">
-        <v>15</v>
-      </c>
-      <c r="C97" t="s">
-        <v>40</v>
       </c>
       <c r="D97">
         <v>112.9934461</v>
       </c>
     </row>
-    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B98" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C98" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D98">
         <v>795.19149128900006</v>
       </c>
     </row>
-    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B99" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C99" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D99">
         <v>418.20360959999999</v>
       </c>
     </row>
-    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B100" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C100" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D100">
         <v>379.16809019999999</v>
       </c>
     </row>
-    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B101" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C101" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D101">
         <v>641.44849673199997</v>
       </c>
     </row>
-    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B102" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C102" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D102">
         <v>495.18126749999999</v>
       </c>
     </row>
-    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B103" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C103" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D103">
         <v>41.564160000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B104" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C104" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D104">
         <v>34.574301900000002</v>
       </c>
     </row>
-    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B105" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C105" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D105">
         <v>17.764817699999998</v>
       </c>
     </row>
-    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B106" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C106" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D106">
         <v>377.74047731399997</v>
       </c>
     </row>
-    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B107" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C107" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D107">
         <v>47.814399999999999</v>
       </c>
     </row>
-    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B108" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C108" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D108">
         <v>105.3778854</v>
       </c>
     </row>
-    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B109" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C109" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D109">
         <v>45.304979000000003</v>
       </c>
     </row>
-    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B110" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C110" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D110">
         <v>883.491355</v>
       </c>
     </row>
-    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B111" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C111" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D111">
         <v>329.83531951999998</v>
       </c>
     </row>
-    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B112" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C112" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D112">
         <v>56.4498575</v>
       </c>
     </row>
-    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B113" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C113" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D113">
         <v>48.783651149999997</v>
       </c>
     </row>
-    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B114" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C114" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D114">
         <v>53.905700000000003</v>
       </c>
     </row>
-    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B115" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C115" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D115">
         <v>897.44555519999994</v>
       </c>
     </row>
-    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B116" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C116" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D116">
         <v>567.41111581400003</v>
       </c>
     </row>
-    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B117" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C117" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D117">
         <v>1219.89348</v>
       </c>
     </row>
-    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B118" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C118" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D118">
         <v>891.07434000000001</v>
       </c>
     </row>
-    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B119" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C119" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D119">
         <v>386.46965</v>
       </c>
     </row>
-    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B120" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C120" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D120">
         <v>376.3553</v>
       </c>
     </row>
-    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B121" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C121" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D121">
         <v>258.97612800000002</v>
       </c>
     </row>
-    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B122" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C122" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D122">
         <v>157.063692</v>
       </c>
     </row>
-    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B123" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C123" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D123">
         <v>80.896979999999999</v>
       </c>
     </row>
-    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B124" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C124" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D124">
         <v>66.592600000000004</v>
       </c>
     </row>
-    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B125" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C125" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D125">
         <v>35.567970000000003</v>
       </c>
     </row>
-    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B126" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C126" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D126">
         <v>32.722560000000001</v>
       </c>
     </row>
-    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B127" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C127" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D127">
         <v>76.413469636000002</v>
       </c>
     </row>
-    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B128" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C128" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D128">
         <v>51.984900000000003</v>
       </c>
     </row>
-    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B129" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C129" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D129">
         <v>54.700949999999999</v>
       </c>
     </row>
-    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B130" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C130" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D130">
         <v>43.162300000000002</v>
       </c>
     </row>
-    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B131" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C131" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D131">
         <v>37.572000000000003</v>
       </c>
     </row>
-    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B132" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C132" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D132">
         <v>26.318750000000001</v>
       </c>
     </row>
-    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B133" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C133" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D133">
         <v>24.028199999999998</v>
       </c>
     </row>
-    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B134" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C134" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D134">
         <v>21.36645</v>
       </c>
     </row>
-    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:4">
       <c r="A135" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B135" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C135" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D135">
         <v>17.355250000000002</v>
       </c>
     </row>
-    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:4">
       <c r="A136" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B136" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C136" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D136">
         <v>17.120100000000001</v>
       </c>
     </row>
-    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:4">
       <c r="A137" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B137" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C137" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D137">
         <v>16.202475</v>
       </c>
     </row>
-    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:4">
       <c r="A138" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B138" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C138" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D138">
         <v>13.5169</v>
       </c>
     </row>
-    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:4">
       <c r="A139" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B139" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C139" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D139">
         <v>8.3619000000000003</v>
       </c>
     </row>
-    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:4">
       <c r="A140" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B140" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C140" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D140">
         <v>2.3957999999999999</v>
       </c>
     </row>
-    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:4">
       <c r="A141" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B141" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C141" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D141">
         <v>1791.136023734</v>
       </c>
     </row>
-    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:4">
       <c r="A142" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B142" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C142" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D142">
         <v>691.42874749999999</v>
       </c>
     </row>
-    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B143" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C143" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D143">
         <v>437.546178</v>
       </c>
     </row>
-    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:4">
       <c r="A144" t="s">
+        <v>52</v>
+      </c>
+      <c r="B144" t="s">
+        <v>17</v>
+      </c>
+      <c r="C144" t="s">
         <v>49</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="s">
-        <v>46</v>
       </c>
       <c r="D144">
         <v>398.44944659999999</v>
       </c>
     </row>
-    <row r="145" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B145" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C145" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D145">
         <v>85.158848000000006</v>
       </c>
     </row>
-    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B146" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C146" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D146">
         <v>56.339108600000003</v>
       </c>
     </row>
-    <row r="147" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B147" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C147" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D147">
         <v>50.207640599999998</v>
       </c>
     </row>
-    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B148" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C148" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D148">
         <v>48.181075200000002</v>
       </c>
     </row>
-    <row r="149" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:4">
       <c r="A149" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B149" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C149" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D149">
         <v>48.151496999999999</v>
       </c>
     </row>
-    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B150" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C150" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D150">
         <v>38.785400000000003</v>
       </c>
     </row>
-    <row r="151" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B151" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C151" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D151">
         <v>33.768990000000002</v>
       </c>
     </row>
-    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B152" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C152" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D152">
         <v>27.742000000000001</v>
       </c>
     </row>
-    <row r="153" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B153" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C153" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D153">
         <v>26.166374399999999</v>
       </c>
     </row>
-    <row r="154" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B154" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C154" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D154">
         <v>312.90250348900003</v>
       </c>
     </row>
-    <row r="155" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B155" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C155" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D155">
         <v>537.23077231399998</v>
       </c>
     </row>
-    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B156" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C156" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D156">
         <v>1.2738610640000001</v>
       </c>
     </row>
-    <row r="157" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B157" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C157" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D157">
         <v>571.68737199999998</v>
       </c>
     </row>
-    <row r="158" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:4">
       <c r="A158" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B158" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C158" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D158">
         <v>1.2426057850000001</v>
       </c>
     </row>
-    <row r="159" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:4">
       <c r="A159" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B159" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C159" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D159">
         <v>81.770314499999998</v>
       </c>
     </row>
-    <row r="160" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:4">
       <c r="A160" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B160" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C160" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D160">
         <v>114.13664420000001</v>
       </c>
     </row>
-    <row r="161" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:4">
       <c r="A161" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B161" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C161" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D161">
         <v>74.028000000000006</v>
       </c>
     </row>
-    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B162" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C162" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D162">
         <v>334.50573044999999</v>
       </c>
     </row>
-    <row r="163" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B163" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C163" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D163">
         <v>82.876750000000001</v>
       </c>
     </row>
-    <row r="164" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B164" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C164" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D164">
         <v>96.033543249999994</v>
       </c>
     </row>
-    <row r="165" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B165" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C165" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D165">
         <v>619.63735652000003</v>
       </c>
     </row>
-    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B166" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C166" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D166">
         <v>66.806430000000006</v>
       </c>
     </row>
-    <row r="167" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B167" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C167" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D167">
         <v>62.841739349999997</v>
       </c>
     </row>
-    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B168" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C168" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D168">
         <v>64.178100000000001</v>
       </c>
     </row>
-    <row r="169" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B169" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C169" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D169">
         <v>462.98242733000001</v>
       </c>
     </row>
-    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:4">
       <c r="A170" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B170" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C170" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B171" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C171" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D171">
         <v>1.0325E-4</v>
       </c>
     </row>
-    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:4">
       <c r="A172" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B172" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C172" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B173" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C173" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D173">
         <v>1.1900000000000001E-4</v>
       </c>
     </row>
-    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B174" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C174" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B175" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C175" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D175">
         <v>64.729280000000003</v>
       </c>
     </row>
-    <row r="176" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:4">
       <c r="A176" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B176" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C176" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D176">
         <v>4.1003119999999997</v>
       </c>
     </row>
-    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:4">
       <c r="A177" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B177" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C177" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D177">
         <v>7.8800173759999996</v>
       </c>
     </row>
-    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B178" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C178" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D178">
         <v>57.4816</v>
       </c>
     </row>
-    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:4">
       <c r="A179" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B179" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C179" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D179">
         <v>3.4080650000000001E-3</v>
       </c>
     </row>
-    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B180" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C180" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D180">
         <v>9.5435766019999999</v>
       </c>
     </row>
-    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B181" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C181" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D181">
         <v>3.4080650000000001E-3</v>
       </c>
     </row>
-    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B182" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C182" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D182">
         <v>127</v>
       </c>
     </row>
-    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B183" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C183" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D183">
         <v>100</v>
       </c>
     </row>
-    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B184" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C184" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D184">
         <v>113</v>
       </c>
     </row>
-    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B185" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C185" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D185">
         <v>85</v>
       </c>
     </row>
-    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B186" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C186" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D186">
         <v>173</v>
       </c>
     </row>
-    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:4">
       <c r="A187" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B187" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C187" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D187">
         <v>179</v>
       </c>
     </row>
-    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:4">
       <c r="A188" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B188" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C188" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D188">
         <v>240</v>
       </c>
     </row>
-    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B189" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C189" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D189">
         <v>283</v>
       </c>
     </row>
-    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:4">
       <c r="A190" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B190" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C190" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D190">
         <v>285</v>
       </c>
     </row>
-    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:4">
       <c r="A191" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B191" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C191" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D191">
         <v>262</v>
       </c>
     </row>
-    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:4">
       <c r="A192" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B192" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C192" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D192">
         <v>47</v>
       </c>
     </row>
-    <row r="193" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B193" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C193" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D193">
         <v>51</v>
       </c>
     </row>
-    <row r="194" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:4">
       <c r="A194" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B194" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C194" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D194">
         <v>3</v>
       </c>
     </row>
-    <row r="195" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:4">
       <c r="A195" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B195" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C195" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D195">
         <v>6</v>
       </c>
     </row>
-    <row r="196" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:4">
       <c r="A196" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B196" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C196" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D196">
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:4">
       <c r="A197" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B197" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C197" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D197">
         <v>463</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:4">
       <c r="A198" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B198" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C198" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D198">
         <v>326</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:4">
       <c r="A199" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B199" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C199" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D199">
         <v>287</v>
       </c>
     </row>
-    <row r="200" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:4">
       <c r="A200" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B200" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C200" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D200">
         <v>1198</v>
       </c>
     </row>
-    <row r="201" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:4">
       <c r="A201" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B201" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C201" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D201">
         <v>1047</v>
       </c>
     </row>
-    <row r="202" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:4">
       <c r="A202" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B202" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C202" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D202">
         <v>555</v>
       </c>
     </row>
-    <row r="203" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B203" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C203" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D203">
         <v>488</v>
       </c>
     </row>
-    <row r="204" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:4">
       <c r="A204" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B204" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C204" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D204">
         <v>478</v>
       </c>
     </row>
-    <row r="205" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:4">
       <c r="A205" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B205" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C205" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D205">
         <v>275</v>
       </c>
     </row>
-    <row r="206" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:4">
       <c r="A206" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B206" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C206" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D206">
         <v>291.53755000000001</v>
       </c>
     </row>
-    <row r="207" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:4">
       <c r="A207" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B207" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C207" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D207">
         <v>97.599699999999999</v>
       </c>
     </row>
-    <row r="208" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:4">
       <c r="A208" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B208" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C208" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D208">
         <v>139.96039999999999</v>
       </c>
     </row>
-    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:5">
       <c r="A209" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B209" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C209" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D209">
         <v>126.0891627</v>
       </c>
     </row>
-    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B210" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C210" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D210">
         <v>484.16045324999999</v>
       </c>
     </row>
-    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:5">
       <c r="A211" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B211" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C211" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E211">
         <v>97.860349999999997</v>
       </c>
     </row>
-    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:5">
       <c r="A212" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B212" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C212" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E212">
         <v>118.3644</v>
       </c>
     </row>
-    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:5">
       <c r="A213" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B213" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C213" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E213">
         <v>40.125</v>
       </c>
     </row>
-    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:5">
       <c r="A214" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B214" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C214" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D214">
         <v>-17.442687286000002</v>
       </c>
     </row>
-    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:5">
       <c r="A215" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B215" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C215" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D215">
         <v>319.48334</v>
       </c>
     </row>
-    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:5">
       <c r="A216" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B216" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C216" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D216">
         <v>1110.0100874</v>
       </c>
     </row>
-    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:5">
       <c r="A217" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B217" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C217" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E217">
         <v>131.24760000000001</v>
       </c>
     </row>
-    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:5">
       <c r="A218" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B218" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C218" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E218">
         <v>77.801199999999994</v>
       </c>
     </row>
-    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:5">
       <c r="A219" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B219" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C219" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E219">
         <v>49.610999999999997</v>
       </c>
     </row>
-    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:5">
       <c r="A220" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B220" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C220" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E220">
         <v>36.58</v>
       </c>
     </row>
-    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:5">
       <c r="A221" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B221" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C221" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D221">
         <v>22.643851017999999</v>
       </c>
     </row>
-    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:5">
       <c r="A222" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B222" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C222" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D222">
         <v>147.13238000000001</v>
       </c>
     </row>
-    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:5">
       <c r="A223" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B223" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C223" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D223">
         <v>102.867975</v>
       </c>
     </row>
-    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:5">
       <c r="A224" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B224" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C224" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D224">
         <v>125.2624716</v>
       </c>
     </row>
-    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:5">
       <c r="A225" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B225" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C225" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D225">
         <v>129.71071259999999</v>
       </c>
     </row>
-    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:5">
       <c r="A226" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B226" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C226" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D226">
         <v>127.5998</v>
       </c>
     </row>
-    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:5">
       <c r="A227" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B227" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C227" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D227">
         <v>466.77496559999997</v>
       </c>
     </row>
-    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:5">
       <c r="A228" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B228" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C228" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E228">
         <v>270.72160000000002</v>
       </c>
     </row>
-    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:5">
       <c r="A229" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B229" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C229" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E229">
         <v>145.33860000000001</v>
       </c>
     </row>
-    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:5">
       <c r="A230" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B230" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C230" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E230">
         <v>50.883000000000003</v>
       </c>
     </row>
-    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:5">
       <c r="A231" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B231" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C231" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E231">
         <v>62.96705</v>
       </c>
     </row>
-    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:5">
       <c r="A232" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B232" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C232" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D232">
         <v>-33.634174170000001</v>
       </c>
     </row>
-    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:5">
       <c r="A233" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B233" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C233" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D233">
         <v>91.021986687999998</v>
       </c>
     </row>
-    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:5">
       <c r="A234" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B234" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C234" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D234">
         <v>66.466997524000007</v>
       </c>
     </row>
-    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:5">
       <c r="A235" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B235" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C235" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D235">
         <v>41.544733348999998</v>
       </c>
     </row>
-    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:5">
       <c r="A236" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B236" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C236" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D236">
         <v>1935.6160052</v>
       </c>
     </row>
-    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:5">
       <c r="A237" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B237" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C237" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D237">
         <v>1093.40625</v>
       </c>
     </row>
-    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:5">
       <c r="A238" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B238" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C238" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D238">
         <v>936.03599999999994</v>
       </c>
     </row>
-    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:5">
       <c r="A239" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B239" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C239" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D239">
         <v>870.293138</v>
       </c>
     </row>
-    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:5">
       <c r="A240" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B240" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C240" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D240">
         <v>703.93795499999999</v>
       </c>
     </row>
-    <row r="241" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B241" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C241" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D241">
         <v>453.33</v>
       </c>
     </row>
-    <row r="242" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:4">
       <c r="A242" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B242" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C242" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D242">
         <v>490.97399999999999</v>
       </c>
     </row>
-    <row r="243" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:4">
       <c r="A243" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B243" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C243" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D243">
         <v>465.35771999999997</v>
       </c>
     </row>
-    <row r="244" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B244" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C244" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D244">
         <v>2569.0349262</v>
       </c>
     </row>
-    <row r="245" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B245" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C245" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D245">
         <v>720</v>
       </c>
     </row>
-    <row r="246" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B246" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C246" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D246">
         <v>959.69100000000003</v>
       </c>
     </row>
-    <row r="247" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:4">
       <c r="A247" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B247" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C247" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D247">
         <v>284.44299999999998</v>
       </c>
     </row>
-    <row r="248" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B248" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C248" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D248">
         <v>1763.249</v>
       </c>
     </row>
-    <row r="249" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B249" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C249" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D249">
         <v>1752.2063000000001</v>
       </c>
     </row>
-    <row r="250" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B250" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C250" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D250">
         <v>2495.8277849999999</v>
       </c>
     </row>
-    <row r="251" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B251" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C251" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D251">
         <v>2574.3249999999998</v>
       </c>
     </row>
-    <row r="252" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:4">
       <c r="A252" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B252" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C252" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D252">
         <v>1101.24</v>
       </c>
     </row>
-    <row r="253" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:4">
       <c r="A253" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B253" t="s">
+        <v>79</v>
+      </c>
+      <c r="C253" t="s">
         <v>78</v>
-      </c>
-      <c r="C253" t="s">
-        <v>75</v>
       </c>
       <c r="D253">
         <v>191.304</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:4">
       <c r="A254" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B254" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C254" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D254">
         <v>388.8</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B255" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C255" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D255">
         <v>106.95099999999999</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B256" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C256" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D256">
         <v>374.26499999999999</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:5">
       <c r="A257" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B257" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C257" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D257">
         <v>122.08</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:5">
       <c r="A258" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B258" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C258" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D258">
         <v>116.294</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:5">
       <c r="A259" t="s">
+        <v>26</v>
+      </c>
+      <c r="B259" t="s">
+        <v>79</v>
+      </c>
+      <c r="C259" t="s">
         <v>25</v>
-      </c>
-      <c r="B259" t="s">
-        <v>78</v>
-      </c>
-      <c r="C259" t="s">
-        <v>24</v>
       </c>
       <c r="D259">
         <v>3805.7429999999999</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:5">
       <c r="A260" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B260" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C260" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E260">
         <v>200</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:5">
       <c r="A261" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B261" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C261" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E261">
         <v>275.238</v>
       </c>
     </row>
-    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:5">
       <c r="A262" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B262" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C262" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D262">
         <v>321.96100000000001</v>
       </c>
     </row>
-    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:5">
       <c r="A263" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B263" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C263" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D263">
         <v>229.74100000000001</v>
       </c>
     </row>
-    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:5">
       <c r="A264" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B264" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C264" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D264">
         <v>157.09299999999999</v>
       </c>
     </row>
-    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:5">
       <c r="A265" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B265" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C265" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D265">
         <v>169.16200000000001</v>
       </c>
     </row>
-    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:5">
       <c r="A266" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B266" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C266" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D266">
         <v>364.79500000000002</v>
       </c>
     </row>
-    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:5">
       <c r="A267" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B267" t="s">
+        <v>79</v>
+      </c>
+      <c r="C267" t="s">
         <v>78</v>
-      </c>
-      <c r="C267" t="s">
-        <v>75</v>
       </c>
       <c r="D267">
         <v>28.222999999999999</v>
       </c>
     </row>
-    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:5">
       <c r="A268" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B268" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C268" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E268">
         <v>111.91</v>
       </c>
     </row>
-    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:5">
       <c r="A269" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B269" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C269" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E269">
         <v>92.884</v>
       </c>
     </row>
-    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:5">
       <c r="A270" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B270" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C270" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E270">
         <v>47.414999999999999</v>
       </c>
     </row>
-    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:5">
       <c r="A271" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B271" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C271" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E271">
         <v>156.172</v>
       </c>
     </row>
-    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:5">
       <c r="A272" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B272" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C272" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="273" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A273" t="s">
-        <v>17</v>
-      </c>
       <c r="B273" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C273" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D273">
         <v>312</v>
       </c>
     </row>
-    <row r="274" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:4">
       <c r="A274" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B274" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C274" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D274">
         <v>8.3079999999999998</v>
       </c>
     </row>
-    <row r="275" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:4">
       <c r="A275" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B275" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C275" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D275">
         <v>111.676</v>
       </c>
     </row>
-    <row r="276" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B276" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C276" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D276">
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:4">
       <c r="A277" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B277" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C277" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D277">
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:4">
       <c r="A278" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B278" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C278" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D278">
         <v>66.446399999999997</v>
       </c>
     </row>
-    <row r="279" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:4">
       <c r="A279" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B279" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C279" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D279">
         <v>60.198599999999999</v>
       </c>
     </row>
-    <row r="280" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B280" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C280" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D280">
         <v>16.675999999999998</v>
       </c>
     </row>
-    <row r="281" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B281" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C281" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D281">
         <v>16.715</v>
       </c>
     </row>
-    <row r="282" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B282" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C282" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D282">
         <v>38.396999999999998</v>
       </c>
     </row>
-    <row r="283" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:4">
       <c r="A283" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B283" t="s">
+        <v>79</v>
+      </c>
+      <c r="C283" t="s">
         <v>78</v>
-      </c>
-      <c r="C283" t="s">
-        <v>75</v>
       </c>
       <c r="D283">
         <v>4.25</v>
       </c>
     </row>
-    <row r="284" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:4">
       <c r="A284" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B284" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C284" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D284">
         <v>338</v>
       </c>
     </row>
-    <row r="285" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:4">
       <c r="A285" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B285" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C285" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D285">
         <v>310</v>
       </c>
     </row>
-    <row r="286" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:4">
       <c r="A286" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B286" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C286" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D286">
         <v>3048</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:4">
       <c r="A287" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B287" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C287" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D287">
         <v>590</v>
       </c>
     </row>
-    <row r="288" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:4">
       <c r="A288" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B288" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C288" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D288">
         <v>74.397000000000006</v>
       </c>
     </row>
-    <row r="289" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B289" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C289" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D289">
         <v>163.31</v>
       </c>
     </row>
-    <row r="290" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:4">
       <c r="A290" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B290" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C290" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D290">
         <v>534.41600000000005</v>
       </c>
     </row>
-    <row r="291" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:4">
       <c r="A291" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B291" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C291" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D291">
         <v>269</v>
       </c>
     </row>
-    <row r="292" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:4">
       <c r="A292" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B292" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C292" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D292" s="2">
         <v>560.84807000000001</v>
       </c>
     </row>
-    <row r="293" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:4">
       <c r="A293" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B293" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C293" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D293" s="2">
         <v>480.37799999999999</v>
       </c>
     </row>
-    <row r="294" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:4">
       <c r="A294" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B294" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C294" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D294" s="2">
         <v>457.70800000000003</v>
       </c>
     </row>
-    <row r="295" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:4">
       <c r="A295" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B295" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C295" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D295" s="2">
         <v>440.096</v>
       </c>
     </row>
-    <row r="296" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:4">
       <c r="A296" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B296" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C296" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D296" s="2">
         <v>388.70979</v>
       </c>
     </row>
-    <row r="297" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:4">
       <c r="A297" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B297" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C297" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D297" s="2">
         <v>386.8227</v>
       </c>
     </row>
-    <row r="298" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B298" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C298" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D298" s="2">
         <v>324.61559999999997</v>
       </c>
     </row>
-    <row r="299" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B299" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C299" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D299" s="2">
         <v>283.223343</v>
       </c>
     </row>
-    <row r="300" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:4">
       <c r="A300" t="s">
+        <v>52</v>
+      </c>
+      <c r="B300" t="s">
+        <v>79</v>
+      </c>
+      <c r="C300" t="s">
         <v>49</v>
-      </c>
-      <c r="B300" t="s">
-        <v>78</v>
-      </c>
-      <c r="C300" t="s">
-        <v>46</v>
       </c>
       <c r="D300" s="2">
         <v>257.17744499999998</v>
       </c>
     </row>
-    <row r="301" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:4">
       <c r="A301" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B301" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C301" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D301" s="2">
         <v>267.80786999999998</v>
       </c>
     </row>
-    <row r="302" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:4">
       <c r="A302" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B302" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C302" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D302" s="2">
         <v>236.04599999999999</v>
       </c>
     </row>
-    <row r="303" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:4">
       <c r="A303" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B303" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C303" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D303" s="2">
         <v>207.93639999999999</v>
       </c>
     </row>
-    <row r="304" spans="1:4" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:4">
       <c r="A304" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B304" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C304" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D304" s="2">
         <v>184.02464000000001</v>
       </c>
     </row>
-    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:5">
       <c r="A305" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B305" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C305" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D305" s="2">
         <v>186.27279999999999</v>
       </c>
     </row>
-    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:5">
       <c r="A306" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B306" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C306" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D306" s="2">
         <v>181.30464520000001</v>
       </c>
     </row>
-    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:5">
       <c r="A307" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B307" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C307" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D307" s="2">
         <v>180.90083999999999</v>
       </c>
     </row>
-    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:5">
       <c r="A308" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B308" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C308" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D308" s="2">
         <v>152.46270000000001</v>
       </c>
     </row>
-    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:5">
       <c r="A309" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B309" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C309" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D309" s="2">
         <v>152.52197609999999</v>
       </c>
     </row>
-    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:5">
       <c r="A310" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B310" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C310" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D310" s="2">
         <v>140.721555</v>
       </c>
     </row>
-    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:5">
       <c r="A311" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B311" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C311" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D311" s="2">
         <v>116.40547100000001</v>
       </c>
     </row>
-    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:5">
       <c r="A312" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B312" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C312" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D312" s="2">
         <v>115.174015</v>
       </c>
     </row>
-    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:5">
       <c r="A313" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B313" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C313" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D313" s="2">
         <v>115.07312</v>
       </c>
     </row>
-    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:5">
       <c r="A314" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B314" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C314" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D314" s="2">
         <v>549.97500000000002</v>
       </c>
     </row>
-    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:5">
       <c r="A315" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B315" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C315" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D315" s="2">
         <v>455.26299999999998</v>
       </c>
     </row>
-    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:5">
       <c r="A316" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B316" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C316" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D316" s="2">
         <v>89</v>
       </c>
     </row>
-    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:5">
       <c r="A317" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B317" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C317" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E317" s="2">
         <v>847.84166740000001</v>
       </c>
     </row>
-    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:5">
       <c r="A318" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B318" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C318" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E318" s="2">
         <v>1503.1095700000001</v>
       </c>
     </row>
-    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:5">
       <c r="A319" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B319" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C319" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E319" s="2">
         <v>211.977859</v>
       </c>
     </row>
-    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:5">
       <c r="A320" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B320" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C320" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E320" s="2">
         <v>94.759552999999997</v>
       </c>
     </row>
-    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:5">
       <c r="A321" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B321" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C321" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E321" s="2">
         <v>487.711995</v>
       </c>
     </row>
-    <row r="322" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:5">
       <c r="A322" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B322" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C322" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E322" s="2">
         <v>915.09</v>
       </c>
     </row>
-    <row r="323" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:5">
       <c r="A323" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B323" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C323" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D323">
         <v>518.94299999999998</v>
       </c>
     </row>
-    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:5">
       <c r="A324" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B324" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C324" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D324">
         <v>575.76700000000005</v>
       </c>
     </row>
-    <row r="325" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:5">
       <c r="A325" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B325" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C325" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D325">
         <v>145.67400000000001</v>
       </c>
     </row>
-    <row r="326" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:5">
       <c r="A326" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B326" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C326" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D326">
         <v>118.684</v>
       </c>
     </row>
-    <row r="327" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:5">
       <c r="A327" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B327" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C327" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D327">
         <v>104.973</v>
       </c>
     </row>
-    <row r="328" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:5">
       <c r="A328" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B328" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C328" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D328">
         <v>476.053</v>
       </c>
     </row>
-    <row r="329" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:5">
       <c r="A329" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B329" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C329" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D329">
         <v>1165.2354190000001</v>
       </c>
     </row>
-    <row r="330" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:5">
       <c r="A330" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B330" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C330" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D330">
         <v>65.673950000000005</v>
       </c>
     </row>
-    <row r="331" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:5">
       <c r="A331" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B331" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C331" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D331">
         <v>43.520085999999999</v>
       </c>
     </row>
-    <row r="332" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:5">
       <c r="A332" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B332" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C332" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D332">
         <v>36.914999999999999</v>
       </c>
     </row>
-    <row r="333" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:5">
       <c r="A333" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B333" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C333" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D333">
         <v>21.004349999999999</v>
       </c>
     </row>
-    <row r="334" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:5">
       <c r="A334" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B334" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C334" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D334">
         <v>21.382999999999999</v>
       </c>
     </row>
-    <row r="335" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:5">
       <c r="A335" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B335" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C335" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D335">
         <v>503.077</v>
       </c>
     </row>
-    <row r="336" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:5">
       <c r="A336" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B336" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C336" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D336">
         <v>1834.9179999999999</v>
       </c>
     </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B337" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C337" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D337" s="3"/>
+      <c r="E337" s="3">
+        <v>130.22819999999999</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B338" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C338" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D338" s="3"/>
+      <c r="E338" s="3">
+        <v>588.78819999999996</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B339" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C339" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D339" s="3"/>
+      <c r="E339" s="3">
+        <v>1945.201</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B340" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C340" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D340" s="3"/>
+      <c r="E340" s="3">
+        <v>1065.241</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B341" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C341" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D341" s="3"/>
+      <c r="E341" s="3">
+        <v>450.94110000000001</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B342" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C342" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D342" s="3"/>
+      <c r="E342" s="3">
+        <v>194.75399999999999</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B343" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C343" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D343" s="3"/>
+      <c r="E343" s="3">
+        <v>148.81469999999999</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B344" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C344" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D344" s="3"/>
+      <c r="E344" s="3">
+        <v>884.07</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B345" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C345" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D345" s="3"/>
+      <c r="E345" s="3">
+        <v>6220.2439999999997</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B346" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C346" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D346" s="3">
+        <v>895.65959999999995</v>
+      </c>
+      <c r="E346" s="3"/>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B347" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C347" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D347" s="3">
+        <v>573.0258</v>
+      </c>
+      <c r="E347" s="3"/>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B348" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C348" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D348" s="3">
+        <v>566.82439999999997</v>
+      </c>
+      <c r="E348" s="3"/>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B349" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C349" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D349" s="3">
+        <v>539.90300000000002</v>
+      </c>
+      <c r="E349" s="3"/>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B350" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C350" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D350" s="3">
+        <v>441.00880000000001</v>
+      </c>
+      <c r="E350" s="3"/>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B351" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C351" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D351" s="3">
+        <v>449.50400000000002</v>
+      </c>
+      <c r="E351" s="3"/>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B352" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C352" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D352" s="3">
+        <v>114.608</v>
+      </c>
+      <c r="E352" s="3"/>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B353" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C353" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D353" s="3">
+        <v>103.3045</v>
+      </c>
+      <c r="E353" s="3"/>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B354" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C354" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D354" s="3">
+        <v>76.75103</v>
+      </c>
+      <c r="E354" s="3"/>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B355" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C355" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D355" s="3">
+        <v>25.04739</v>
+      </c>
+      <c r="E355" s="3"/>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B356" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C356" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D356" s="3">
+        <v>156.39400000000001</v>
+      </c>
+      <c r="E356" s="3"/>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B357" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C357" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D357" s="3">
+        <v>85.742490000000004</v>
+      </c>
+      <c r="E357" s="3"/>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B358" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C358" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D358" s="3">
+        <v>146.5582</v>
+      </c>
+      <c r="E358" s="3"/>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B359" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C359" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D359" s="3">
+        <v>103.8274</v>
+      </c>
+      <c r="E359" s="3"/>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B360" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C360" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D360" s="3">
+        <v>192.77430000000001</v>
+      </c>
+      <c r="E360" s="3"/>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B361" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C361" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D361" s="3">
+        <v>263.05500000000001</v>
+      </c>
+      <c r="E361" s="3"/>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B362" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C362" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D362" s="3">
+        <v>6.526484</v>
+      </c>
+      <c r="E362" s="3"/>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B363" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C363" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D363" s="3">
+        <v>128.44560000000001</v>
+      </c>
+      <c r="E363" s="3"/>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B364" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C364" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D364" s="3">
+        <v>53.37612</v>
+      </c>
+      <c r="E364" s="3"/>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B365" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C365" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D365" s="3">
+        <v>389.4</v>
+      </c>
+      <c r="E365" s="3"/>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B366" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C366" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D366" s="3">
+        <v>3.5529540000000002</v>
+      </c>
+      <c r="E366" s="3"/>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B367" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C367" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D367" s="3">
+        <v>411.45280000000002</v>
+      </c>
+      <c r="E367" s="3"/>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B368" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C368" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D368" s="3">
+        <v>157.95849999999999</v>
+      </c>
+      <c r="E368" s="3"/>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B369" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C369" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D369" s="3">
+        <v>71.276629999999997</v>
+      </c>
+      <c r="E369" s="3"/>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B370" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C370" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D370" s="3">
+        <v>112.9006</v>
+      </c>
+      <c r="E370" s="3"/>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B371" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C371" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D371" s="3">
+        <v>110.31440000000001</v>
+      </c>
+      <c r="E371" s="3"/>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B372" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C372" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D372" s="3">
+        <v>294.10660000000001</v>
+      </c>
+      <c r="E372" s="3"/>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B373" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C373" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D373" s="3"/>
+      <c r="E373" s="3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B374" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C374" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D374" s="3"/>
+      <c r="E374" s="3">
+        <v>108.3771</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B375" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C375" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D375" s="3"/>
+      <c r="E375" s="3">
+        <v>85.412999999999997</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B376" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C376" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D376" s="3"/>
+      <c r="E376" s="3">
+        <v>54.938780000000001</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B377" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C377" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D377" s="3"/>
+      <c r="E377" s="3">
+        <v>58.121400000000001</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B378" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C378" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D378" s="3">
+        <v>1444.508</v>
+      </c>
+      <c r="E378" s="3"/>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B379" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C379" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D379" s="3">
+        <v>4419</v>
+      </c>
+      <c r="E379" s="3"/>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B380" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C380" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D380" s="3">
+        <v>1960.6859999999999</v>
+      </c>
+      <c r="E380" s="3"/>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B381" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C381" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D381" s="3">
+        <v>3680.4520000000002</v>
+      </c>
+      <c r="E381" s="3"/>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B382" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C382" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D382" s="3">
+        <v>161.2002</v>
+      </c>
+      <c r="E382" s="3"/>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B383" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C383" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D383" s="3">
+        <v>187.70400000000001</v>
+      </c>
+      <c r="E383" s="3"/>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B384" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C384" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D384" s="3">
+        <v>207.11250000000001</v>
+      </c>
+      <c r="E384" s="3"/>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B385" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C385" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D385" s="3">
+        <v>112.6781</v>
+      </c>
+      <c r="E385" s="3"/>
+    </row>
+    <row r="386" spans="1:5">
+      <c r="A386" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B386" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C386" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D386" s="3">
+        <v>4982.0159999999996</v>
+      </c>
+      <c r="E386" s="3"/>
+    </row>
+    <row r="387" spans="1:5">
+      <c r="A387" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B387" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C387" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D387" s="3"/>
+      <c r="E387" s="3">
+        <v>1098.9069999999999</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5">
+      <c r="A388" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B388" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C388" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D388" s="3"/>
+      <c r="E388" s="3">
+        <v>24.5916</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5">
+      <c r="A389" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B389" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C389" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D389" s="3"/>
+      <c r="E389" s="3">
+        <v>412.8</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5">
+      <c r="A390" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B390" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C390" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D390">
+        <v>23.5277064</v>
+      </c>
+      <c r="E390" s="3"/>
+    </row>
+    <row r="391" spans="1:5">
+      <c r="A391" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B391" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C391" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D391">
+        <v>19.495491600000001</v>
+      </c>
+      <c r="E391" s="3"/>
+    </row>
+    <row r="392" spans="1:5">
+      <c r="A392" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B392" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C392" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D392">
+        <v>14.71466865</v>
+      </c>
+      <c r="E392" s="3"/>
+    </row>
+    <row r="393" spans="1:5">
+      <c r="A393" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B393" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C393" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D393">
+        <v>12.832848</v>
+      </c>
+      <c r="E393" s="3"/>
+    </row>
+    <row r="394" spans="1:5">
+      <c r="A394" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B394" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C394" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D394">
+        <v>5.9976611999999996</v>
+      </c>
+      <c r="E394" s="3"/>
+    </row>
+    <row r="395" spans="1:5">
+      <c r="A395" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B395" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C395" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D395">
+        <v>128.57965262900001</v>
+      </c>
+      <c r="E395" s="3"/>
+    </row>
+    <row r="396" spans="1:5">
+      <c r="A396" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B396" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C396" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D396">
+        <v>477.28037699999999</v>
+      </c>
+      <c r="E396" s="3"/>
+    </row>
+    <row r="397" spans="1:5">
+      <c r="A397" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B397" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C397" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D397">
+        <v>136.056116014</v>
+      </c>
+      <c r="E397" s="3"/>
+    </row>
+    <row r="398" spans="1:5">
+      <c r="A398" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B398" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C398" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D398">
+        <v>117.494845</v>
+      </c>
+      <c r="E398" s="3"/>
+    </row>
+    <row r="399" spans="1:5">
+      <c r="A399" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B399" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C399" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D399">
+        <v>1258.667852863</v>
+      </c>
+      <c r="E399" s="3"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E336" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="SHS"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:E336" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>